--- a/Financial Analysis/GPN.xlsx
+++ b/Financial Analysis/GPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{436C61DC-D82B-494B-9906-7A239926BB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C021EA47-1F82-41E3-AC2A-B62CF1BD66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{AC685D6A-8DC8-48D8-9A0E-762C4546B5AC}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="89">
   <si>
     <t>Price</t>
   </si>
@@ -209,9 +209,6 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Heavily overvalued</t>
-  </si>
-  <si>
     <t>debt is concerning, will margins get better?</t>
   </si>
   <si>
@@ -321,6 +318,15 @@
   </si>
   <si>
     <t>Q425</t>
+  </si>
+  <si>
+    <t>Q125 8K</t>
+  </si>
+  <si>
+    <t>Overvalued</t>
+  </si>
+  <si>
+    <t>FCF</t>
   </si>
 </sst>
 </file>
@@ -403,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -421,6 +427,7 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -840,108 +847,109 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BE2981-9185-411C-AB0F-A5F42B1AF254}">
-  <dimension ref="C2:H11"/>
+  <dimension ref="C2:I12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="11.21875" customWidth="1"/>
-    <col min="6" max="8" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="E2" s="2" t="s">
+        <v>7</v>
+      </c>
       <c r="F2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>92.41</v>
+        <v>75</v>
+      </c>
+      <c r="E3" s="3">
+        <v>45804</v>
       </c>
       <c r="F3" s="3">
-        <v>45751</v>
+        <f ca="1">TODAY()</f>
+        <v>45804</v>
       </c>
       <c r="G3" s="3">
-        <f ca="1">TODAY()</f>
-        <v>45751</v>
-      </c>
-      <c r="H3" s="3">
-        <v>45782</v>
-      </c>
-    </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.3">
+        <v>45873</v>
+      </c>
+    </row>
+    <row r="4" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <f>247.6</f>
-        <v>247.6</v>
+        <f>246.7</f>
+        <v>246.7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>22880.716</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+        <v>18502.5</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <f>2538.4</f>
-        <v>2538.4</v>
+        <f>2896</f>
+        <v>2896</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>4</v>
       </c>
       <c r="D7" s="1">
-        <f>503.4+1075.7+15164.7</f>
-        <v>16743.8</v>
+        <f>728+1180.4+15014.4</f>
+        <v>16922.8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="1">
         <f>D6-D7</f>
-        <v>-14205.4</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+        <v>-14026.8</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>37086.116000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="E11" t="s">
-        <v>50</v>
+        <v>32529.3</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I12" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -951,7 +959,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9961A0B3-6913-40B3-BC3C-2855853C34E2}">
-  <dimension ref="A2:EN70"/>
+  <dimension ref="A2:EN71"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
@@ -998,16 +1006,16 @@
         <v>32</v>
       </c>
       <c r="O2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="Q2" s="4" t="s">
+      <c r="R2" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="R2" s="4" t="s">
-        <v>86</v>
       </c>
       <c r="T2">
         <v>2019</v>
@@ -1103,20 +1111,19 @@
         <v>2515.4</v>
       </c>
       <c r="O3" s="7">
-        <f>K3*1.03</f>
-        <v>2492.806</v>
+        <v>2412.1</v>
       </c>
       <c r="P3" s="7">
-        <f t="shared" ref="P3:R3" si="0">L3*1.03</f>
-        <v>2645.864</v>
+        <f>L3*1.01</f>
+        <v>2594.4880000000003</v>
       </c>
       <c r="Q3" s="7">
-        <f t="shared" si="0"/>
-        <v>2679.6480000000001</v>
+        <f t="shared" ref="Q3:R3" si="0">M3*1.01</f>
+        <v>2627.616</v>
       </c>
       <c r="R3" s="7">
         <f t="shared" si="0"/>
-        <v>2590.8620000000001</v>
+        <v>2540.5540000000001</v>
       </c>
       <c r="T3" s="7">
         <v>4911.8999999999996</v>
@@ -1141,47 +1148,47 @@
       </c>
       <c r="Z3" s="7">
         <f>SUM(O3:R3)</f>
-        <v>10409.18</v>
+        <v>10174.758</v>
       </c>
       <c r="AA3" s="7">
         <f>Z3*1.03</f>
-        <v>10721.455400000001</v>
+        <v>10480.000739999999</v>
       </c>
       <c r="AB3" s="7">
         <f>AA3*1.02</f>
-        <v>10935.884508000001</v>
+        <v>10689.6007548</v>
       </c>
       <c r="AC3" s="7">
         <f t="shared" ref="AC3:AD3" si="1">AB3*1.02</f>
-        <v>11154.602198160001</v>
+        <v>10903.392769896</v>
       </c>
       <c r="AD3" s="7">
         <f t="shared" si="1"/>
-        <v>11377.694242123202</v>
+        <v>11121.460625293919</v>
       </c>
       <c r="AE3" s="7">
         <f>AD3*1.01</f>
-        <v>11491.471184544434</v>
+        <v>11232.675231546858</v>
       </c>
       <c r="AF3" s="7">
         <f t="shared" ref="AF3:AJ3" si="2">AE3*1.01</f>
-        <v>11606.385896389878</v>
+        <v>11345.001983862327</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" si="2"/>
-        <v>11722.449755353777</v>
+        <v>11458.45200370095</v>
       </c>
       <c r="AH3" s="7">
         <f t="shared" si="2"/>
-        <v>11839.674252907314</v>
+        <v>11573.036523737959</v>
       </c>
       <c r="AI3" s="7">
         <f t="shared" si="2"/>
-        <v>11958.070995436388</v>
+        <v>11688.766888975339</v>
       </c>
       <c r="AJ3" s="7">
         <f t="shared" si="2"/>
-        <v>12077.651705390752</v>
+        <v>11805.654557865091</v>
       </c>
     </row>
     <row r="4" spans="1:144" x14ac:dyDescent="0.3">
@@ -1225,20 +1232,19 @@
         <v>952.3</v>
       </c>
       <c r="O4" s="1">
-        <f>O3-O5</f>
-        <v>922.33822000000009</v>
+        <v>921.2</v>
       </c>
       <c r="P4" s="1">
         <f t="shared" ref="P4:R4" si="3">P3-P5</f>
-        <v>978.96967999999993</v>
+        <v>959.96055999999999</v>
       </c>
       <c r="Q4" s="1">
         <f t="shared" si="3"/>
-        <v>964.67327999999998</v>
+        <v>945.94175999999993</v>
       </c>
       <c r="R4" s="1">
         <f t="shared" si="3"/>
-        <v>984.52755999999999</v>
+        <v>965.41052000000013</v>
       </c>
       <c r="T4" s="1">
         <v>2073.8000000000002</v>
@@ -1263,47 +1269,47 @@
       </c>
       <c r="Z4" s="1">
         <f>SUM(O4:R4)</f>
-        <v>3850.5087399999998</v>
+        <v>3792.5128400000003</v>
       </c>
       <c r="AA4" s="1">
         <f t="shared" ref="AA4:AJ4" si="4">AA3-AA5</f>
-        <v>3752.5093900000002</v>
+        <v>3668.0002589999995</v>
       </c>
       <c r="AB4" s="1">
         <f t="shared" si="4"/>
-        <v>3827.5595777999997</v>
+        <v>3741.3602641799998</v>
       </c>
       <c r="AC4" s="1">
         <f t="shared" si="4"/>
-        <v>3904.1107693559998</v>
+        <v>3816.1874694635999</v>
       </c>
       <c r="AD4" s="1">
         <f t="shared" si="4"/>
-        <v>3982.1929847431202</v>
+        <v>3892.5112188528719</v>
       </c>
       <c r="AE4" s="1">
         <f t="shared" si="4"/>
-        <v>4022.0149145905516</v>
+        <v>3931.4363310414001</v>
       </c>
       <c r="AF4" s="1">
         <f t="shared" si="4"/>
-        <v>4062.2350637364571</v>
+        <v>3970.7506943518138</v>
       </c>
       <c r="AG4" s="1">
         <f t="shared" si="4"/>
-        <v>4102.8574143738215</v>
+        <v>4010.4582012953324</v>
       </c>
       <c r="AH4" s="1">
         <f t="shared" si="4"/>
-        <v>4143.8859885175598</v>
+        <v>4050.5627833082854</v>
       </c>
       <c r="AI4" s="1">
         <f t="shared" si="4"/>
-        <v>4185.3248484027354</v>
+        <v>4091.0684111413684</v>
       </c>
       <c r="AJ4" s="1">
         <f t="shared" si="4"/>
-        <v>4227.1780968867633</v>
+        <v>4131.9790952527819</v>
       </c>
     </row>
     <row r="5" spans="1:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1312,7 +1318,7 @@
         <v>33</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:N5" si="5">C3-C4</f>
+        <f t="shared" ref="C5:O5" si="5">C3-C4</f>
         <v>1199.1000000000001</v>
       </c>
       <c r="D5" s="7">
@@ -1360,20 +1366,20 @@
         <v>1563.1000000000001</v>
       </c>
       <c r="O5" s="7">
-        <f>O3*0.63</f>
-        <v>1570.4677799999999</v>
+        <f t="shared" si="5"/>
+        <v>1490.8999999999999</v>
       </c>
       <c r="P5" s="7">
         <f>P3*0.63</f>
-        <v>1666.8943200000001</v>
+        <v>1634.5274400000003</v>
       </c>
       <c r="Q5" s="7">
         <f>Q3*0.64</f>
-        <v>1714.9747200000002</v>
+        <v>1681.6742400000001</v>
       </c>
       <c r="R5" s="7">
         <f t="shared" ref="R5" si="6">R3*0.62</f>
-        <v>1606.3344400000001</v>
+        <v>1575.14348</v>
       </c>
       <c r="T5" s="7">
         <f t="shared" ref="T5:Y5" si="7">T3-T4</f>
@@ -1401,47 +1407,47 @@
       </c>
       <c r="Z5" s="7">
         <f>Z3*0.64</f>
-        <v>6661.8752000000004</v>
+        <v>6511.84512</v>
       </c>
       <c r="AA5" s="7">
         <f>AA3*0.65</f>
-        <v>6968.9460100000006</v>
+        <v>6812.000481</v>
       </c>
       <c r="AB5" s="7">
         <f t="shared" ref="AB5:AJ5" si="8">AB3*0.65</f>
-        <v>7108.3249302000013</v>
+        <v>6948.2404906199999</v>
       </c>
       <c r="AC5" s="7">
         <f t="shared" si="8"/>
-        <v>7250.4914288040009</v>
+        <v>7087.2053004323998</v>
       </c>
       <c r="AD5" s="7">
         <f t="shared" si="8"/>
-        <v>7395.5012573800814</v>
+        <v>7228.9494064410474</v>
       </c>
       <c r="AE5" s="7">
         <f t="shared" si="8"/>
-        <v>7469.4562699538828</v>
+        <v>7301.2389005054583</v>
       </c>
       <c r="AF5" s="7">
         <f t="shared" si="8"/>
-        <v>7544.1508326534213</v>
+        <v>7374.2512895105128</v>
       </c>
       <c r="AG5" s="7">
         <f t="shared" si="8"/>
-        <v>7619.5923409799552</v>
+        <v>7447.9938024056173</v>
       </c>
       <c r="AH5" s="7">
         <f t="shared" si="8"/>
-        <v>7695.7882643897547</v>
+        <v>7522.4737404296739</v>
       </c>
       <c r="AI5" s="7">
         <f t="shared" si="8"/>
-        <v>7772.746147033653</v>
+        <v>7597.6984778339702</v>
       </c>
       <c r="AJ5" s="7">
         <f t="shared" si="8"/>
-        <v>7850.4736085039885</v>
+        <v>7673.6754626123093</v>
       </c>
     </row>
     <row r="6" spans="1:144" x14ac:dyDescent="0.3">
@@ -1485,20 +1491,19 @@
         <v>1003.1</v>
       </c>
       <c r="O6" s="1">
-        <f>O3*0.43</f>
-        <v>1071.9065800000001</v>
+        <v>1024</v>
       </c>
       <c r="P6" s="1">
         <f>P3*0.42</f>
-        <v>1111.26288</v>
+        <v>1089.68496</v>
       </c>
       <c r="Q6" s="1">
         <f>Q3*0.42</f>
-        <v>1125.45216</v>
+        <v>1103.59872</v>
       </c>
       <c r="R6" s="1">
         <f>R3*0.39</f>
-        <v>1010.43618</v>
+        <v>990.81606000000011</v>
       </c>
       <c r="T6" s="1">
         <v>2046.7</v>
@@ -1523,47 +1528,47 @@
       </c>
       <c r="Z6" s="1">
         <f>SUM(O6:R6)</f>
-        <v>4319.0577999999996</v>
+        <v>4208.0997399999997</v>
       </c>
       <c r="AA6" s="1">
         <f>AA3*0.4</f>
-        <v>4288.5821600000008</v>
+        <v>4192.0002960000002</v>
       </c>
       <c r="AB6" s="1">
         <f>AB3*0.39</f>
-        <v>4264.9949581200008</v>
+        <v>4168.9442943719996</v>
       </c>
       <c r="AC6" s="1">
         <f t="shared" ref="AC6:AJ6" si="9">AC3*0.39</f>
-        <v>4350.2948572824007</v>
+        <v>4252.3231802594401</v>
       </c>
       <c r="AD6" s="1">
         <f t="shared" si="9"/>
-        <v>4437.300754428049</v>
+        <v>4337.3696438646284</v>
       </c>
       <c r="AE6" s="1">
         <f t="shared" si="9"/>
-        <v>4481.6737619723299</v>
+        <v>4380.7433403032746</v>
       </c>
       <c r="AF6" s="1">
         <f t="shared" si="9"/>
-        <v>4526.4904995920524</v>
+        <v>4424.5507737063072</v>
       </c>
       <c r="AG6" s="1">
         <f t="shared" si="9"/>
-        <v>4571.7554045879733</v>
+        <v>4468.7962814433704</v>
       </c>
       <c r="AH6" s="1">
         <f t="shared" si="9"/>
-        <v>4617.4729586338526</v>
+        <v>4513.4842442578047</v>
       </c>
       <c r="AI6" s="1">
         <f t="shared" si="9"/>
-        <v>4663.6476882201914</v>
+        <v>4558.6190867003825</v>
       </c>
       <c r="AJ6" s="1">
         <f t="shared" si="9"/>
-        <v>4710.2841651023937</v>
+        <v>4604.2052775673856</v>
       </c>
     </row>
     <row r="7" spans="1:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1621,19 +1626,19 @@
       </c>
       <c r="O7" s="7">
         <f t="shared" si="11"/>
-        <v>498.56119999999987</v>
+        <v>466.89999999999986</v>
       </c>
       <c r="P7" s="7">
         <f t="shared" si="11"/>
-        <v>555.63144000000011</v>
+        <v>544.84248000000025</v>
       </c>
       <c r="Q7" s="7">
         <f t="shared" si="11"/>
-        <v>589.52256000000011</v>
+        <v>578.0755200000001</v>
       </c>
       <c r="R7" s="7">
         <f t="shared" si="11"/>
-        <v>595.89826000000005</v>
+        <v>584.32741999999985</v>
       </c>
       <c r="T7" s="7">
         <f t="shared" ref="T7:Y7" si="12">T5-T6</f>
@@ -1661,47 +1666,47 @@
       </c>
       <c r="Z7" s="7">
         <f t="shared" ref="Z7:AJ7" si="13">Z5-Z6</f>
-        <v>2342.8174000000008</v>
+        <v>2303.7453800000003</v>
       </c>
       <c r="AA7" s="7">
         <f t="shared" si="13"/>
-        <v>2680.3638499999997</v>
+        <v>2620.0001849999999</v>
       </c>
       <c r="AB7" s="7">
         <f t="shared" si="13"/>
-        <v>2843.3299720800005</v>
+        <v>2779.2961962480003</v>
       </c>
       <c r="AC7" s="7">
         <f t="shared" si="13"/>
-        <v>2900.1965715216002</v>
+        <v>2834.8821201729597</v>
       </c>
       <c r="AD7" s="7">
         <f t="shared" si="13"/>
-        <v>2958.2005029520324</v>
+        <v>2891.5797625764189</v>
       </c>
       <c r="AE7" s="7">
         <f t="shared" si="13"/>
-        <v>2987.782507981553</v>
+        <v>2920.4955602021837</v>
       </c>
       <c r="AF7" s="7">
         <f t="shared" si="13"/>
-        <v>3017.6603330613689</v>
+        <v>2949.7005158042057</v>
       </c>
       <c r="AG7" s="7">
         <f t="shared" si="13"/>
-        <v>3047.8369363919819</v>
+        <v>2979.1975209622469</v>
       </c>
       <c r="AH7" s="7">
         <f t="shared" si="13"/>
-        <v>3078.315305755902</v>
+        <v>3008.9894961718692</v>
       </c>
       <c r="AI7" s="7">
         <f t="shared" si="13"/>
-        <v>3109.0984588134615</v>
+        <v>3039.0793911335877</v>
       </c>
       <c r="AJ7" s="7">
         <f t="shared" si="13"/>
-        <v>3140.1894434015949</v>
+        <v>3069.4701850449237</v>
       </c>
     </row>
     <row r="8" spans="1:144" x14ac:dyDescent="0.3">
@@ -1746,7 +1751,7 @@
         <v>-273.10000000000002</v>
       </c>
       <c r="O8" s="1">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="P8" s="1">
         <v>0</v>
@@ -1780,7 +1785,7 @@
       </c>
       <c r="Z8" s="1">
         <f>SUM(O8:R8)</f>
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="AA8" s="1">
         <v>0</v>
@@ -1854,8 +1859,7 @@
         <v>-42.6</v>
       </c>
       <c r="O9" s="1">
-        <f>K9*1.01</f>
-        <v>-36.259</v>
+        <v>-39.4</v>
       </c>
       <c r="P9" s="1">
         <f t="shared" ref="P9:R9" si="14">L9*1.01</f>
@@ -1892,47 +1896,47 @@
       </c>
       <c r="Z9" s="1">
         <f>SUM(O9:R9)</f>
-        <v>-170.791</v>
+        <v>-173.93200000000002</v>
       </c>
       <c r="AA9" s="1">
         <f>Z9*1.03</f>
-        <v>-175.91472999999999</v>
+        <v>-179.14996000000002</v>
       </c>
       <c r="AB9" s="1">
         <f t="shared" ref="AB9:AJ9" si="15">AA9*1.03</f>
-        <v>-181.19217190000001</v>
+        <v>-184.52445880000002</v>
       </c>
       <c r="AC9" s="1">
         <f t="shared" si="15"/>
-        <v>-186.627937057</v>
+        <v>-190.06019256400003</v>
       </c>
       <c r="AD9" s="1">
         <f t="shared" si="15"/>
-        <v>-192.22677516870999</v>
+        <v>-195.76199834092003</v>
       </c>
       <c r="AE9" s="1">
         <f t="shared" si="15"/>
-        <v>-197.99357842377128</v>
+        <v>-201.63485829114762</v>
       </c>
       <c r="AF9" s="1">
         <f t="shared" si="15"/>
-        <v>-203.93338577648441</v>
+        <v>-207.68390403988207</v>
       </c>
       <c r="AG9" s="1">
         <f t="shared" si="15"/>
-        <v>-210.05138734977896</v>
+        <v>-213.91442116107854</v>
       </c>
       <c r="AH9" s="1">
         <f t="shared" si="15"/>
-        <v>-216.35292897027233</v>
+        <v>-220.33185379591089</v>
       </c>
       <c r="AI9" s="1">
         <f t="shared" si="15"/>
-        <v>-222.8435168393805</v>
+        <v>-226.94180940978822</v>
       </c>
       <c r="AJ9" s="1">
         <f t="shared" si="15"/>
-        <v>-229.52882234456192</v>
+        <v>-233.75006369208188</v>
       </c>
     </row>
     <row r="10" spans="1:144" x14ac:dyDescent="0.3">
@@ -1976,8 +1980,7 @@
         <v>156.80000000000001</v>
       </c>
       <c r="O10" s="1">
-        <f>K10*0.99</f>
-        <v>160.47899999999998</v>
+        <v>157.1</v>
       </c>
       <c r="P10" s="1">
         <f t="shared" ref="P10:R10" si="16">L10*0.99</f>
@@ -2014,47 +2017,47 @@
       </c>
       <c r="Z10" s="1">
         <f>SUM(O10:R10)</f>
-        <v>627.66</v>
+        <v>624.28099999999995</v>
       </c>
       <c r="AA10" s="1">
         <f t="shared" ref="AA10:AJ10" si="17">Z10*0.99</f>
-        <v>621.38339999999994</v>
+        <v>618.03818999999999</v>
       </c>
       <c r="AB10" s="1">
         <f t="shared" si="17"/>
-        <v>615.16956599999992</v>
+        <v>611.85780809999994</v>
       </c>
       <c r="AC10" s="1">
         <f t="shared" si="17"/>
-        <v>609.01787033999994</v>
+        <v>605.73923001899993</v>
       </c>
       <c r="AD10" s="1">
         <f t="shared" si="17"/>
-        <v>602.92769163659989</v>
+        <v>599.6818377188099</v>
       </c>
       <c r="AE10" s="1">
         <f t="shared" si="17"/>
-        <v>596.89841472023386</v>
+        <v>593.6850193416218</v>
       </c>
       <c r="AF10" s="1">
         <f t="shared" si="17"/>
-        <v>590.92943057303148</v>
+        <v>587.74816914820553</v>
       </c>
       <c r="AG10" s="1">
         <f t="shared" si="17"/>
-        <v>585.02013626730115</v>
+        <v>581.87068745672343</v>
       </c>
       <c r="AH10" s="1">
         <f t="shared" si="17"/>
-        <v>579.16993490462812</v>
+        <v>576.05198058215615</v>
       </c>
       <c r="AI10" s="1">
         <f t="shared" si="17"/>
-        <v>573.3782355555818</v>
+        <v>570.29146077633459</v>
       </c>
       <c r="AJ10" s="1">
         <f t="shared" si="17"/>
-        <v>567.64445320002596</v>
+        <v>564.58854616857127</v>
       </c>
     </row>
     <row r="11" spans="1:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2112,19 +2115,19 @@
       </c>
       <c r="O11" s="7">
         <f t="shared" si="19"/>
-        <v>374.3411999999999</v>
+        <v>353.19999999999982</v>
       </c>
       <c r="P11" s="7">
         <f t="shared" si="19"/>
-        <v>433.67644000000018</v>
+        <v>422.88748000000032</v>
       </c>
       <c r="Q11" s="7">
         <f t="shared" si="19"/>
-        <v>491.03456000000006</v>
+        <v>479.58752000000004</v>
       </c>
       <c r="R11" s="7">
         <f t="shared" si="19"/>
-        <v>483.69226000000003</v>
+        <v>472.12141999999983</v>
       </c>
       <c r="T11" s="7">
         <f t="shared" ref="T11:Z11" si="20">T7-T8-T9-T10</f>
@@ -2152,47 +2155,47 @@
       </c>
       <c r="Z11" s="7">
         <f t="shared" si="20"/>
-        <v>1885.9484000000011</v>
+        <v>1857.3963800000001</v>
       </c>
       <c r="AA11" s="7">
         <f t="shared" ref="AA11:AJ11" si="21">AA7-AA8-AA9-AA10</f>
-        <v>2234.8951799999995</v>
+        <v>2181.1119550000003</v>
       </c>
       <c r="AB11" s="7">
         <f t="shared" si="21"/>
-        <v>2409.3525779800007</v>
+        <v>2351.9628469480003</v>
       </c>
       <c r="AC11" s="7">
         <f t="shared" si="21"/>
-        <v>2477.8066382386005</v>
+        <v>2419.2030827179597</v>
       </c>
       <c r="AD11" s="7">
         <f t="shared" si="21"/>
-        <v>2547.4995864841426</v>
+        <v>2487.6599231985292</v>
       </c>
       <c r="AE11" s="7">
         <f t="shared" si="21"/>
-        <v>2588.8776716850907</v>
+        <v>2528.4453991517098</v>
       </c>
       <c r="AF11" s="7">
         <f t="shared" si="21"/>
-        <v>2630.6642882648221</v>
+        <v>2569.6362506958822</v>
       </c>
       <c r="AG11" s="7">
         <f t="shared" si="21"/>
-        <v>2672.8681874744598</v>
+        <v>2611.2412546666023</v>
       </c>
       <c r="AH11" s="7">
         <f t="shared" si="21"/>
-        <v>2715.4982998215464</v>
+        <v>2653.2693693856236</v>
       </c>
       <c r="AI11" s="7">
         <f t="shared" si="21"/>
-        <v>2758.5637400972601</v>
+        <v>2695.7297397670413</v>
       </c>
       <c r="AJ11" s="7">
         <f t="shared" si="21"/>
-        <v>2802.0738125461307</v>
+        <v>2738.6317025684343</v>
       </c>
     </row>
     <row r="12" spans="1:144" x14ac:dyDescent="0.3">
@@ -2236,20 +2239,19 @@
         <v>140.5</v>
       </c>
       <c r="O12" s="1">
-        <f>O11*0.16</f>
-        <v>59.894591999999989</v>
+        <v>58.7</v>
       </c>
       <c r="P12" s="1">
         <f t="shared" ref="P12:R12" si="22">P11*0.16</f>
-        <v>69.388230400000026</v>
+        <v>67.661996800000054</v>
       </c>
       <c r="Q12" s="1">
         <f t="shared" si="22"/>
-        <v>78.565529600000005</v>
+        <v>76.734003200000004</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" si="22"/>
-        <v>77.390761600000005</v>
+        <v>75.539427199999977</v>
       </c>
       <c r="T12" s="1">
         <v>62.2</v>
@@ -2274,47 +2276,47 @@
       </c>
       <c r="Z12" s="1">
         <f>SUM(O12:R12)</f>
-        <v>285.23911360000005</v>
+        <v>278.63542720000004</v>
       </c>
       <c r="AA12" s="1">
         <f t="shared" ref="AA12:AJ12" si="23">AA11*0.17</f>
-        <v>379.93218059999992</v>
+        <v>370.78903235000007</v>
       </c>
       <c r="AB12" s="1">
         <f t="shared" si="23"/>
-        <v>409.58993825660013</v>
+        <v>399.83368398116011</v>
       </c>
       <c r="AC12" s="1">
         <f t="shared" si="23"/>
-        <v>421.22712850056212</v>
+        <v>411.26452406205317</v>
       </c>
       <c r="AD12" s="1">
         <f t="shared" si="23"/>
-        <v>433.07492970230425</v>
+        <v>422.90218694375</v>
       </c>
       <c r="AE12" s="1">
         <f t="shared" si="23"/>
-        <v>440.10920418646543</v>
+        <v>429.83571785579068</v>
       </c>
       <c r="AF12" s="1">
         <f t="shared" si="23"/>
-        <v>447.21292900501976</v>
+        <v>436.83816261829998</v>
       </c>
       <c r="AG12" s="1">
         <f t="shared" si="23"/>
-        <v>454.38759187065818</v>
+        <v>443.91101329332241</v>
       </c>
       <c r="AH12" s="1">
         <f t="shared" si="23"/>
-        <v>461.63471096966293</v>
+        <v>451.05579279555604</v>
       </c>
       <c r="AI12" s="1">
         <f t="shared" si="23"/>
-        <v>468.95583581653426</v>
+        <v>458.27405576039706</v>
       </c>
       <c r="AJ12" s="1">
         <f t="shared" si="23"/>
-        <v>476.35254813284229</v>
+        <v>465.56738943663385</v>
       </c>
     </row>
     <row r="13" spans="1:144" x14ac:dyDescent="0.3">
@@ -2358,20 +2360,19 @@
         <v>-19.899999999999999</v>
       </c>
       <c r="O13" s="1">
-        <f>-O11*0.04</f>
-        <v>-14.973647999999997</v>
+        <v>-18.3</v>
       </c>
       <c r="P13" s="1">
         <f t="shared" ref="P13:R13" si="24">-P11*0.04</f>
-        <v>-17.347057600000007</v>
+        <v>-16.915499200000014</v>
       </c>
       <c r="Q13" s="1">
         <f t="shared" si="24"/>
-        <v>-19.641382400000001</v>
+        <v>-19.183500800000001</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" si="24"/>
-        <v>-19.347690400000001</v>
+        <v>-18.884856799999994</v>
       </c>
       <c r="T13" s="1">
         <v>-13.5</v>
@@ -2396,47 +2397,47 @@
       </c>
       <c r="Z13" s="1">
         <f>SUM(O13:R13)</f>
-        <v>-71.309778400000013</v>
+        <v>-73.283856800000009</v>
       </c>
       <c r="AA13" s="1">
         <f>Z13*1.02</f>
-        <v>-72.73597396800001</v>
+        <v>-74.749533936000006</v>
       </c>
       <c r="AB13" s="1">
         <f t="shared" ref="AB13:AJ13" si="25">AA13*1.02</f>
-        <v>-74.190693447360019</v>
+        <v>-76.244524614720007</v>
       </c>
       <c r="AC13" s="1">
         <f t="shared" si="25"/>
-        <v>-75.674507316307214</v>
+        <v>-77.76941510701441</v>
       </c>
       <c r="AD13" s="1">
         <f t="shared" si="25"/>
-        <v>-77.187997462633362</v>
+        <v>-79.324803409154697</v>
       </c>
       <c r="AE13" s="1">
         <f t="shared" si="25"/>
-        <v>-78.731757411886036</v>
+        <v>-80.911299477337792</v>
       </c>
       <c r="AF13" s="1">
         <f t="shared" si="25"/>
-        <v>-80.306392560123754</v>
+        <v>-82.52952546688455</v>
       </c>
       <c r="AG13" s="1">
         <f t="shared" si="25"/>
-        <v>-81.912520411326227</v>
+        <v>-84.18011597622224</v>
       </c>
       <c r="AH13" s="1">
         <f t="shared" si="25"/>
-        <v>-83.550770819552753</v>
+        <v>-85.863718295746679</v>
       </c>
       <c r="AI13" s="1">
         <f t="shared" si="25"/>
-        <v>-85.22178623594381</v>
+        <v>-87.580992661661611</v>
       </c>
       <c r="AJ13" s="1">
         <f t="shared" si="25"/>
-        <v>-86.926221960662687</v>
+        <v>-89.332612514894848</v>
       </c>
     </row>
     <row r="14" spans="1:144" x14ac:dyDescent="0.3">
@@ -2480,20 +2481,19 @@
         <v>31.1</v>
       </c>
       <c r="O14" s="1">
-        <f>O11*0.045</f>
-        <v>16.845353999999993</v>
+        <v>7</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" ref="P14:R14" si="26">P11*0.045</f>
-        <v>19.515439800000006</v>
+        <v>19.029936600000013</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="26"/>
-        <v>22.096555200000001</v>
+        <v>21.5814384</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" si="26"/>
-        <v>21.766151700000002</v>
+        <v>21.24546389999999</v>
       </c>
       <c r="T14" s="1">
         <v>38.700000000000003</v>
@@ -2518,47 +2518,47 @@
       </c>
       <c r="Z14" s="1">
         <f>SUM(O14:R14)</f>
-        <v>80.223500699999988</v>
+        <v>68.8568389</v>
       </c>
       <c r="AA14" s="1">
         <f t="shared" ref="AA14:AJ14" si="27">Z14*1.005</f>
-        <v>80.624618203499978</v>
+        <v>69.201123094499991</v>
       </c>
       <c r="AB14" s="1">
         <f t="shared" si="27"/>
-        <v>81.027741294517469</v>
+        <v>69.547128709972483</v>
       </c>
       <c r="AC14" s="1">
         <f t="shared" si="27"/>
-        <v>81.432880000990053</v>
+        <v>69.894864353522337</v>
       </c>
       <c r="AD14" s="1">
         <f t="shared" si="27"/>
-        <v>81.840044400994998</v>
+        <v>70.244338675289939</v>
       </c>
       <c r="AE14" s="1">
         <f t="shared" si="27"/>
-        <v>82.249244622999967</v>
+        <v>70.595560368666384</v>
       </c>
       <c r="AF14" s="1">
         <f t="shared" si="27"/>
-        <v>82.660490846114953</v>
+        <v>70.948538170509707</v>
       </c>
       <c r="AG14" s="1">
         <f t="shared" si="27"/>
-        <v>83.073793300345514</v>
+        <v>71.303280861362254</v>
       </c>
       <c r="AH14" s="1">
         <f t="shared" si="27"/>
-        <v>83.489162266847231</v>
+        <v>71.659797265669056</v>
       </c>
       <c r="AI14" s="1">
         <f t="shared" si="27"/>
-        <v>83.906608078181463</v>
+        <v>72.018096251997392</v>
       </c>
       <c r="AJ14" s="1">
         <f t="shared" si="27"/>
-        <v>84.326141118572366</v>
+        <v>72.378186733257365</v>
       </c>
     </row>
     <row r="15" spans="1:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2616,19 +2616,19 @@
       </c>
       <c r="O15" s="7">
         <f t="shared" ref="O15:R15" si="30">O11-O12-O13-O14</f>
-        <v>312.57490199999989</v>
+        <v>305.79999999999984</v>
       </c>
       <c r="P15" s="7">
         <f t="shared" si="30"/>
-        <v>362.11982740000019</v>
+        <v>353.11104580000028</v>
       </c>
       <c r="Q15" s="7">
         <f t="shared" si="30"/>
-        <v>410.01385760000005</v>
+        <v>400.45557919999999</v>
       </c>
       <c r="R15" s="7">
         <f t="shared" si="30"/>
-        <v>403.88303709999997</v>
+        <v>394.22138569999981</v>
       </c>
       <c r="T15" s="7">
         <f t="shared" ref="T15:Y15" si="31">T11-T12-T13-T14</f>
@@ -2656,479 +2656,479 @@
       </c>
       <c r="Z15" s="7">
         <f t="shared" ref="Z15" si="32">Z11-Z12-Z13-Z14</f>
-        <v>1591.795564100001</v>
+        <v>1583.1879707000001</v>
       </c>
       <c r="AA15" s="7">
         <f t="shared" ref="AA15" si="33">AA11-AA12-AA13-AA14</f>
-        <v>1847.0743551644998</v>
+        <v>1815.8713334915003</v>
       </c>
       <c r="AB15" s="7">
         <f t="shared" ref="AB15" si="34">AB11-AB12-AB13-AB14</f>
-        <v>1992.9255918762433</v>
+        <v>1958.8265588715878</v>
       </c>
       <c r="AC15" s="7">
         <f t="shared" ref="AC15" si="35">AC11-AC12-AC13-AC14</f>
-        <v>2050.8211370533554</v>
+        <v>2015.8131094093987</v>
       </c>
       <c r="AD15" s="7">
         <f t="shared" ref="AD15" si="36">AD11-AD12-AD13-AD14</f>
-        <v>2109.7726098434769</v>
+        <v>2073.8382009886441</v>
       </c>
       <c r="AE15" s="7">
         <f t="shared" ref="AE15" si="37">AE11-AE12-AE13-AE14</f>
-        <v>2145.2509802875115</v>
+        <v>2108.9254204045901</v>
       </c>
       <c r="AF15" s="7">
         <f t="shared" ref="AF15" si="38">AF11-AF12-AF13-AF14</f>
-        <v>2181.097260973811</v>
+        <v>2144.3790753739568</v>
       </c>
       <c r="AG15" s="7">
         <f t="shared" ref="AG15" si="39">AG11-AG12-AG13-AG14</f>
-        <v>2217.3193227147822</v>
+        <v>2180.20707648814</v>
       </c>
       <c r="AH15" s="7">
         <f t="shared" ref="AH15" si="40">AH11-AH12-AH13-AH14</f>
-        <v>2253.9251974045887</v>
+        <v>2216.4174976201452</v>
       </c>
       <c r="AI15" s="7">
         <f t="shared" ref="AI15" si="41">AI11-AI12-AI13-AI14</f>
-        <v>2290.9230824384886</v>
+        <v>2253.0185804163084</v>
       </c>
       <c r="AJ15" s="7">
         <f t="shared" ref="AJ15" si="42">AJ11-AJ12-AJ13-AJ14</f>
-        <v>2328.3213452553787</v>
+        <v>2290.018738913438</v>
       </c>
       <c r="AK15" s="10">
         <f>AJ15+(AJ15*$AN$20)</f>
-        <v>2305.0381318028249</v>
+        <v>2267.1185515243037</v>
       </c>
       <c r="AL15" s="10">
         <f t="shared" ref="AL15:CW15" si="43">AK15+(AK15*$AN$20)</f>
-        <v>2281.9877504847968</v>
+        <v>2244.4473660090607</v>
       </c>
       <c r="AM15" s="10">
         <f t="shared" si="43"/>
-        <v>2259.1678729799487</v>
+        <v>2222.0028923489699</v>
       </c>
       <c r="AN15" s="10">
         <f t="shared" si="43"/>
-        <v>2236.576194250149</v>
+        <v>2199.7828634254802</v>
       </c>
       <c r="AO15" s="10">
         <f t="shared" si="43"/>
-        <v>2214.2104323076474</v>
+        <v>2177.7850347912254</v>
       </c>
       <c r="AP15" s="10">
         <f t="shared" si="43"/>
-        <v>2192.0683279845707</v>
+        <v>2156.0071844433132</v>
       </c>
       <c r="AQ15" s="10">
         <f t="shared" si="43"/>
-        <v>2170.1476447047248</v>
+        <v>2134.4471125988803</v>
       </c>
       <c r="AR15" s="10">
         <f t="shared" si="43"/>
-        <v>2148.4461682576775</v>
+        <v>2113.1026414728913</v>
       </c>
       <c r="AS15" s="10">
         <f t="shared" si="43"/>
-        <v>2126.9617065751008</v>
+        <v>2091.9716150581626</v>
       </c>
       <c r="AT15" s="10">
         <f t="shared" si="43"/>
-        <v>2105.6920895093499</v>
+        <v>2071.0518989075808</v>
       </c>
       <c r="AU15" s="10">
         <f t="shared" si="43"/>
-        <v>2084.6351686142566</v>
+        <v>2050.341379918505</v>
       </c>
       <c r="AV15" s="10">
         <f t="shared" si="43"/>
-        <v>2063.7888169281141</v>
+        <v>2029.8379661193201</v>
       </c>
       <c r="AW15" s="10">
         <f t="shared" si="43"/>
-        <v>2043.1509287588331</v>
+        <v>2009.5395864581269</v>
       </c>
       <c r="AX15" s="10">
         <f t="shared" si="43"/>
-        <v>2022.7194194712447</v>
+        <v>1989.4441905935457</v>
       </c>
       <c r="AY15" s="10">
         <f t="shared" si="43"/>
-        <v>2002.4922252765323</v>
+        <v>1969.5497486876102</v>
       </c>
       <c r="AZ15" s="10">
         <f t="shared" si="43"/>
-        <v>1982.467303023767</v>
+        <v>1949.8542512007341</v>
       </c>
       <c r="BA15" s="10">
         <f t="shared" si="43"/>
-        <v>1962.6426299935295</v>
+        <v>1930.3557086887267</v>
       </c>
       <c r="BB15" s="10">
         <f t="shared" si="43"/>
-        <v>1943.0162036935942</v>
+        <v>1911.0521516018396</v>
       </c>
       <c r="BC15" s="10">
         <f t="shared" si="43"/>
-        <v>1923.5860416566582</v>
+        <v>1891.9416300858211</v>
       </c>
       <c r="BD15" s="10">
         <f t="shared" si="43"/>
-        <v>1904.3501812400916</v>
+        <v>1873.0222137849628</v>
       </c>
       <c r="BE15" s="10">
         <f t="shared" si="43"/>
-        <v>1885.3066794276906</v>
+        <v>1854.2919916471133</v>
       </c>
       <c r="BF15" s="10">
         <f t="shared" si="43"/>
-        <v>1866.4536126334137</v>
+        <v>1835.7490717306421</v>
       </c>
       <c r="BG15" s="10">
         <f t="shared" si="43"/>
-        <v>1847.7890765070797</v>
+        <v>1817.3915810133356</v>
       </c>
       <c r="BH15" s="10">
         <f t="shared" si="43"/>
-        <v>1829.311185742009</v>
+        <v>1799.2176652032022</v>
       </c>
       <c r="BI15" s="10">
         <f t="shared" si="43"/>
-        <v>1811.0180738845888</v>
+        <v>1781.2254885511702</v>
       </c>
       <c r="BJ15" s="10">
         <f t="shared" si="43"/>
-        <v>1792.9078931457429</v>
+        <v>1763.4132336656585</v>
       </c>
       <c r="BK15" s="10">
         <f t="shared" si="43"/>
-        <v>1774.9788142142854</v>
+        <v>1745.7791013290018</v>
       </c>
       <c r="BL15" s="10">
         <f t="shared" si="43"/>
-        <v>1757.2290260721425</v>
+        <v>1728.3213103157118</v>
       </c>
       <c r="BM15" s="10">
         <f t="shared" si="43"/>
-        <v>1739.656735811421</v>
+        <v>1711.0380972125547</v>
       </c>
       <c r="BN15" s="10">
         <f t="shared" si="43"/>
-        <v>1722.2601684533067</v>
+        <v>1693.9277162404292</v>
       </c>
       <c r="BO15" s="10">
         <f t="shared" si="43"/>
-        <v>1705.0375667687736</v>
+        <v>1676.9884390780248</v>
       </c>
       <c r="BP15" s="10">
         <f t="shared" si="43"/>
-        <v>1687.9871911010857</v>
+        <v>1660.2185546872447</v>
       </c>
       <c r="BQ15" s="10">
         <f t="shared" si="43"/>
-        <v>1671.1073191900748</v>
+        <v>1643.6163691403722</v>
       </c>
       <c r="BR15" s="10">
         <f t="shared" si="43"/>
-        <v>1654.396245998174</v>
+        <v>1627.1802054489685</v>
       </c>
       <c r="BS15" s="10">
         <f t="shared" si="43"/>
-        <v>1637.8522835381923</v>
+        <v>1610.9084033944789</v>
       </c>
       <c r="BT15" s="10">
         <f t="shared" si="43"/>
-        <v>1621.4737607028103</v>
+        <v>1594.7993193605341</v>
       </c>
       <c r="BU15" s="10">
         <f t="shared" si="43"/>
-        <v>1605.2590230957821</v>
+        <v>1578.8513261669289</v>
       </c>
       <c r="BV15" s="10">
         <f t="shared" si="43"/>
-        <v>1589.2064328648244</v>
+        <v>1563.0628129052595</v>
       </c>
       <c r="BW15" s="10">
         <f t="shared" si="43"/>
-        <v>1573.3143685361761</v>
+        <v>1547.4321847762069</v>
       </c>
       <c r="BX15" s="10">
         <f t="shared" si="43"/>
-        <v>1557.5812248508144</v>
+        <v>1531.9578629284449</v>
       </c>
       <c r="BY15" s="10">
         <f t="shared" si="43"/>
-        <v>1542.0054126023063</v>
+        <v>1516.6382842991604</v>
       </c>
       <c r="BZ15" s="10">
         <f t="shared" si="43"/>
-        <v>1526.5853584762831</v>
+        <v>1501.4719014561688</v>
       </c>
       <c r="CA15" s="10">
         <f t="shared" si="43"/>
-        <v>1511.3195048915202</v>
+        <v>1486.4571824416071</v>
       </c>
       <c r="CB15" s="10">
         <f t="shared" si="43"/>
-        <v>1496.2063098426049</v>
+        <v>1471.592610617191</v>
       </c>
       <c r="CC15" s="10">
         <f t="shared" si="43"/>
-        <v>1481.2442467441788</v>
+        <v>1456.876684511019</v>
       </c>
       <c r="CD15" s="10">
         <f t="shared" si="43"/>
-        <v>1466.431804276737</v>
+        <v>1442.3079176659089</v>
       </c>
       <c r="CE15" s="10">
         <f t="shared" si="43"/>
-        <v>1451.7674862339697</v>
+        <v>1427.8848384892499</v>
       </c>
       <c r="CF15" s="10">
         <f t="shared" si="43"/>
-        <v>1437.2498113716301</v>
+        <v>1413.6059901043575</v>
       </c>
       <c r="CG15" s="10">
         <f t="shared" si="43"/>
-        <v>1422.8773132579138</v>
+        <v>1399.4699302033139</v>
       </c>
       <c r="CH15" s="10">
         <f t="shared" si="43"/>
-        <v>1408.6485401253346</v>
+        <v>1385.4752309012808</v>
       </c>
       <c r="CI15" s="10">
         <f t="shared" si="43"/>
-        <v>1394.5620547240812</v>
+        <v>1371.620478592268</v>
       </c>
       <c r="CJ15" s="10">
         <f t="shared" si="43"/>
-        <v>1380.6164341768404</v>
+        <v>1357.9042738063454</v>
       </c>
       <c r="CK15" s="10">
         <f t="shared" si="43"/>
-        <v>1366.8102698350719</v>
+        <v>1344.3252310682819</v>
       </c>
       <c r="CL15" s="10">
         <f t="shared" si="43"/>
-        <v>1353.1421671367211</v>
+        <v>1330.8819787575992</v>
       </c>
       <c r="CM15" s="10">
         <f t="shared" si="43"/>
-        <v>1339.6107454653538</v>
+        <v>1317.5731589700233</v>
       </c>
       <c r="CN15" s="10">
         <f t="shared" si="43"/>
-        <v>1326.2146380107004</v>
+        <v>1304.3974273803231</v>
       </c>
       <c r="CO15" s="10">
         <f t="shared" si="43"/>
-        <v>1312.9524916305934</v>
+        <v>1291.3534531065197</v>
       </c>
       <c r="CP15" s="10">
         <f t="shared" si="43"/>
-        <v>1299.8229667142875</v>
+        <v>1278.4399185754546</v>
       </c>
       <c r="CQ15" s="10">
         <f t="shared" si="43"/>
-        <v>1286.8247370471447</v>
+        <v>1265.6555193897</v>
       </c>
       <c r="CR15" s="10">
         <f t="shared" si="43"/>
-        <v>1273.9564896766733</v>
+        <v>1252.998964195803</v>
       </c>
       <c r="CS15" s="10">
         <f t="shared" si="43"/>
-        <v>1261.2169247799065</v>
+        <v>1240.4689745538449</v>
       </c>
       <c r="CT15" s="10">
         <f t="shared" si="43"/>
-        <v>1248.6047555321074</v>
+        <v>1228.0642848083064</v>
       </c>
       <c r="CU15" s="10">
         <f t="shared" si="43"/>
-        <v>1236.1187079767865</v>
+        <v>1215.7836419602233</v>
       </c>
       <c r="CV15" s="10">
         <f t="shared" si="43"/>
-        <v>1223.7575208970186</v>
+        <v>1203.6258055406211</v>
       </c>
       <c r="CW15" s="10">
         <f t="shared" si="43"/>
-        <v>1211.5199456880484</v>
+        <v>1191.5895474852148</v>
       </c>
       <c r="CX15" s="10">
         <f t="shared" ref="CX15:EN15" si="44">CW15+(CW15*$AN$20)</f>
-        <v>1199.404746231168</v>
+        <v>1179.6736520103627</v>
       </c>
       <c r="CY15" s="10">
         <f t="shared" si="44"/>
-        <v>1187.4106987688563</v>
+        <v>1167.8769154902591</v>
       </c>
       <c r="CZ15" s="10">
         <f t="shared" si="44"/>
-        <v>1175.5365917811678</v>
+        <v>1156.1981463353566</v>
       </c>
       <c r="DA15" s="10">
         <f t="shared" si="44"/>
-        <v>1163.781225863356</v>
+        <v>1144.6361648720031</v>
       </c>
       <c r="DB15" s="10">
         <f t="shared" si="44"/>
-        <v>1152.1434136047224</v>
+        <v>1133.189803223283</v>
       </c>
       <c r="DC15" s="10">
         <f t="shared" si="44"/>
-        <v>1140.6219794686751</v>
+        <v>1121.8579051910501</v>
       </c>
       <c r="DD15" s="10">
         <f t="shared" si="44"/>
-        <v>1129.2157596739885</v>
+        <v>1110.6393261391397</v>
       </c>
       <c r="DE15" s="10">
         <f t="shared" si="44"/>
-        <v>1117.9236020772487</v>
+        <v>1099.5329328777484</v>
       </c>
       <c r="DF15" s="10">
         <f t="shared" si="44"/>
-        <v>1106.7443660564761</v>
+        <v>1088.537603548971</v>
       </c>
       <c r="DG15" s="10">
         <f t="shared" si="44"/>
-        <v>1095.6769223959113</v>
+        <v>1077.6522275134812</v>
       </c>
       <c r="DH15" s="10">
         <f t="shared" si="44"/>
-        <v>1084.7201531719522</v>
+        <v>1066.8757052383464</v>
       </c>
       <c r="DI15" s="10">
         <f t="shared" si="44"/>
-        <v>1073.8729516402327</v>
+        <v>1056.206948185963</v>
       </c>
       <c r="DJ15" s="10">
         <f t="shared" si="44"/>
-        <v>1063.1342221238303</v>
+        <v>1045.6448787041033</v>
       </c>
       <c r="DK15" s="10">
         <f t="shared" si="44"/>
-        <v>1052.502879902592</v>
+        <v>1035.1884299170624</v>
       </c>
       <c r="DL15" s="10">
         <f t="shared" si="44"/>
-        <v>1041.9778511035661</v>
+        <v>1024.8365456178917</v>
       </c>
       <c r="DM15" s="10">
         <f t="shared" si="44"/>
-        <v>1031.5580725925304</v>
+        <v>1014.5881801617128</v>
       </c>
       <c r="DN15" s="10">
         <f t="shared" si="44"/>
-        <v>1021.2424918666051</v>
+        <v>1004.4422983600956</v>
       </c>
       <c r="DO15" s="10">
         <f t="shared" si="44"/>
-        <v>1011.030066947939</v>
+        <v>994.39787537649465</v>
       </c>
       <c r="DP15" s="10">
         <f t="shared" si="44"/>
-        <v>1000.9197662784595</v>
+        <v>984.45389662272976</v>
       </c>
       <c r="DQ15" s="10">
         <f t="shared" si="44"/>
-        <v>990.91056861567495</v>
+        <v>974.60935765650243</v>
       </c>
       <c r="DR15" s="10">
         <f t="shared" si="44"/>
-        <v>981.0014629295182</v>
+        <v>964.86326407993738</v>
       </c>
       <c r="DS15" s="10">
         <f t="shared" si="44"/>
-        <v>971.19144830022299</v>
+        <v>955.21463143913797</v>
       </c>
       <c r="DT15" s="10">
         <f t="shared" si="44"/>
-        <v>961.47953381722073</v>
+        <v>945.66248512474658</v>
       </c>
       <c r="DU15" s="10">
         <f t="shared" si="44"/>
-        <v>951.86473847904847</v>
+        <v>936.20586027349907</v>
       </c>
       <c r="DV15" s="10">
         <f t="shared" si="44"/>
-        <v>942.34609109425799</v>
+        <v>926.84380167076404</v>
       </c>
       <c r="DW15" s="10">
         <f t="shared" si="44"/>
-        <v>932.92263018331539</v>
+        <v>917.57536365405645</v>
       </c>
       <c r="DX15" s="10">
         <f t="shared" si="44"/>
-        <v>923.59340388148223</v>
+        <v>908.3996100175159</v>
       </c>
       <c r="DY15" s="10">
         <f t="shared" si="44"/>
-        <v>914.35746984266746</v>
+        <v>899.31561391734078</v>
       </c>
       <c r="DZ15" s="10">
         <f t="shared" si="44"/>
-        <v>905.21389514424084</v>
+        <v>890.3224577781674</v>
       </c>
       <c r="EA15" s="10">
         <f t="shared" si="44"/>
-        <v>896.16175619279841</v>
+        <v>881.41923320038575</v>
       </c>
       <c r="EB15" s="10">
         <f t="shared" si="44"/>
-        <v>887.20013863087047</v>
+        <v>872.60504086838193</v>
       </c>
       <c r="EC15" s="10">
         <f t="shared" si="44"/>
-        <v>878.32813724456173</v>
+        <v>863.87899045969812</v>
       </c>
       <c r="ED15" s="10">
         <f t="shared" si="44"/>
-        <v>869.54485587211616</v>
+        <v>855.24020055510118</v>
       </c>
       <c r="EE15" s="10">
         <f t="shared" si="44"/>
-        <v>860.84940731339498</v>
+        <v>846.68779854955017</v>
       </c>
       <c r="EF15" s="10">
         <f t="shared" si="44"/>
-        <v>852.24091324026108</v>
+        <v>838.22092056405461</v>
       </c>
       <c r="EG15" s="10">
         <f t="shared" si="44"/>
-        <v>843.71850410785851</v>
+        <v>829.83871135841412</v>
       </c>
       <c r="EH15" s="10">
         <f t="shared" si="44"/>
-        <v>835.28131906677993</v>
+        <v>821.54032424483</v>
       </c>
       <c r="EI15" s="10">
         <f t="shared" si="44"/>
-        <v>826.92850587611213</v>
+        <v>813.32492100238176</v>
       </c>
       <c r="EJ15" s="10">
         <f t="shared" si="44"/>
-        <v>818.65922081735096</v>
+        <v>805.19167179235797</v>
       </c>
       <c r="EK15" s="10">
         <f t="shared" si="44"/>
-        <v>810.47262860917749</v>
+        <v>797.13975507443433</v>
       </c>
       <c r="EL15" s="10">
         <f t="shared" si="44"/>
-        <v>802.36790232308567</v>
+        <v>789.16835752369002</v>
       </c>
       <c r="EM15" s="10">
         <f t="shared" si="44"/>
-        <v>794.34422329985478</v>
+        <v>781.27667394845309</v>
       </c>
       <c r="EN15" s="10">
         <f t="shared" si="44"/>
-        <v>786.40078106685621</v>
+        <v>773.46390720896852</v>
       </c>
     </row>
     <row r="16" spans="1:144" x14ac:dyDescent="0.3">
@@ -3173,20 +3173,20 @@
         <v>247.6</v>
       </c>
       <c r="O16" s="1">
-        <f t="shared" ref="O16:R16" si="45">247.6</f>
-        <v>247.6</v>
+        <f>246.7</f>
+        <v>246.7</v>
       </c>
       <c r="P16" s="1">
-        <f t="shared" si="45"/>
-        <v>247.6</v>
+        <f>246.7</f>
+        <v>246.7</v>
       </c>
       <c r="Q16" s="1">
-        <f t="shared" si="45"/>
-        <v>247.6</v>
+        <f>246.7</f>
+        <v>246.7</v>
       </c>
       <c r="R16" s="1">
-        <f t="shared" si="45"/>
-        <v>247.6</v>
+        <f>246.7</f>
+        <v>246.7</v>
       </c>
       <c r="T16" s="1">
         <v>255.2</v>
@@ -3204,52 +3204,52 @@
         <v>255.2</v>
       </c>
       <c r="Y16" s="1">
-        <f t="shared" ref="Y16:AJ16" si="46">247.6</f>
+        <f t="shared" ref="Y16" si="45">247.6</f>
         <v>247.6</v>
       </c>
       <c r="Z16" s="1">
-        <f t="shared" si="46"/>
-        <v>247.6</v>
+        <f t="shared" ref="Z16:AJ16" si="46">246.7</f>
+        <v>246.7</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" si="46"/>
-        <v>247.6</v>
+        <v>246.7</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" si="46"/>
-        <v>247.6</v>
+        <v>246.7</v>
       </c>
       <c r="AC16" s="1">
         <f t="shared" si="46"/>
-        <v>247.6</v>
+        <v>246.7</v>
       </c>
       <c r="AD16" s="1">
         <f t="shared" si="46"/>
-        <v>247.6</v>
+        <v>246.7</v>
       </c>
       <c r="AE16" s="1">
         <f t="shared" si="46"/>
-        <v>247.6</v>
+        <v>246.7</v>
       </c>
       <c r="AF16" s="1">
         <f t="shared" si="46"/>
-        <v>247.6</v>
+        <v>246.7</v>
       </c>
       <c r="AG16" s="1">
         <f t="shared" si="46"/>
-        <v>247.6</v>
+        <v>246.7</v>
       </c>
       <c r="AH16" s="1">
         <f t="shared" si="46"/>
-        <v>247.6</v>
+        <v>246.7</v>
       </c>
       <c r="AI16" s="1">
         <f t="shared" si="46"/>
-        <v>247.6</v>
+        <v>246.7</v>
       </c>
       <c r="AJ16" s="1">
         <f t="shared" si="46"/>
-        <v>247.6</v>
+        <v>246.7</v>
       </c>
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.3">
@@ -3306,19 +3306,19 @@
       </c>
       <c r="O17" s="5">
         <f t="shared" ref="O17:R17" si="49">O15/O16</f>
-        <v>1.2624188287560578</v>
+        <v>1.2395622213214426</v>
       </c>
       <c r="P17" s="5">
         <f t="shared" si="49"/>
-        <v>1.462519496768983</v>
+        <v>1.4313378427239574</v>
       </c>
       <c r="Q17" s="5">
         <f t="shared" si="49"/>
-        <v>1.6559525751211635</v>
+        <v>1.6232492063234698</v>
       </c>
       <c r="R17" s="5">
         <f t="shared" si="49"/>
-        <v>1.631191587641357</v>
+        <v>1.5979788638021881</v>
       </c>
       <c r="T17" s="5">
         <f t="shared" ref="T17:Y17" si="50">T15/T16</f>
@@ -3346,47 +3346,47 @@
       </c>
       <c r="Z17" s="5">
         <f t="shared" ref="Z17" si="51">Z15/Z16</f>
-        <v>6.4288996934571934</v>
+        <v>6.4174623862991496</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" ref="AA17" si="52">AA15/AA16</f>
-        <v>7.4599125814398217</v>
+        <v>7.360645859308879</v>
       </c>
       <c r="AB17" s="5">
         <f t="shared" ref="AB17" si="53">AB15/AB16</f>
-        <v>8.0489725035389466</v>
+        <v>7.9401157635654149</v>
       </c>
       <c r="AC17" s="5">
         <f t="shared" ref="AC17" si="54">AC15/AC16</f>
-        <v>8.2827994226710633</v>
+        <v>8.1711111042132103</v>
       </c>
       <c r="AD17" s="5">
         <f t="shared" ref="AD17" si="55">AD15/AD16</f>
-        <v>8.5208909929058034</v>
+        <v>8.4063161774975441</v>
       </c>
       <c r="AE17" s="5">
         <f t="shared" ref="AE17" si="56">AE15/AE16</f>
-        <v>8.6641800496264612</v>
+        <v>8.5485424418507918</v>
       </c>
       <c r="AF17" s="5">
         <f t="shared" ref="AF17" si="57">AF15/AF16</f>
-        <v>8.8089550120105446</v>
+        <v>8.6922540550221186</v>
       </c>
       <c r="AG17" s="5">
         <f t="shared" ref="AG17" si="58">AG15/AG16</f>
-        <v>8.9552476684765026</v>
+        <v>8.8374830826434536</v>
       </c>
       <c r="AH17" s="5">
         <f t="shared" ref="AH17" si="59">AH15/AH16</f>
-        <v>9.103090458015302</v>
+        <v>8.9842622522097493</v>
       </c>
       <c r="AI17" s="5">
         <f t="shared" ref="AI17" si="60">AI15/AI16</f>
-        <v>9.2525164880391308</v>
+        <v>9.1326249712862122</v>
       </c>
       <c r="AJ17" s="5">
         <f t="shared" ref="AJ17" si="61">AJ15/AJ16</f>
-        <v>9.4035595527277014</v>
+        <v>9.2826053462239084</v>
       </c>
     </row>
     <row r="19" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3428,19 +3428,19 @@
       </c>
       <c r="O19" s="8">
         <f t="shared" ref="O19" si="63">O3/K3-1</f>
-        <v>3.0000000000000027E-2</v>
+        <v>-3.346830840426418E-3</v>
       </c>
       <c r="P19" s="8">
         <f t="shared" ref="P19" si="64">P3/L3-1</f>
-        <v>3.0000000000000027E-2</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="Q19" s="8">
         <f t="shared" ref="Q19" si="65">Q3/M3-1</f>
-        <v>3.0000000000000027E-2</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="R19" s="8">
         <f t="shared" ref="R19" si="66">R3/N3-1</f>
-        <v>3.0000000000000027E-2</v>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="U19" s="8">
         <f>U3/T3-1</f>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="Z19" s="8">
         <f t="shared" si="67"/>
-        <v>3.0000000000000027E-2</v>
+        <v>6.8036809815950061E-3</v>
       </c>
       <c r="AA19" s="8">
         <f t="shared" si="67"/>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="O20" s="9">
         <f t="shared" ref="O20:R20" si="70">O5/O3</f>
-        <v>0.63</v>
+        <v>0.61809211890054305</v>
       </c>
       <c r="P20" s="9">
         <f t="shared" si="70"/>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="O21" s="9">
         <f t="shared" ref="O21:R21" si="74">O6/O3</f>
-        <v>0.43000000000000005</v>
+        <v>0.42452634633721653</v>
       </c>
       <c r="P21" s="9">
         <f t="shared" si="74"/>
@@ -3744,15 +3744,15 @@
       </c>
       <c r="Z21" s="9">
         <f t="shared" si="75"/>
-        <v>0.41492776568375217</v>
+        <v>0.41358229257147933</v>
       </c>
       <c r="AA21" s="9">
         <f t="shared" si="75"/>
-        <v>0.40000000000000008</v>
+        <v>0.4</v>
       </c>
       <c r="AB21" s="9">
         <f t="shared" si="75"/>
-        <v>0.39</v>
+        <v>0.38999999999999996</v>
       </c>
       <c r="AC21" s="9">
         <f t="shared" si="75"/>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="AF21" s="9">
         <f t="shared" si="75"/>
-        <v>0.39</v>
+        <v>0.38999999999999996</v>
       </c>
       <c r="AG21" s="9">
         <f t="shared" si="75"/>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AH21" s="9">
         <f t="shared" si="75"/>
-        <v>0.39</v>
+        <v>0.39000000000000007</v>
       </c>
       <c r="AI21" s="9">
         <f t="shared" si="75"/>
@@ -3847,11 +3847,11 @@
       </c>
       <c r="O22" s="9">
         <f t="shared" ref="O22:R22" si="78">O7/O3</f>
-        <v>0.19999999999999996</v>
+        <v>0.19356577256332652</v>
       </c>
       <c r="P22" s="9">
         <f t="shared" si="78"/>
-        <v>0.21000000000000005</v>
+        <v>0.21000000000000008</v>
       </c>
       <c r="Q22" s="9">
         <f t="shared" si="78"/>
@@ -3859,7 +3859,7 @@
       </c>
       <c r="R22" s="9">
         <f t="shared" si="78"/>
-        <v>0.23</v>
+        <v>0.22999999999999993</v>
       </c>
       <c r="T22" s="9">
         <f t="shared" ref="T22:AJ22" si="79">T7/T3</f>
@@ -3887,15 +3887,15 @@
       </c>
       <c r="Z22" s="9">
         <f t="shared" si="79"/>
-        <v>0.22507223431624784</v>
+        <v>0.22641770742852069</v>
       </c>
       <c r="AA22" s="9">
         <f t="shared" si="79"/>
-        <v>0.24999999999999994</v>
+        <v>0.25</v>
       </c>
       <c r="AB22" s="9">
         <f t="shared" si="79"/>
-        <v>0.26</v>
+        <v>0.26000000000000006</v>
       </c>
       <c r="AC22" s="9">
         <f t="shared" si="79"/>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="AE22" s="9">
         <f t="shared" si="79"/>
-        <v>0.26</v>
+        <v>0.26000000000000006</v>
       </c>
       <c r="AF22" s="9">
         <f t="shared" si="79"/>
@@ -3923,18 +3923,18 @@
       </c>
       <c r="AI22" s="9">
         <f t="shared" si="79"/>
-        <v>0.26000000000000006</v>
+        <v>0.25999999999999995</v>
       </c>
       <c r="AJ22" s="9">
         <f t="shared" si="79"/>
-        <v>0.25999999999999995</v>
+        <v>0.26</v>
       </c>
       <c r="AM22" t="s">
         <v>42</v>
       </c>
       <c r="AN22" s="1">
         <f>NPV(AN21,Z15:EN15)</f>
-        <v>25575.941021104089</v>
+        <v>25166.162395609612</v>
       </c>
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.3">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="O23" s="9">
         <f t="shared" ref="O23:R23" si="82">O12/O11</f>
-        <v>0.16</v>
+        <v>0.1661947904869763</v>
       </c>
       <c r="P23" s="9">
         <f t="shared" si="82"/>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="Z23" s="9">
         <f t="shared" si="83"/>
-        <v>0.15124438908296742</v>
+        <v>0.15001398204512492</v>
       </c>
       <c r="AA23" s="9">
         <f t="shared" si="83"/>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="AN23" s="1">
         <f>Main!D8</f>
-        <v>-14205.4</v>
+        <v>-14026.8</v>
       </c>
     </row>
     <row r="24" spans="1:40" x14ac:dyDescent="0.3">
@@ -4135,19 +4135,19 @@
       </c>
       <c r="O24" s="9">
         <f t="shared" ref="O24:R24" si="85">O14/O3</f>
-        <v>6.7575872330217406E-3</v>
+        <v>2.9020355706645662E-3</v>
       </c>
       <c r="P24" s="9">
         <f t="shared" si="85"/>
-        <v>7.3758287651973066E-3</v>
+        <v>7.3347560674784434E-3</v>
       </c>
       <c r="Q24" s="9">
         <f t="shared" si="85"/>
-        <v>8.2460663490130041E-3</v>
+        <v>8.2133151876073208E-3</v>
       </c>
       <c r="R24" s="9">
         <f t="shared" si="85"/>
-        <v>8.4011235256837308E-3</v>
+        <v>8.362531912330929E-3</v>
       </c>
       <c r="T24" s="9">
         <f t="shared" ref="T24:AJ24" si="86">T14/T3</f>
@@ -4175,59 +4175,59 @@
       </c>
       <c r="Z24" s="9">
         <f t="shared" si="86"/>
-        <v>7.7069952388180421E-3</v>
+        <v>6.7674178491517935E-3</v>
       </c>
       <c r="AA24" s="9">
         <f t="shared" si="86"/>
-        <v>7.5199322475845935E-3</v>
+        <v>6.6031601343665546E-3</v>
       </c>
       <c r="AB24" s="9">
         <f t="shared" si="86"/>
-        <v>7.4093450086495241E-3</v>
+        <v>6.5060548382729283E-3</v>
       </c>
       <c r="AC24" s="9">
         <f t="shared" si="86"/>
-        <v>7.3003840526399723E-3</v>
+        <v>6.410377561239502E-3</v>
       </c>
       <c r="AD24" s="9">
         <f t="shared" si="86"/>
-        <v>7.1930254636305606E-3</v>
+        <v>6.3161073029859788E-3</v>
       </c>
       <c r="AE24" s="9">
         <f t="shared" si="86"/>
-        <v>7.1574164266818927E-3</v>
+        <v>6.2848394450504049E-3</v>
       </c>
       <c r="AF24" s="9">
         <f t="shared" si="86"/>
-        <v>7.1219836720943577E-3</v>
+        <v>6.2537263784907485E-3</v>
       </c>
       <c r="AG24" s="9">
         <f t="shared" si="86"/>
-        <v>7.0867263271829992E-3</v>
+        <v>6.2227673370130717E-3</v>
       </c>
       <c r="AH24" s="9">
         <f t="shared" si="86"/>
-        <v>7.0516435235830821E-3</v>
+        <v>6.1919615581169669E-3</v>
       </c>
       <c r="AI24" s="9">
         <f t="shared" si="86"/>
-        <v>7.0167343972287102E-3</v>
+        <v>6.1613082830767833E-3</v>
       </c>
       <c r="AJ24" s="9">
         <f t="shared" si="86"/>
-        <v>6.9819980883315379E-3</v>
+        <v>6.1308067569229366E-3</v>
       </c>
       <c r="AM24" t="s">
         <v>44</v>
       </c>
       <c r="AN24" s="1">
         <f>AN22+AN23</f>
-        <v>11370.541021104089</v>
+        <v>11139.362395609613</v>
       </c>
     </row>
     <row r="25" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C25" s="9">
         <f>C15/C3</f>
@@ -4279,19 +4279,19 @@
       </c>
       <c r="O25" s="9">
         <f t="shared" ref="O25:R25" si="88">O15/O3</f>
-        <v>0.12539078532384787</v>
+        <v>0.12677749678703198</v>
       </c>
       <c r="P25" s="9">
         <f t="shared" si="88"/>
-        <v>0.13686260042088338</v>
+        <v>0.13610047369654446</v>
       </c>
       <c r="Q25" s="9">
         <f t="shared" si="88"/>
-        <v>0.153010342253908</v>
+        <v>0.15240262625893586</v>
       </c>
       <c r="R25" s="9">
         <f t="shared" si="88"/>
-        <v>0.15588751430990919</v>
+        <v>0.15517142548436277</v>
       </c>
       <c r="T25" s="9">
         <f t="shared" ref="T25:AJ25" si="89">T15/T3</f>
@@ -4319,54 +4319,54 @@
       </c>
       <c r="Z25" s="9">
         <f t="shared" si="89"/>
-        <v>0.15292228245644718</v>
+        <v>0.15559957010279754</v>
       </c>
       <c r="AA25" s="9">
         <f t="shared" si="89"/>
-        <v>0.17227832288184491</v>
+        <v>0.17327015317476976</v>
       </c>
       <c r="AB25" s="9">
         <f t="shared" si="89"/>
-        <v>0.18223725665887794</v>
+        <v>0.18324599803149871</v>
       </c>
       <c r="AC25" s="9">
         <f t="shared" si="89"/>
-        <v>0.18385426038695016</v>
+        <v>0.18487943633242393</v>
       </c>
       <c r="AD25" s="9">
         <f t="shared" si="89"/>
-        <v>0.18543059471861589</v>
+        <v>0.18647174780910006</v>
       </c>
       <c r="AE25" s="9">
         <f t="shared" si="89"/>
-        <v>0.18668201362874995</v>
+        <v>0.18774916722257701</v>
       </c>
       <c r="AF25" s="9">
         <f t="shared" si="89"/>
-        <v>0.18792217322812202</v>
+        <v>0.18901531074425762</v>
       </c>
       <c r="AG25" s="9">
         <f t="shared" si="89"/>
-        <v>0.18915153137697238</v>
+        <v>0.19027064701095384</v>
       </c>
       <c r="AH25" s="9">
         <f t="shared" si="89"/>
-        <v>0.19037054138977866</v>
+        <v>0.19151564008926739</v>
       </c>
       <c r="AI25" s="9">
         <f t="shared" si="89"/>
-        <v>0.19157965221253359</v>
+        <v>0.19275074965703357</v>
       </c>
       <c r="AJ25" s="9">
         <f t="shared" si="89"/>
-        <v>0.19277930859822306</v>
+        <v>0.19397643118295341</v>
       </c>
       <c r="AM25" t="s">
         <v>45</v>
       </c>
       <c r="AN25" s="11">
         <f>AN24/AJ16</f>
-        <v>45.923025125622331</v>
+        <v>45.153475458490526</v>
       </c>
     </row>
     <row r="26" spans="1:40" x14ac:dyDescent="0.3">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="AN26" s="11">
         <f>Main!D3</f>
-        <v>92.41</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AN27" s="8">
         <f>AN25/AN26-1</f>
-        <v>-0.50305134589738842</v>
+        <v>-0.39795366055345971</v>
       </c>
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.3">
@@ -4419,12 +4419,12 @@
         <v>48</v>
       </c>
       <c r="AN28" s="4" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J29" s="1">
         <v>1120.0999999999999</v>
@@ -4438,7 +4438,7 @@
     </row>
     <row r="30" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J30" s="1">
         <v>4097.3999999999996</v>
@@ -4452,7 +4452,7 @@
     </row>
     <row r="31" spans="1:40" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J31" s="1">
         <v>767.4</v>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="32" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B32" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J32" s="7">
         <f>SUM(J28:J31)</f>
@@ -4483,7 +4483,7 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J33" s="1">
         <v>26743.5</v>
@@ -4497,7 +4497,7 @@
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J34" s="1">
         <v>10168</v>
@@ -4511,7 +4511,7 @@
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J35" s="1">
         <v>2190</v>
@@ -4525,7 +4525,7 @@
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J36" s="1">
         <v>111.7</v>
@@ -4539,7 +4539,7 @@
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J37" s="1">
         <v>713.1</v>
@@ -4553,7 +4553,7 @@
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J38" s="1">
         <v>2570</v>
@@ -4567,7 +4567,7 @@
     </row>
     <row r="39" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B39" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J39" s="7">
         <f>SUM(J33:J38)</f>
@@ -4584,7 +4584,7 @@
     </row>
     <row r="40" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J40" s="12">
         <f>J32+J39</f>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J41" s="1">
         <v>981.2</v>
@@ -4629,7 +4629,7 @@
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J43" s="1">
         <v>2825</v>
@@ -4643,7 +4643,7 @@
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J44" s="1">
         <v>3698.9</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="45" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B45" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J45" s="7">
         <f>SUM(J41:J44)</f>
@@ -4688,7 +4688,7 @@
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J47" s="1">
         <v>2242.1</v>
@@ -4702,7 +4702,7 @@
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J48" s="1">
         <v>722.5</v>
@@ -4714,9 +4714,9 @@
         <v>639.20000000000005</v>
       </c>
     </row>
-    <row r="49" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B49" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J49" s="7">
         <f>SUM(J46:J48)</f>
@@ -4731,9 +4731,9 @@
         <v>18261.7</v>
       </c>
     </row>
-    <row r="50" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B50" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J50" s="7">
         <f>508+23279.6</f>
@@ -4748,9 +4748,9 @@
         <v>23161.100000000002</v>
       </c>
     </row>
-    <row r="51" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B51" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J51" s="12">
         <f>J45+J49+J50</f>
@@ -4765,9 +4765,9 @@
         <v>50752.100000000006</v>
       </c>
     </row>
-    <row r="53" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B53" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G53" s="7">
         <f>G15+G14</f>
@@ -4785,10 +4785,14 @@
         <f>L15+L14</f>
         <v>389.2000000000001</v>
       </c>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O53" s="7">
+        <f>O15+O14</f>
+        <v>312.79999999999984</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G54" s="1">
         <v>106</v>
@@ -4804,10 +4808,13 @@
         <f>241.9-K54</f>
         <v>124</v>
       </c>
-    </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O54" s="1">
+        <v>122.8</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G55" s="1">
         <f>301.3+29.3</f>
@@ -4825,10 +4832,14 @@
         <f>689.2+68-K55</f>
         <v>381.10000000000008</v>
       </c>
-    </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O55" s="1">
+        <f>329.3+34.4</f>
+        <v>363.7</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G56" s="1">
         <v>90</v>
@@ -4844,10 +4855,13 @@
         <f>83.4-K56</f>
         <v>43.300000000000004</v>
       </c>
-    </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O56" s="1">
+        <v>39.700000000000003</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B57" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G57" s="1">
         <v>29.9</v>
@@ -4863,10 +4877,13 @@
         <f>41-K57</f>
         <v>21.6</v>
       </c>
-    </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O57" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G58" s="1">
         <v>15.8</v>
@@ -4882,10 +4899,13 @@
         <f>29.7-K58</f>
         <v>14.299999999999999</v>
       </c>
-    </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O58" s="1">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B59" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G59" s="1">
         <v>-160</v>
@@ -4901,10 +4921,13 @@
         <f>-185-K59</f>
         <v>-73.099999999999994</v>
       </c>
-    </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O59" s="1">
+        <v>-70.7</v>
+      </c>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B60" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1">
@@ -4914,8 +4937,11 @@
       <c r="L60" s="1">
         <v>-35.9</v>
       </c>
-    </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O60" s="1">
+        <v>-19.5</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B61" t="s">
         <v>34</v>
       </c>
@@ -4933,10 +4959,13 @@
         <f>-34.8-K61</f>
         <v>-18.399999999999999</v>
       </c>
-    </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O61" s="1">
+        <v>-18.3</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B62" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G62" s="1">
         <v>5.2</v>
@@ -4950,10 +4979,13 @@
       <c r="L62" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O62" s="1">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B63" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G63" s="1">
         <v>244.8</v>
@@ -4968,10 +5000,13 @@
       <c r="L63" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O63" s="1">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B64" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G64" s="1">
         <v>10.5</v>
@@ -4987,10 +5022,13 @@
         <f>23-K64</f>
         <v>28.6</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O64" s="1">
+        <v>19.3</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B65" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G65" s="1">
         <v>30.8</v>
@@ -5006,10 +5044,13 @@
         <f>-29.7-K65</f>
         <v>-80.599999999999994</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O65" s="1">
+        <v>-36.700000000000003</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B66" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G66" s="1">
         <v>248.7</v>
@@ -5025,10 +5066,11 @@
         <f>-57.7-K66</f>
         <v>-33</v>
       </c>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O66" s="1"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B67" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G67" s="1">
         <v>-119.5</v>
@@ -5044,10 +5086,13 @@
         <f>-160.1-K67</f>
         <v>-39.299999999999997</v>
       </c>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O67" s="1">
+        <v>-93.6</v>
+      </c>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B68" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G68" s="1">
         <v>-209.1</v>
@@ -5063,10 +5108,13 @@
         <f>-232.4-K68</f>
         <v>14.799999999999983</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O68" s="1">
+        <v>-102.1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B69" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G69" s="7">
         <f>G53+SUM(G54:G68)</f>
@@ -5084,8 +5132,15 @@
         <f>L53+SUM(L54:L68)</f>
         <v>736.60000000000014</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="O69" s="7">
+        <f>O53+SUM(O54:O68)</f>
+        <v>555.09999999999991</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>56</v>
+      </c>
       <c r="H70" s="1">
         <f>H69+G69</f>
         <v>1169.7000000000003</v>
@@ -5093,6 +5148,18 @@
       <c r="L70" s="1">
         <f>L69+K69</f>
         <v>1152.8999999999999</v>
+      </c>
+      <c r="O70" s="1">
+        <v>127.6</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B71" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="O71" s="7">
+        <f>O69-O70</f>
+        <v>427.49999999999989</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/GPN.xlsx
+++ b/Financial Analysis/GPN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C021EA47-1F82-41E3-AC2A-B62CF1BD66D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECA56C7-CBFB-47C4-AA1D-EEE2F37576D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{AC685D6A-8DC8-48D8-9A0E-762C4546B5AC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AC685D6A-8DC8-48D8-9A0E-762C4546B5AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="88">
   <si>
     <t>Price</t>
   </si>
@@ -320,13 +320,10 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Q125 8K</t>
-  </si>
-  <si>
-    <t>Overvalued</t>
-  </si>
-  <si>
     <t>FCF</t>
+  </si>
+  <si>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
@@ -449,14 +446,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>54</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
@@ -473,7 +470,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9235440" y="15240"/>
+          <a:off x="10462260" y="15240"/>
           <a:ext cx="0" cy="10012680"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -871,17 +868,17 @@
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>75</v>
+        <v>82.74</v>
       </c>
       <c r="E3" s="3">
-        <v>45804</v>
+        <v>45875</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45875</v>
       </c>
       <c r="G3" s="3">
-        <v>45873</v>
+        <v>45965</v>
       </c>
     </row>
     <row r="4" spans="3:9" x14ac:dyDescent="0.3">
@@ -889,11 +886,11 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <f>246.7</f>
-        <v>246.7</v>
+        <f>242.6</f>
+        <v>242.6</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="3:9" x14ac:dyDescent="0.3">
@@ -902,7 +899,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>18502.5</v>
+        <v>20072.723999999998</v>
       </c>
     </row>
     <row r="6" spans="3:9" x14ac:dyDescent="0.3">
@@ -910,11 +907,11 @@
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <f>2896</f>
-        <v>2896</v>
+        <f>2611.7</f>
+        <v>2611.6999999999998</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.3">
@@ -922,11 +919,11 @@
         <v>4</v>
       </c>
       <c r="D7" s="1">
-        <f>728+1180.4+15014.4</f>
-        <v>16922.8</v>
+        <f>627.9+1868.3+14151</f>
+        <v>16647.2</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.3">
@@ -935,7 +932,7 @@
       </c>
       <c r="D8" s="1">
         <f>D6-D7</f>
-        <v>-14026.8</v>
+        <v>-14035.5</v>
       </c>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.3">
@@ -944,7 +941,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>32529.3</v>
+        <v>34108.224000000002</v>
       </c>
     </row>
     <row r="12" spans="3:9" x14ac:dyDescent="0.3">
@@ -1114,16 +1111,13 @@
         <v>2412.1</v>
       </c>
       <c r="P3" s="7">
-        <f>L3*1.01</f>
-        <v>2594.4880000000003</v>
+        <v>1956.7</v>
       </c>
       <c r="Q3" s="7">
-        <f t="shared" ref="Q3:R3" si="0">M3*1.01</f>
-        <v>2627.616</v>
+        <v>1971</v>
       </c>
       <c r="R3" s="7">
-        <f t="shared" si="0"/>
-        <v>2540.5540000000001</v>
+        <v>2000</v>
       </c>
       <c r="T3" s="7">
         <v>4911.8999999999996</v>
@@ -1148,47 +1142,47 @@
       </c>
       <c r="Z3" s="7">
         <f>SUM(O3:R3)</f>
-        <v>10174.758</v>
+        <v>8339.7999999999993</v>
       </c>
       <c r="AA3" s="7">
         <f>Z3*1.03</f>
-        <v>10480.000739999999</v>
+        <v>8589.9939999999988</v>
       </c>
       <c r="AB3" s="7">
         <f>AA3*1.02</f>
-        <v>10689.6007548</v>
+        <v>8761.7938799999993</v>
       </c>
       <c r="AC3" s="7">
-        <f t="shared" ref="AC3:AD3" si="1">AB3*1.02</f>
-        <v>10903.392769896</v>
+        <f t="shared" ref="AC3:AD3" si="0">AB3*1.02</f>
+        <v>8937.0297575999994</v>
       </c>
       <c r="AD3" s="7">
-        <f t="shared" si="1"/>
-        <v>11121.460625293919</v>
+        <f t="shared" si="0"/>
+        <v>9115.7703527519989</v>
       </c>
       <c r="AE3" s="7">
         <f>AD3*1.01</f>
-        <v>11232.675231546858</v>
+        <v>9206.9280562795193</v>
       </c>
       <c r="AF3" s="7">
-        <f t="shared" ref="AF3:AJ3" si="2">AE3*1.01</f>
-        <v>11345.001983862327</v>
+        <f t="shared" ref="AF3:AJ3" si="1">AE3*1.01</f>
+        <v>9298.9973368423143</v>
       </c>
       <c r="AG3" s="7">
-        <f t="shared" si="2"/>
-        <v>11458.45200370095</v>
+        <f t="shared" si="1"/>
+        <v>9391.9873102107376</v>
       </c>
       <c r="AH3" s="7">
-        <f t="shared" si="2"/>
-        <v>11573.036523737959</v>
+        <f t="shared" si="1"/>
+        <v>9485.9071833128455</v>
       </c>
       <c r="AI3" s="7">
-        <f t="shared" si="2"/>
-        <v>11688.766888975339</v>
+        <f t="shared" si="1"/>
+        <v>9580.7662551459744</v>
       </c>
       <c r="AJ3" s="7">
-        <f t="shared" si="2"/>
-        <v>11805.654557865091</v>
+        <f t="shared" si="1"/>
+        <v>9676.5739176974348</v>
       </c>
     </row>
     <row r="4" spans="1:144" x14ac:dyDescent="0.3">
@@ -1235,16 +1229,15 @@
         <v>921.2</v>
       </c>
       <c r="P4" s="1">
-        <f t="shared" ref="P4:R4" si="3">P3-P5</f>
-        <v>959.96055999999999</v>
+        <v>498.8</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" si="3"/>
-        <v>945.94175999999993</v>
+        <f t="shared" ref="P4:R4" si="2">Q3-Q5</f>
+        <v>492.75</v>
       </c>
       <c r="R4" s="1">
-        <f t="shared" si="3"/>
-        <v>965.41052000000013</v>
+        <f t="shared" si="2"/>
+        <v>560</v>
       </c>
       <c r="T4" s="1">
         <v>2073.8000000000002</v>
@@ -1269,47 +1262,47 @@
       </c>
       <c r="Z4" s="1">
         <f>SUM(O4:R4)</f>
-        <v>3792.5128400000003</v>
+        <v>2472.75</v>
       </c>
       <c r="AA4" s="1">
-        <f t="shared" ref="AA4:AJ4" si="4">AA3-AA5</f>
-        <v>3668.0002589999995</v>
+        <f t="shared" ref="AA4:AJ4" si="3">AA3-AA5</f>
+        <v>2147.4984999999997</v>
       </c>
       <c r="AB4" s="1">
-        <f t="shared" si="4"/>
-        <v>3741.3602641799998</v>
+        <f t="shared" si="3"/>
+        <v>2190.4484699999994</v>
       </c>
       <c r="AC4" s="1">
-        <f t="shared" si="4"/>
-        <v>3816.1874694635999</v>
+        <f t="shared" si="3"/>
+        <v>2234.2574394000003</v>
       </c>
       <c r="AD4" s="1">
-        <f t="shared" si="4"/>
-        <v>3892.5112188528719</v>
+        <f t="shared" si="3"/>
+        <v>2278.9425881879997</v>
       </c>
       <c r="AE4" s="1">
-        <f t="shared" si="4"/>
-        <v>3931.4363310414001</v>
+        <f t="shared" si="3"/>
+        <v>2301.7320140698794</v>
       </c>
       <c r="AF4" s="1">
-        <f t="shared" si="4"/>
-        <v>3970.7506943518138</v>
+        <f t="shared" si="3"/>
+        <v>2324.749334210579</v>
       </c>
       <c r="AG4" s="1">
-        <f t="shared" si="4"/>
-        <v>4010.4582012953324</v>
+        <f t="shared" si="3"/>
+        <v>2347.9968275526844</v>
       </c>
       <c r="AH4" s="1">
-        <f t="shared" si="4"/>
-        <v>4050.5627833082854</v>
+        <f t="shared" si="3"/>
+        <v>2371.4767958282118</v>
       </c>
       <c r="AI4" s="1">
-        <f t="shared" si="4"/>
-        <v>4091.0684111413684</v>
+        <f t="shared" si="3"/>
+        <v>2395.1915637864931</v>
       </c>
       <c r="AJ4" s="1">
-        <f t="shared" si="4"/>
-        <v>4131.9790952527819</v>
+        <f t="shared" si="3"/>
+        <v>2419.1434794243587</v>
       </c>
     </row>
     <row r="5" spans="1:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1318,136 +1311,136 @@
         <v>33</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:O5" si="5">C3-C4</f>
+        <f t="shared" ref="C5:P5" si="4">C3-C4</f>
         <v>1199.1000000000001</v>
       </c>
       <c r="D5" s="7">
+        <f t="shared" si="4"/>
+        <v>1318.6000000000001</v>
+      </c>
+      <c r="E5" s="7">
+        <f t="shared" si="4"/>
+        <v>1354.2</v>
+      </c>
+      <c r="F5" s="7">
+        <f t="shared" si="4"/>
+        <v>1325.1</v>
+      </c>
+      <c r="G5" s="7">
+        <f t="shared" si="4"/>
+        <v>1344.6000000000001</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="4"/>
+        <v>1510.5</v>
+      </c>
+      <c r="I5" s="7">
+        <f t="shared" si="4"/>
+        <v>1560.1999999999998</v>
+      </c>
+      <c r="J5" s="7">
+        <f t="shared" si="4"/>
+        <v>1511.5000000000002</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="4"/>
+        <v>1497.7999999999997</v>
+      </c>
+      <c r="L5" s="7">
+        <f t="shared" si="4"/>
+        <v>1630.3000000000002</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="4"/>
+        <v>1654.6999999999998</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="4"/>
+        <v>1563.1000000000001</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="4"/>
+        <v>1490.8999999999999</v>
+      </c>
+      <c r="P5" s="7">
+        <f t="shared" si="4"/>
+        <v>1457.9</v>
+      </c>
+      <c r="Q5" s="7">
+        <f>Q3*0.75</f>
+        <v>1478.25</v>
+      </c>
+      <c r="R5" s="7">
+        <f>R3*0.72</f>
+        <v>1440</v>
+      </c>
+      <c r="T5" s="7">
+        <f t="shared" ref="T5:Y5" si="5">T3-T4</f>
+        <v>2838.0999999999995</v>
+      </c>
+      <c r="U5" s="7">
         <f t="shared" si="5"/>
-        <v>1318.6000000000001</v>
-      </c>
-      <c r="E5" s="7">
+        <v>3772.9000000000005</v>
+      </c>
+      <c r="V5" s="7">
         <f t="shared" si="5"/>
-        <v>1354.2</v>
-      </c>
-      <c r="F5" s="7">
+        <v>4750.0999999999995</v>
+      </c>
+      <c r="W5" s="7">
         <f t="shared" si="5"/>
-        <v>1325.1</v>
-      </c>
-      <c r="G5" s="7">
+        <v>5197</v>
+      </c>
+      <c r="X5" s="7">
         <f t="shared" si="5"/>
-        <v>1344.6000000000001</v>
-      </c>
-      <c r="H5" s="7">
+        <v>5926.7999999999993</v>
+      </c>
+      <c r="Y5" s="7">
         <f t="shared" si="5"/>
-        <v>1510.5</v>
-      </c>
-      <c r="I5" s="7">
-        <f t="shared" si="5"/>
-        <v>1560.1999999999998</v>
-      </c>
-      <c r="J5" s="7">
-        <f t="shared" si="5"/>
-        <v>1511.5000000000002</v>
-      </c>
-      <c r="K5" s="7">
-        <f t="shared" si="5"/>
-        <v>1497.7999999999997</v>
-      </c>
-      <c r="L5" s="7">
-        <f t="shared" si="5"/>
-        <v>1630.3000000000002</v>
-      </c>
-      <c r="M5" s="7">
-        <f t="shared" si="5"/>
-        <v>1654.6999999999998</v>
-      </c>
-      <c r="N5" s="7">
-        <f t="shared" si="5"/>
-        <v>1563.1000000000001</v>
-      </c>
-      <c r="O5" s="7">
-        <f t="shared" si="5"/>
-        <v>1490.8999999999999</v>
-      </c>
-      <c r="P5" s="7">
-        <f>P3*0.63</f>
-        <v>1634.5274400000003</v>
-      </c>
-      <c r="Q5" s="7">
-        <f>Q3*0.64</f>
-        <v>1681.6742400000001</v>
-      </c>
-      <c r="R5" s="7">
-        <f t="shared" ref="R5" si="6">R3*0.62</f>
-        <v>1575.14348</v>
-      </c>
-      <c r="T5" s="7">
-        <f t="shared" ref="T5:Y5" si="7">T3-T4</f>
-        <v>2838.0999999999995</v>
-      </c>
-      <c r="U5" s="7">
-        <f t="shared" si="7"/>
-        <v>3772.9000000000005</v>
-      </c>
-      <c r="V5" s="7">
-        <f t="shared" si="7"/>
-        <v>4750.0999999999995</v>
-      </c>
-      <c r="W5" s="7">
-        <f t="shared" si="7"/>
-        <v>5197</v>
-      </c>
-      <c r="X5" s="7">
-        <f t="shared" si="7"/>
-        <v>5926.7999999999993</v>
-      </c>
-      <c r="Y5" s="7">
-        <f t="shared" si="7"/>
         <v>6345.9</v>
       </c>
       <c r="Z5" s="7">
         <f>Z3*0.64</f>
-        <v>6511.84512</v>
+        <v>5337.4719999999998</v>
       </c>
       <c r="AA5" s="7">
-        <f>AA3*0.65</f>
-        <v>6812.000481</v>
+        <f>AA3*0.75</f>
+        <v>6442.4954999999991</v>
       </c>
       <c r="AB5" s="7">
-        <f t="shared" ref="AB5:AJ5" si="8">AB3*0.65</f>
-        <v>6948.2404906199999</v>
+        <f t="shared" ref="AB5:AJ5" si="6">AB3*0.75</f>
+        <v>6571.3454099999999</v>
       </c>
       <c r="AC5" s="7">
-        <f t="shared" si="8"/>
-        <v>7087.2053004323998</v>
+        <f t="shared" si="6"/>
+        <v>6702.7723181999991</v>
       </c>
       <c r="AD5" s="7">
-        <f t="shared" si="8"/>
-        <v>7228.9494064410474</v>
+        <f t="shared" si="6"/>
+        <v>6836.8277645639992</v>
       </c>
       <c r="AE5" s="7">
-        <f t="shared" si="8"/>
-        <v>7301.2389005054583</v>
+        <f t="shared" si="6"/>
+        <v>6905.1960422096399</v>
       </c>
       <c r="AF5" s="7">
-        <f t="shared" si="8"/>
-        <v>7374.2512895105128</v>
+        <f t="shared" si="6"/>
+        <v>6974.2480026317353</v>
       </c>
       <c r="AG5" s="7">
-        <f t="shared" si="8"/>
-        <v>7447.9938024056173</v>
+        <f t="shared" si="6"/>
+        <v>7043.9904826580532</v>
       </c>
       <c r="AH5" s="7">
-        <f t="shared" si="8"/>
-        <v>7522.4737404296739</v>
+        <f t="shared" si="6"/>
+        <v>7114.4303874846337</v>
       </c>
       <c r="AI5" s="7">
-        <f t="shared" si="8"/>
-        <v>7597.6984778339702</v>
+        <f t="shared" si="6"/>
+        <v>7185.5746913594812</v>
       </c>
       <c r="AJ5" s="7">
-        <f t="shared" si="8"/>
-        <v>7673.6754626123093</v>
+        <f t="shared" si="6"/>
+        <v>7257.4304382730761</v>
       </c>
     </row>
     <row r="6" spans="1:144" x14ac:dyDescent="0.3">
@@ -1494,16 +1487,15 @@
         <v>1024</v>
       </c>
       <c r="P6" s="1">
-        <f>P3*0.42</f>
-        <v>1089.68496</v>
+        <v>1031</v>
       </c>
       <c r="Q6" s="1">
-        <f>Q3*0.42</f>
-        <v>1103.59872</v>
+        <f>Q3*0.53</f>
+        <v>1044.6300000000001</v>
       </c>
       <c r="R6" s="1">
-        <f>R3*0.39</f>
-        <v>990.81606000000011</v>
+        <f>R3*0.53</f>
+        <v>1060</v>
       </c>
       <c r="T6" s="1">
         <v>2046.7</v>
@@ -1528,47 +1520,47 @@
       </c>
       <c r="Z6" s="1">
         <f>SUM(O6:R6)</f>
-        <v>4208.0997399999997</v>
+        <v>4159.63</v>
       </c>
       <c r="AA6" s="1">
-        <f>AA3*0.4</f>
-        <v>4192.0002960000002</v>
+        <f>AA3*0.48</f>
+        <v>4123.1971199999989</v>
       </c>
       <c r="AB6" s="1">
-        <f>AB3*0.39</f>
-        <v>4168.9442943719996</v>
+        <f t="shared" ref="AB6:AJ6" si="7">AB3*0.48</f>
+        <v>4205.6610623999995</v>
       </c>
       <c r="AC6" s="1">
-        <f t="shared" ref="AC6:AJ6" si="9">AC3*0.39</f>
-        <v>4252.3231802594401</v>
+        <f t="shared" si="7"/>
+        <v>4289.7742836479993</v>
       </c>
       <c r="AD6" s="1">
-        <f t="shared" si="9"/>
-        <v>4337.3696438646284</v>
+        <f t="shared" si="7"/>
+        <v>4375.5697693209595</v>
       </c>
       <c r="AE6" s="1">
-        <f t="shared" si="9"/>
-        <v>4380.7433403032746</v>
+        <f t="shared" si="7"/>
+        <v>4419.3254670141687</v>
       </c>
       <c r="AF6" s="1">
-        <f t="shared" si="9"/>
-        <v>4424.5507737063072</v>
+        <f t="shared" si="7"/>
+        <v>4463.5187216843105</v>
       </c>
       <c r="AG6" s="1">
-        <f t="shared" si="9"/>
-        <v>4468.7962814433704</v>
+        <f t="shared" si="7"/>
+        <v>4508.153908901154</v>
       </c>
       <c r="AH6" s="1">
-        <f t="shared" si="9"/>
-        <v>4513.4842442578047</v>
+        <f t="shared" si="7"/>
+        <v>4553.235447990166</v>
       </c>
       <c r="AI6" s="1">
-        <f t="shared" si="9"/>
-        <v>4558.6190867003825</v>
+        <f t="shared" si="7"/>
+        <v>4598.7678024700672</v>
       </c>
       <c r="AJ6" s="1">
-        <f t="shared" si="9"/>
-        <v>4604.2052775673856</v>
+        <f t="shared" si="7"/>
+        <v>4644.7554804947686</v>
       </c>
     </row>
     <row r="7" spans="1:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1577,136 +1569,136 @@
         <v>14</v>
       </c>
       <c r="C7" s="7">
-        <f t="shared" ref="C7:K7" si="10">C5-C6</f>
+        <f t="shared" ref="C7:K7" si="8">C5-C6</f>
         <v>376.00000000000011</v>
       </c>
       <c r="D7" s="7">
+        <f t="shared" si="8"/>
+        <v>455.40000000000009</v>
+      </c>
+      <c r="E7" s="7">
+        <f t="shared" si="8"/>
+        <v>435.40000000000009</v>
+      </c>
+      <c r="F7" s="7">
+        <f t="shared" si="8"/>
+        <v>405.59999999999991</v>
+      </c>
+      <c r="G7" s="7">
+        <f t="shared" si="8"/>
+        <v>301.50000000000023</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="8"/>
+        <v>497</v>
+      </c>
+      <c r="I7" s="7">
+        <f t="shared" si="8"/>
+        <v>558.19999999999982</v>
+      </c>
+      <c r="J7" s="7">
+        <f t="shared" si="8"/>
+        <v>496.30000000000018</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="8"/>
+        <v>452.29999999999973</v>
+      </c>
+      <c r="L7" s="7">
+        <f t="shared" ref="L7:R7" si="9">L5-L6</f>
+        <v>572.60000000000014</v>
+      </c>
+      <c r="M7" s="7">
+        <f t="shared" si="9"/>
+        <v>475.69999999999982</v>
+      </c>
+      <c r="N7" s="7">
+        <f t="shared" si="9"/>
+        <v>560.00000000000011</v>
+      </c>
+      <c r="O7" s="7">
+        <f t="shared" si="9"/>
+        <v>466.89999999999986</v>
+      </c>
+      <c r="P7" s="7">
+        <f t="shared" si="9"/>
+        <v>426.90000000000009</v>
+      </c>
+      <c r="Q7" s="7">
+        <f t="shared" si="9"/>
+        <v>433.61999999999989</v>
+      </c>
+      <c r="R7" s="7">
+        <f t="shared" si="9"/>
+        <v>380</v>
+      </c>
+      <c r="T7" s="7">
+        <f t="shared" ref="T7:Y7" si="10">T5-T6</f>
+        <v>791.39999999999941</v>
+      </c>
+      <c r="U7" s="7">
         <f t="shared" si="10"/>
-        <v>455.40000000000009</v>
-      </c>
-      <c r="E7" s="7">
+        <v>894.00000000000045</v>
+      </c>
+      <c r="V7" s="7">
         <f t="shared" si="10"/>
-        <v>435.40000000000009</v>
-      </c>
-      <c r="F7" s="7">
+        <v>1358.8999999999996</v>
+      </c>
+      <c r="W7" s="7">
         <f t="shared" si="10"/>
-        <v>405.59999999999991</v>
-      </c>
-      <c r="G7" s="7">
+        <v>1672.3999999999996</v>
+      </c>
+      <c r="X7" s="7">
         <f t="shared" si="10"/>
-        <v>301.50000000000023</v>
-      </c>
-      <c r="H7" s="7">
+        <v>1852.9999999999991</v>
+      </c>
+      <c r="Y7" s="7">
         <f t="shared" si="10"/>
-        <v>497</v>
-      </c>
-      <c r="I7" s="7">
-        <f t="shared" si="10"/>
-        <v>558.19999999999982</v>
-      </c>
-      <c r="J7" s="7">
-        <f t="shared" si="10"/>
-        <v>496.30000000000018</v>
-      </c>
-      <c r="K7" s="7">
-        <f t="shared" si="10"/>
-        <v>452.29999999999973</v>
-      </c>
-      <c r="L7" s="7">
-        <f t="shared" ref="L7:R7" si="11">L5-L6</f>
-        <v>572.60000000000014</v>
-      </c>
-      <c r="M7" s="7">
+        <v>2060.5999999999995</v>
+      </c>
+      <c r="Z7" s="7">
+        <f t="shared" ref="Z7:AJ7" si="11">Z5-Z6</f>
+        <v>1177.8419999999996</v>
+      </c>
+      <c r="AA7" s="7">
         <f t="shared" si="11"/>
-        <v>475.69999999999982</v>
-      </c>
-      <c r="N7" s="7">
+        <v>2319.2983800000002</v>
+      </c>
+      <c r="AB7" s="7">
         <f t="shared" si="11"/>
-        <v>560.00000000000011</v>
-      </c>
-      <c r="O7" s="7">
+        <v>2365.6843476000004</v>
+      </c>
+      <c r="AC7" s="7">
         <f t="shared" si="11"/>
-        <v>466.89999999999986</v>
-      </c>
-      <c r="P7" s="7">
+        <v>2412.9980345519998</v>
+      </c>
+      <c r="AD7" s="7">
         <f t="shared" si="11"/>
-        <v>544.84248000000025</v>
-      </c>
-      <c r="Q7" s="7">
+        <v>2461.2579952430397</v>
+      </c>
+      <c r="AE7" s="7">
         <f t="shared" si="11"/>
-        <v>578.0755200000001</v>
-      </c>
-      <c r="R7" s="7">
+        <v>2485.8705751954712</v>
+      </c>
+      <c r="AF7" s="7">
         <f t="shared" si="11"/>
-        <v>584.32741999999985</v>
-      </c>
-      <c r="T7" s="7">
-        <f t="shared" ref="T7:Y7" si="12">T5-T6</f>
-        <v>791.39999999999941</v>
-      </c>
-      <c r="U7" s="7">
-        <f t="shared" si="12"/>
-        <v>894.00000000000045</v>
-      </c>
-      <c r="V7" s="7">
-        <f t="shared" si="12"/>
-        <v>1358.8999999999996</v>
-      </c>
-      <c r="W7" s="7">
-        <f t="shared" si="12"/>
-        <v>1672.3999999999996</v>
-      </c>
-      <c r="X7" s="7">
-        <f t="shared" si="12"/>
-        <v>1852.9999999999991</v>
-      </c>
-      <c r="Y7" s="7">
-        <f t="shared" si="12"/>
-        <v>2060.5999999999995</v>
-      </c>
-      <c r="Z7" s="7">
-        <f t="shared" ref="Z7:AJ7" si="13">Z5-Z6</f>
-        <v>2303.7453800000003</v>
-      </c>
-      <c r="AA7" s="7">
-        <f t="shared" si="13"/>
-        <v>2620.0001849999999</v>
-      </c>
-      <c r="AB7" s="7">
-        <f t="shared" si="13"/>
-        <v>2779.2961962480003</v>
-      </c>
-      <c r="AC7" s="7">
-        <f t="shared" si="13"/>
-        <v>2834.8821201729597</v>
-      </c>
-      <c r="AD7" s="7">
-        <f t="shared" si="13"/>
-        <v>2891.5797625764189</v>
-      </c>
-      <c r="AE7" s="7">
-        <f t="shared" si="13"/>
-        <v>2920.4955602021837</v>
-      </c>
-      <c r="AF7" s="7">
-        <f t="shared" si="13"/>
-        <v>2949.7005158042057</v>
+        <v>2510.7292809474247</v>
       </c>
       <c r="AG7" s="7">
-        <f t="shared" si="13"/>
-        <v>2979.1975209622469</v>
+        <f t="shared" si="11"/>
+        <v>2535.8365737568993</v>
       </c>
       <c r="AH7" s="7">
-        <f t="shared" si="13"/>
-        <v>3008.9894961718692</v>
+        <f t="shared" si="11"/>
+        <v>2561.1949394944677</v>
       </c>
       <c r="AI7" s="7">
-        <f t="shared" si="13"/>
-        <v>3039.0793911335877</v>
+        <f t="shared" si="11"/>
+        <v>2586.806888889414</v>
       </c>
       <c r="AJ7" s="7">
-        <f t="shared" si="13"/>
-        <v>3069.4701850449237</v>
+        <f t="shared" si="11"/>
+        <v>2612.6749577783075</v>
       </c>
     </row>
     <row r="8" spans="1:144" x14ac:dyDescent="0.3">
@@ -1754,7 +1746,7 @@
         <v>-4</v>
       </c>
       <c r="P8" s="1">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="Q8" s="1">
         <v>0</v>
@@ -1785,7 +1777,7 @@
       </c>
       <c r="Z8" s="1">
         <f>SUM(O8:R8)</f>
-        <v>-4</v>
+        <v>-4.3</v>
       </c>
       <c r="AA8" s="1">
         <v>0</v>
@@ -1862,15 +1854,14 @@
         <v>-39.4</v>
       </c>
       <c r="P9" s="1">
-        <f t="shared" ref="P9:R9" si="14">L9*1.01</f>
-        <v>-35.652999999999999</v>
+        <v>-35.5</v>
       </c>
       <c r="Q9" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="P9:R9" si="12">M9*1.01</f>
         <v>-55.852999999999994</v>
       </c>
       <c r="R9" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>-43.026000000000003</v>
       </c>
       <c r="T9" s="1">
@@ -1896,47 +1887,47 @@
       </c>
       <c r="Z9" s="1">
         <f>SUM(O9:R9)</f>
-        <v>-173.93200000000002</v>
+        <v>-173.779</v>
       </c>
       <c r="AA9" s="1">
         <f>Z9*1.03</f>
-        <v>-179.14996000000002</v>
+        <v>-178.99236999999999</v>
       </c>
       <c r="AB9" s="1">
-        <f t="shared" ref="AB9:AJ9" si="15">AA9*1.03</f>
-        <v>-184.52445880000002</v>
+        <f t="shared" ref="AB9:AJ9" si="13">AA9*1.03</f>
+        <v>-184.3621411</v>
       </c>
       <c r="AC9" s="1">
-        <f t="shared" si="15"/>
-        <v>-190.06019256400003</v>
+        <f t="shared" si="13"/>
+        <v>-189.89300533300002</v>
       </c>
       <c r="AD9" s="1">
-        <f t="shared" si="15"/>
-        <v>-195.76199834092003</v>
+        <f t="shared" si="13"/>
+        <v>-195.58979549299002</v>
       </c>
       <c r="AE9" s="1">
-        <f t="shared" si="15"/>
-        <v>-201.63485829114762</v>
+        <f t="shared" si="13"/>
+        <v>-201.45748935777974</v>
       </c>
       <c r="AF9" s="1">
-        <f t="shared" si="15"/>
-        <v>-207.68390403988207</v>
+        <f t="shared" si="13"/>
+        <v>-207.50121403851313</v>
       </c>
       <c r="AG9" s="1">
-        <f t="shared" si="15"/>
-        <v>-213.91442116107854</v>
+        <f t="shared" si="13"/>
+        <v>-213.72625045966853</v>
       </c>
       <c r="AH9" s="1">
-        <f t="shared" si="15"/>
-        <v>-220.33185379591089</v>
+        <f t="shared" si="13"/>
+        <v>-220.13803797345861</v>
       </c>
       <c r="AI9" s="1">
-        <f t="shared" si="15"/>
-        <v>-226.94180940978822</v>
+        <f t="shared" si="13"/>
+        <v>-226.74217911266237</v>
       </c>
       <c r="AJ9" s="1">
-        <f t="shared" si="15"/>
-        <v>-233.75006369208188</v>
+        <f t="shared" si="13"/>
+        <v>-233.54444448604224</v>
       </c>
     </row>
     <row r="10" spans="1:144" x14ac:dyDescent="0.3">
@@ -1983,15 +1974,14 @@
         <v>157.1</v>
       </c>
       <c r="P10" s="1">
-        <f t="shared" ref="P10:R10" si="16">L10*0.99</f>
-        <v>157.60799999999998</v>
+        <v>152.19999999999999</v>
       </c>
       <c r="Q10" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="P10:R10" si="14">M10*0.99</f>
         <v>154.34100000000001</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" si="16"/>
+        <f t="shared" si="14"/>
         <v>155.232</v>
       </c>
       <c r="T10" s="1">
@@ -2017,47 +2007,47 @@
       </c>
       <c r="Z10" s="1">
         <f>SUM(O10:R10)</f>
-        <v>624.28099999999995</v>
+        <v>618.87299999999993</v>
       </c>
       <c r="AA10" s="1">
-        <f t="shared" ref="AA10:AJ10" si="17">Z10*0.99</f>
-        <v>618.03818999999999</v>
+        <f t="shared" ref="AA10:AJ10" si="15">Z10*0.99</f>
+        <v>612.68426999999997</v>
       </c>
       <c r="AB10" s="1">
-        <f t="shared" si="17"/>
-        <v>611.85780809999994</v>
+        <f t="shared" si="15"/>
+        <v>606.55742729999997</v>
       </c>
       <c r="AC10" s="1">
-        <f t="shared" si="17"/>
-        <v>605.73923001899993</v>
+        <f t="shared" si="15"/>
+        <v>600.49185302699993</v>
       </c>
       <c r="AD10" s="1">
-        <f t="shared" si="17"/>
-        <v>599.6818377188099</v>
+        <f t="shared" si="15"/>
+        <v>594.48693449672987</v>
       </c>
       <c r="AE10" s="1">
-        <f t="shared" si="17"/>
-        <v>593.6850193416218</v>
+        <f t="shared" si="15"/>
+        <v>588.54206515176259</v>
       </c>
       <c r="AF10" s="1">
-        <f t="shared" si="17"/>
-        <v>587.74816914820553</v>
+        <f t="shared" si="15"/>
+        <v>582.65664450024497</v>
       </c>
       <c r="AG10" s="1">
-        <f t="shared" si="17"/>
-        <v>581.87068745672343</v>
+        <f t="shared" si="15"/>
+        <v>576.83007805524255</v>
       </c>
       <c r="AH10" s="1">
-        <f t="shared" si="17"/>
-        <v>576.05198058215615</v>
+        <f t="shared" si="15"/>
+        <v>571.06177727469014</v>
       </c>
       <c r="AI10" s="1">
-        <f t="shared" si="17"/>
-        <v>570.29146077633459</v>
+        <f t="shared" si="15"/>
+        <v>565.35115950194324</v>
       </c>
       <c r="AJ10" s="1">
-        <f t="shared" si="17"/>
-        <v>564.58854616857127</v>
+        <f t="shared" si="15"/>
+        <v>559.69764790692386</v>
       </c>
     </row>
     <row r="11" spans="1:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2066,136 +2056,136 @@
         <v>17</v>
       </c>
       <c r="C11" s="7">
-        <f t="shared" ref="C11:K11" si="18">C7-C8-C9-C10</f>
+        <f t="shared" ref="C11:K11" si="16">C7-C8-C9-C10</f>
         <v>284.40000000000009</v>
       </c>
       <c r="D11" s="7">
+        <f t="shared" si="16"/>
+        <v>-626.09999999999991</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" si="16"/>
+        <v>271.7000000000001</v>
+      </c>
+      <c r="F11" s="7">
+        <f t="shared" si="16"/>
+        <v>294.39999999999992</v>
+      </c>
+      <c r="G11" s="7">
+        <f t="shared" si="16"/>
+        <v>-54.999999999999787</v>
+      </c>
+      <c r="H11" s="7">
+        <f t="shared" si="16"/>
+        <v>439.20000000000005</v>
+      </c>
+      <c r="I11" s="7">
+        <f t="shared" si="16"/>
+        <v>417.79999999999984</v>
+      </c>
+      <c r="J11" s="7">
+        <f t="shared" si="16"/>
+        <v>367.90000000000015</v>
+      </c>
+      <c r="K11" s="7">
+        <f t="shared" si="16"/>
+        <v>326.09999999999968</v>
+      </c>
+      <c r="L11" s="7">
+        <f t="shared" ref="L11:R11" si="17">L7-L8-L9-L10</f>
+        <v>448.7000000000001</v>
+      </c>
+      <c r="M11" s="7">
+        <f t="shared" si="17"/>
+        <v>375.0999999999998</v>
+      </c>
+      <c r="N11" s="7">
+        <f t="shared" si="17"/>
+        <v>718.90000000000009</v>
+      </c>
+      <c r="O11" s="7">
+        <f t="shared" si="17"/>
+        <v>353.19999999999982</v>
+      </c>
+      <c r="P11" s="7">
+        <f t="shared" si="17"/>
+        <v>310.50000000000011</v>
+      </c>
+      <c r="Q11" s="7">
+        <f t="shared" si="17"/>
+        <v>335.13199999999989</v>
+      </c>
+      <c r="R11" s="7">
+        <f t="shared" si="17"/>
+        <v>267.79399999999998</v>
+      </c>
+      <c r="T11" s="7">
+        <f t="shared" ref="T11:Z11" si="18">T7-T8-T9-T10</f>
+        <v>517.89999999999941</v>
+      </c>
+      <c r="U11" s="7">
         <f t="shared" si="18"/>
-        <v>-626.09999999999991</v>
-      </c>
-      <c r="E11" s="7">
+        <v>594.10000000000048</v>
+      </c>
+      <c r="V11" s="7">
         <f t="shared" si="18"/>
-        <v>271.7000000000001</v>
-      </c>
-      <c r="F11" s="7">
+        <v>1044.4999999999995</v>
+      </c>
+      <c r="W11" s="7">
         <f t="shared" si="18"/>
-        <v>294.39999999999992</v>
-      </c>
-      <c r="G11" s="7">
+        <v>224.39999999999952</v>
+      </c>
+      <c r="X11" s="7">
         <f t="shared" si="18"/>
-        <v>-54.999999999999787</v>
-      </c>
-      <c r="H11" s="7">
+        <v>1169.8999999999992</v>
+      </c>
+      <c r="Y11" s="7">
         <f t="shared" si="18"/>
-        <v>439.20000000000005</v>
-      </c>
-      <c r="I11" s="7">
+        <v>1868.7999999999993</v>
+      </c>
+      <c r="Z11" s="7">
         <f t="shared" si="18"/>
-        <v>417.79999999999984</v>
-      </c>
-      <c r="J11" s="7">
-        <f t="shared" si="18"/>
-        <v>367.90000000000015</v>
-      </c>
-      <c r="K11" s="7">
-        <f t="shared" si="18"/>
-        <v>326.09999999999968</v>
-      </c>
-      <c r="L11" s="7">
-        <f t="shared" ref="L11:R11" si="19">L7-L8-L9-L10</f>
-        <v>448.7000000000001</v>
-      </c>
-      <c r="M11" s="7">
+        <v>737.04799999999966</v>
+      </c>
+      <c r="AA11" s="7">
+        <f t="shared" ref="AA11:AJ11" si="19">AA7-AA8-AA9-AA10</f>
+        <v>1885.6064800000001</v>
+      </c>
+      <c r="AB11" s="7">
         <f t="shared" si="19"/>
-        <v>375.0999999999998</v>
-      </c>
-      <c r="N11" s="7">
+        <v>1943.4890614000003</v>
+      </c>
+      <c r="AC11" s="7">
         <f t="shared" si="19"/>
-        <v>718.90000000000009</v>
-      </c>
-      <c r="O11" s="7">
+        <v>2002.3991868579999</v>
+      </c>
+      <c r="AD11" s="7">
         <f t="shared" si="19"/>
-        <v>353.19999999999982</v>
-      </c>
-      <c r="P11" s="7">
+        <v>2062.3608562393001</v>
+      </c>
+      <c r="AE11" s="7">
         <f t="shared" si="19"/>
-        <v>422.88748000000032</v>
-      </c>
-      <c r="Q11" s="7">
+        <v>2098.7859994014884</v>
+      </c>
+      <c r="AF11" s="7">
         <f t="shared" si="19"/>
-        <v>479.58752000000004</v>
-      </c>
-      <c r="R11" s="7">
+        <v>2135.5738504856931</v>
+      </c>
+      <c r="AG11" s="7">
         <f t="shared" si="19"/>
-        <v>472.12141999999983</v>
-      </c>
-      <c r="T11" s="7">
-        <f t="shared" ref="T11:Z11" si="20">T7-T8-T9-T10</f>
-        <v>517.89999999999941</v>
-      </c>
-      <c r="U11" s="7">
-        <f t="shared" si="20"/>
-        <v>594.10000000000048</v>
-      </c>
-      <c r="V11" s="7">
-        <f t="shared" si="20"/>
-        <v>1044.4999999999995</v>
-      </c>
-      <c r="W11" s="7">
-        <f t="shared" si="20"/>
-        <v>224.39999999999952</v>
-      </c>
-      <c r="X11" s="7">
-        <f t="shared" si="20"/>
-        <v>1169.8999999999992</v>
-      </c>
-      <c r="Y11" s="7">
-        <f t="shared" si="20"/>
-        <v>1868.7999999999993</v>
-      </c>
-      <c r="Z11" s="7">
-        <f t="shared" si="20"/>
-        <v>1857.3963800000001</v>
-      </c>
-      <c r="AA11" s="7">
-        <f t="shared" ref="AA11:AJ11" si="21">AA7-AA8-AA9-AA10</f>
-        <v>2181.1119550000003</v>
-      </c>
-      <c r="AB11" s="7">
-        <f t="shared" si="21"/>
-        <v>2351.9628469480003</v>
-      </c>
-      <c r="AC11" s="7">
-        <f t="shared" si="21"/>
-        <v>2419.2030827179597</v>
-      </c>
-      <c r="AD11" s="7">
-        <f t="shared" si="21"/>
-        <v>2487.6599231985292</v>
-      </c>
-      <c r="AE11" s="7">
-        <f t="shared" si="21"/>
-        <v>2528.4453991517098</v>
-      </c>
-      <c r="AF11" s="7">
-        <f t="shared" si="21"/>
-        <v>2569.6362506958822</v>
-      </c>
-      <c r="AG11" s="7">
-        <f t="shared" si="21"/>
-        <v>2611.2412546666023</v>
+        <v>2172.7327461613249</v>
       </c>
       <c r="AH11" s="7">
-        <f t="shared" si="21"/>
-        <v>2653.2693693856236</v>
+        <f t="shared" si="19"/>
+        <v>2210.2712001932364</v>
       </c>
       <c r="AI11" s="7">
-        <f t="shared" si="21"/>
-        <v>2695.7297397670413</v>
+        <f t="shared" si="19"/>
+        <v>2248.1979085001335</v>
       </c>
       <c r="AJ11" s="7">
-        <f t="shared" si="21"/>
-        <v>2738.6317025684343</v>
+        <f t="shared" si="19"/>
+        <v>2286.5217543574258</v>
       </c>
     </row>
     <row r="12" spans="1:144" x14ac:dyDescent="0.3">
@@ -2242,16 +2232,15 @@
         <v>58.7</v>
       </c>
       <c r="P12" s="1">
-        <f t="shared" ref="P12:R12" si="22">P11*0.16</f>
-        <v>67.661996800000054</v>
+        <v>118.3</v>
       </c>
       <c r="Q12" s="1">
-        <f t="shared" si="22"/>
-        <v>76.734003200000004</v>
+        <f t="shared" ref="P12:R12" si="20">Q11*0.16</f>
+        <v>53.621119999999983</v>
       </c>
       <c r="R12" s="1">
-        <f t="shared" si="22"/>
-        <v>75.539427199999977</v>
+        <f t="shared" si="20"/>
+        <v>42.84704</v>
       </c>
       <c r="T12" s="1">
         <v>62.2</v>
@@ -2276,47 +2265,47 @@
       </c>
       <c r="Z12" s="1">
         <f>SUM(O12:R12)</f>
-        <v>278.63542720000004</v>
+        <v>273.46816000000001</v>
       </c>
       <c r="AA12" s="1">
-        <f t="shared" ref="AA12:AJ12" si="23">AA11*0.17</f>
-        <v>370.78903235000007</v>
+        <f t="shared" ref="AA12:AJ12" si="21">AA11*0.17</f>
+        <v>320.55310160000005</v>
       </c>
       <c r="AB12" s="1">
-        <f t="shared" si="23"/>
-        <v>399.83368398116011</v>
+        <f t="shared" si="21"/>
+        <v>330.3931404380001</v>
       </c>
       <c r="AC12" s="1">
-        <f t="shared" si="23"/>
-        <v>411.26452406205317</v>
+        <f t="shared" si="21"/>
+        <v>340.40786176585999</v>
       </c>
       <c r="AD12" s="1">
-        <f t="shared" si="23"/>
-        <v>422.90218694375</v>
+        <f t="shared" si="21"/>
+        <v>350.60134556068107</v>
       </c>
       <c r="AE12" s="1">
-        <f t="shared" si="23"/>
-        <v>429.83571785579068</v>
+        <f t="shared" si="21"/>
+        <v>356.79361989825304</v>
       </c>
       <c r="AF12" s="1">
-        <f t="shared" si="23"/>
-        <v>436.83816261829998</v>
+        <f t="shared" si="21"/>
+        <v>363.04755458256784</v>
       </c>
       <c r="AG12" s="1">
-        <f t="shared" si="23"/>
-        <v>443.91101329332241</v>
+        <f t="shared" si="21"/>
+        <v>369.36456684742529</v>
       </c>
       <c r="AH12" s="1">
-        <f t="shared" si="23"/>
-        <v>451.05579279555604</v>
+        <f t="shared" si="21"/>
+        <v>375.74610403285021</v>
       </c>
       <c r="AI12" s="1">
-        <f t="shared" si="23"/>
-        <v>458.27405576039706</v>
+        <f t="shared" si="21"/>
+        <v>382.1936444450227</v>
       </c>
       <c r="AJ12" s="1">
-        <f t="shared" si="23"/>
-        <v>465.56738943663385</v>
+        <f t="shared" si="21"/>
+        <v>388.70869824076243</v>
       </c>
     </row>
     <row r="13" spans="1:144" x14ac:dyDescent="0.3">
@@ -2363,16 +2352,13 @@
         <v>-18.3</v>
       </c>
       <c r="P13" s="1">
-        <f t="shared" ref="P13:R13" si="24">-P11*0.04</f>
-        <v>-16.915499200000014</v>
+        <v>-20</v>
       </c>
       <c r="Q13" s="1">
-        <f t="shared" si="24"/>
-        <v>-19.183500800000001</v>
+        <v>-20</v>
       </c>
       <c r="R13" s="1">
-        <f t="shared" si="24"/>
-        <v>-18.884856799999994</v>
+        <v>-20</v>
       </c>
       <c r="T13" s="1">
         <v>-13.5</v>
@@ -2397,47 +2383,47 @@
       </c>
       <c r="Z13" s="1">
         <f>SUM(O13:R13)</f>
-        <v>-73.283856800000009</v>
+        <v>-78.3</v>
       </c>
       <c r="AA13" s="1">
         <f>Z13*1.02</f>
-        <v>-74.749533936000006</v>
+        <v>-79.866</v>
       </c>
       <c r="AB13" s="1">
-        <f t="shared" ref="AB13:AJ13" si="25">AA13*1.02</f>
-        <v>-76.244524614720007</v>
+        <f t="shared" ref="AB13:AJ13" si="22">AA13*1.02</f>
+        <v>-81.463319999999996</v>
       </c>
       <c r="AC13" s="1">
-        <f t="shared" si="25"/>
-        <v>-77.76941510701441</v>
+        <f t="shared" si="22"/>
+        <v>-83.092586400000002</v>
       </c>
       <c r="AD13" s="1">
-        <f t="shared" si="25"/>
-        <v>-79.324803409154697</v>
+        <f t="shared" si="22"/>
+        <v>-84.754438128000004</v>
       </c>
       <c r="AE13" s="1">
-        <f t="shared" si="25"/>
-        <v>-80.911299477337792</v>
+        <f t="shared" si="22"/>
+        <v>-86.449526890560008</v>
       </c>
       <c r="AF13" s="1">
-        <f t="shared" si="25"/>
-        <v>-82.52952546688455</v>
+        <f t="shared" si="22"/>
+        <v>-88.178517428371208</v>
       </c>
       <c r="AG13" s="1">
-        <f t="shared" si="25"/>
-        <v>-84.18011597622224</v>
+        <f t="shared" si="22"/>
+        <v>-89.942087776938635</v>
       </c>
       <c r="AH13" s="1">
-        <f t="shared" si="25"/>
-        <v>-85.863718295746679</v>
+        <f t="shared" si="22"/>
+        <v>-91.740929532477409</v>
       </c>
       <c r="AI13" s="1">
-        <f t="shared" si="25"/>
-        <v>-87.580992661661611</v>
+        <f t="shared" si="22"/>
+        <v>-93.575748123126957</v>
       </c>
       <c r="AJ13" s="1">
-        <f t="shared" si="25"/>
-        <v>-89.332612514894848</v>
+        <f t="shared" si="22"/>
+        <v>-95.447263085589498</v>
       </c>
     </row>
     <row r="14" spans="1:144" x14ac:dyDescent="0.3">
@@ -2484,16 +2470,14 @@
         <v>7</v>
       </c>
       <c r="P14" s="1">
-        <f t="shared" ref="P14:R14" si="26">P11*0.045</f>
-        <v>19.029936600000013</v>
+        <f>-34+4.5</f>
+        <v>-29.5</v>
       </c>
       <c r="Q14" s="1">
-        <f t="shared" si="26"/>
-        <v>21.5814384</v>
+        <v>-30</v>
       </c>
       <c r="R14" s="1">
-        <f t="shared" si="26"/>
-        <v>21.24546389999999</v>
+        <v>-30</v>
       </c>
       <c r="T14" s="1">
         <v>38.700000000000003</v>
@@ -2518,47 +2502,47 @@
       </c>
       <c r="Z14" s="1">
         <f>SUM(O14:R14)</f>
-        <v>68.8568389</v>
+        <v>-82.5</v>
       </c>
       <c r="AA14" s="1">
-        <f t="shared" ref="AA14:AJ14" si="27">Z14*1.005</f>
-        <v>69.201123094499991</v>
+        <f t="shared" ref="AA14:AJ14" si="23">Z14*1.005</f>
+        <v>-82.912499999999994</v>
       </c>
       <c r="AB14" s="1">
-        <f t="shared" si="27"/>
-        <v>69.547128709972483</v>
+        <f t="shared" si="23"/>
+        <v>-83.327062499999982</v>
       </c>
       <c r="AC14" s="1">
-        <f t="shared" si="27"/>
-        <v>69.894864353522337</v>
+        <f t="shared" si="23"/>
+        <v>-83.743697812499974</v>
       </c>
       <c r="AD14" s="1">
-        <f t="shared" si="27"/>
-        <v>70.244338675289939</v>
+        <f t="shared" si="23"/>
+        <v>-84.162416301562459</v>
       </c>
       <c r="AE14" s="1">
-        <f t="shared" si="27"/>
-        <v>70.595560368666384</v>
+        <f t="shared" si="23"/>
+        <v>-84.583228383070264</v>
       </c>
       <c r="AF14" s="1">
-        <f t="shared" si="27"/>
-        <v>70.948538170509707</v>
+        <f t="shared" si="23"/>
+        <v>-85.006144524985601</v>
       </c>
       <c r="AG14" s="1">
-        <f t="shared" si="27"/>
-        <v>71.303280861362254</v>
+        <f t="shared" si="23"/>
+        <v>-85.431175247610526</v>
       </c>
       <c r="AH14" s="1">
-        <f t="shared" si="27"/>
-        <v>71.659797265669056</v>
+        <f t="shared" si="23"/>
+        <v>-85.858331123848572</v>
       </c>
       <c r="AI14" s="1">
-        <f t="shared" si="27"/>
-        <v>72.018096251997392</v>
+        <f t="shared" si="23"/>
+        <v>-86.28762277946781</v>
       </c>
       <c r="AJ14" s="1">
-        <f t="shared" si="27"/>
-        <v>72.378186733257365</v>
+        <f t="shared" si="23"/>
+        <v>-86.719060893365139</v>
       </c>
     </row>
     <row r="15" spans="1:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2567,568 +2551,568 @@
         <v>19</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:K15" si="28">C11-C12-C13-C14</f>
+        <f t="shared" ref="C15:K15" si="24">C11-C12-C13-C14</f>
         <v>244.8000000000001</v>
       </c>
       <c r="D15" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>-672.99999999999989</v>
       </c>
       <c r="E15" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>290.50000000000011</v>
       </c>
       <c r="F15" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>249.2999999999999</v>
       </c>
       <c r="G15" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>-10.999999999999789</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>274.10000000000002</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>361.79999999999984</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>361.30000000000013</v>
       </c>
       <c r="K15" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v>313.29999999999967</v>
       </c>
       <c r="L15" s="7">
-        <f t="shared" ref="L15:N15" si="29">L11-L12-L13-L14</f>
+        <f t="shared" ref="L15:N15" si="25">L11-L12-L13-L14</f>
         <v>374.7000000000001</v>
       </c>
       <c r="M15" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>315.19999999999982</v>
       </c>
       <c r="N15" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v>567.20000000000005</v>
       </c>
       <c r="O15" s="7">
-        <f t="shared" ref="O15:R15" si="30">O11-O12-O13-O14</f>
+        <f t="shared" ref="O15:R15" si="26">O11-O12-O13-O14</f>
         <v>305.79999999999984</v>
       </c>
       <c r="P15" s="7">
-        <f t="shared" si="30"/>
-        <v>353.11104580000028</v>
+        <f t="shared" si="26"/>
+        <v>241.7000000000001</v>
       </c>
       <c r="Q15" s="7">
-        <f t="shared" si="30"/>
-        <v>400.45557919999999</v>
+        <f t="shared" si="26"/>
+        <v>331.51087999999993</v>
       </c>
       <c r="R15" s="7">
-        <f t="shared" si="30"/>
-        <v>394.22138569999981</v>
+        <f t="shared" si="26"/>
+        <v>274.94695999999999</v>
       </c>
       <c r="T15" s="7">
-        <f t="shared" ref="T15:Y15" si="31">T11-T12-T13-T14</f>
+        <f t="shared" ref="T15:Y15" si="27">T11-T12-T13-T14</f>
         <v>430.49999999999943</v>
       </c>
       <c r="U15" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="27"/>
         <v>584.60000000000036</v>
       </c>
       <c r="V15" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="27"/>
         <v>965.49999999999955</v>
       </c>
       <c r="W15" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="27"/>
         <v>111.59999999999953</v>
       </c>
       <c r="X15" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="27"/>
         <v>986.19999999999925</v>
       </c>
       <c r="Y15" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="27"/>
         <v>1570.3999999999994</v>
       </c>
       <c r="Z15" s="7">
-        <f t="shared" ref="Z15" si="32">Z11-Z12-Z13-Z14</f>
-        <v>1583.1879707000001</v>
+        <f t="shared" ref="Z15" si="28">Z11-Z12-Z13-Z14</f>
+        <v>624.3798399999996</v>
       </c>
       <c r="AA15" s="7">
-        <f t="shared" ref="AA15" si="33">AA11-AA12-AA13-AA14</f>
-        <v>1815.8713334915003</v>
+        <f t="shared" ref="AA15" si="29">AA11-AA12-AA13-AA14</f>
+        <v>1727.8318784000001</v>
       </c>
       <c r="AB15" s="7">
-        <f t="shared" ref="AB15" si="34">AB11-AB12-AB13-AB14</f>
-        <v>1958.8265588715878</v>
+        <f t="shared" ref="AB15" si="30">AB11-AB12-AB13-AB14</f>
+        <v>1777.8863034620003</v>
       </c>
       <c r="AC15" s="7">
-        <f t="shared" ref="AC15" si="35">AC11-AC12-AC13-AC14</f>
-        <v>2015.8131094093987</v>
+        <f t="shared" ref="AC15" si="31">AC11-AC12-AC13-AC14</f>
+        <v>1828.82760930464</v>
       </c>
       <c r="AD15" s="7">
-        <f t="shared" ref="AD15" si="36">AD11-AD12-AD13-AD14</f>
-        <v>2073.8382009886441</v>
+        <f t="shared" ref="AD15" si="32">AD11-AD12-AD13-AD14</f>
+        <v>1880.6763651081815</v>
       </c>
       <c r="AE15" s="7">
-        <f t="shared" ref="AE15" si="37">AE11-AE12-AE13-AE14</f>
-        <v>2108.9254204045901</v>
+        <f t="shared" ref="AE15" si="33">AE11-AE12-AE13-AE14</f>
+        <v>1913.0251347768658</v>
       </c>
       <c r="AF15" s="7">
-        <f t="shared" ref="AF15" si="38">AF11-AF12-AF13-AF14</f>
-        <v>2144.3790753739568</v>
+        <f t="shared" ref="AF15" si="34">AF11-AF12-AF13-AF14</f>
+        <v>1945.7109578564819</v>
       </c>
       <c r="AG15" s="7">
-        <f t="shared" ref="AG15" si="39">AG11-AG12-AG13-AG14</f>
-        <v>2180.20707648814</v>
+        <f t="shared" ref="AG15" si="35">AG11-AG12-AG13-AG14</f>
+        <v>1978.7414423384489</v>
       </c>
       <c r="AH15" s="7">
-        <f t="shared" ref="AH15" si="40">AH11-AH12-AH13-AH14</f>
-        <v>2216.4174976201452</v>
+        <f t="shared" ref="AH15" si="36">AH11-AH12-AH13-AH14</f>
+        <v>2012.124356816712</v>
       </c>
       <c r="AI15" s="7">
-        <f t="shared" ref="AI15" si="41">AI11-AI12-AI13-AI14</f>
-        <v>2253.0185804163084</v>
+        <f t="shared" ref="AI15" si="37">AI11-AI12-AI13-AI14</f>
+        <v>2045.8676349577054</v>
       </c>
       <c r="AJ15" s="7">
-        <f t="shared" ref="AJ15" si="42">AJ11-AJ12-AJ13-AJ14</f>
-        <v>2290.018738913438</v>
+        <f t="shared" ref="AJ15" si="38">AJ11-AJ12-AJ13-AJ14</f>
+        <v>2079.9793800956181</v>
       </c>
       <c r="AK15" s="10">
         <f>AJ15+(AJ15*$AN$20)</f>
-        <v>2267.1185515243037</v>
+        <v>2059.1795862946619</v>
       </c>
       <c r="AL15" s="10">
-        <f t="shared" ref="AL15:CW15" si="43">AK15+(AK15*$AN$20)</f>
-        <v>2244.4473660090607</v>
+        <f t="shared" ref="AL15:CW15" si="39">AK15+(AK15*$AN$20)</f>
+        <v>2038.5877904317153</v>
       </c>
       <c r="AM15" s="10">
-        <f t="shared" si="43"/>
-        <v>2222.0028923489699</v>
+        <f t="shared" si="39"/>
+        <v>2018.2019125273982</v>
       </c>
       <c r="AN15" s="10">
-        <f t="shared" si="43"/>
-        <v>2199.7828634254802</v>
+        <f t="shared" si="39"/>
+        <v>1998.0198934021244</v>
       </c>
       <c r="AO15" s="10">
-        <f t="shared" si="43"/>
-        <v>2177.7850347912254</v>
+        <f t="shared" si="39"/>
+        <v>1978.0396944681031</v>
       </c>
       <c r="AP15" s="10">
-        <f t="shared" si="43"/>
-        <v>2156.0071844433132</v>
+        <f t="shared" si="39"/>
+        <v>1958.259297523422</v>
       </c>
       <c r="AQ15" s="10">
-        <f t="shared" si="43"/>
-        <v>2134.4471125988803</v>
+        <f t="shared" si="39"/>
+        <v>1938.6767045481877</v>
       </c>
       <c r="AR15" s="10">
-        <f t="shared" si="43"/>
-        <v>2113.1026414728913</v>
+        <f t="shared" si="39"/>
+        <v>1919.2899375027057</v>
       </c>
       <c r="AS15" s="10">
-        <f t="shared" si="43"/>
-        <v>2091.9716150581626</v>
+        <f t="shared" si="39"/>
+        <v>1900.0970381276786</v>
       </c>
       <c r="AT15" s="10">
-        <f t="shared" si="43"/>
-        <v>2071.0518989075808</v>
+        <f t="shared" si="39"/>
+        <v>1881.0960677464018</v>
       </c>
       <c r="AU15" s="10">
-        <f t="shared" si="43"/>
-        <v>2050.341379918505</v>
+        <f t="shared" si="39"/>
+        <v>1862.2851070689378</v>
       </c>
       <c r="AV15" s="10">
-        <f t="shared" si="43"/>
-        <v>2029.8379661193201</v>
+        <f t="shared" si="39"/>
+        <v>1843.6622559982484</v>
       </c>
       <c r="AW15" s="10">
-        <f t="shared" si="43"/>
-        <v>2009.5395864581269</v>
+        <f t="shared" si="39"/>
+        <v>1825.225633438266</v>
       </c>
       <c r="AX15" s="10">
-        <f t="shared" si="43"/>
-        <v>1989.4441905935457</v>
+        <f t="shared" si="39"/>
+        <v>1806.9733771038832</v>
       </c>
       <c r="AY15" s="10">
-        <f t="shared" si="43"/>
-        <v>1969.5497486876102</v>
+        <f t="shared" si="39"/>
+        <v>1788.9036433328445</v>
       </c>
       <c r="AZ15" s="10">
-        <f t="shared" si="43"/>
-        <v>1949.8542512007341</v>
+        <f t="shared" si="39"/>
+        <v>1771.0146068995159</v>
       </c>
       <c r="BA15" s="10">
-        <f t="shared" si="43"/>
-        <v>1930.3557086887267</v>
+        <f t="shared" si="39"/>
+        <v>1753.3044608305208</v>
       </c>
       <c r="BB15" s="10">
-        <f t="shared" si="43"/>
-        <v>1911.0521516018396</v>
+        <f t="shared" si="39"/>
+        <v>1735.7714162222155</v>
       </c>
       <c r="BC15" s="10">
-        <f t="shared" si="43"/>
-        <v>1891.9416300858211</v>
+        <f t="shared" si="39"/>
+        <v>1718.4137020599933</v>
       </c>
       <c r="BD15" s="10">
-        <f t="shared" si="43"/>
-        <v>1873.0222137849628</v>
+        <f t="shared" si="39"/>
+        <v>1701.2295650393933</v>
       </c>
       <c r="BE15" s="10">
-        <f t="shared" si="43"/>
-        <v>1854.2919916471133</v>
+        <f t="shared" si="39"/>
+        <v>1684.2172693889993</v>
       </c>
       <c r="BF15" s="10">
-        <f t="shared" si="43"/>
-        <v>1835.7490717306421</v>
+        <f t="shared" si="39"/>
+        <v>1667.3750966951093</v>
       </c>
       <c r="BG15" s="10">
-        <f t="shared" si="43"/>
-        <v>1817.3915810133356</v>
+        <f t="shared" si="39"/>
+        <v>1650.7013457281582</v>
       </c>
       <c r="BH15" s="10">
-        <f t="shared" si="43"/>
-        <v>1799.2176652032022</v>
+        <f t="shared" si="39"/>
+        <v>1634.1943322708767</v>
       </c>
       <c r="BI15" s="10">
-        <f t="shared" si="43"/>
-        <v>1781.2254885511702</v>
+        <f t="shared" si="39"/>
+        <v>1617.8523889481678</v>
       </c>
       <c r="BJ15" s="10">
-        <f t="shared" si="43"/>
-        <v>1763.4132336656585</v>
+        <f t="shared" si="39"/>
+        <v>1601.673865058686</v>
       </c>
       <c r="BK15" s="10">
-        <f t="shared" si="43"/>
-        <v>1745.7791013290018</v>
+        <f t="shared" si="39"/>
+        <v>1585.6571264080992</v>
       </c>
       <c r="BL15" s="10">
-        <f t="shared" si="43"/>
-        <v>1728.3213103157118</v>
+        <f t="shared" si="39"/>
+        <v>1569.8005551440183</v>
       </c>
       <c r="BM15" s="10">
-        <f t="shared" si="43"/>
-        <v>1711.0380972125547</v>
+        <f t="shared" si="39"/>
+        <v>1554.102549592578</v>
       </c>
       <c r="BN15" s="10">
-        <f t="shared" si="43"/>
-        <v>1693.9277162404292</v>
+        <f t="shared" si="39"/>
+        <v>1538.5615240966522</v>
       </c>
       <c r="BO15" s="10">
-        <f t="shared" si="43"/>
-        <v>1676.9884390780248</v>
+        <f t="shared" si="39"/>
+        <v>1523.1759088556857</v>
       </c>
       <c r="BP15" s="10">
-        <f t="shared" si="43"/>
-        <v>1660.2185546872447</v>
+        <f t="shared" si="39"/>
+        <v>1507.9441497671289</v>
       </c>
       <c r="BQ15" s="10">
-        <f t="shared" si="43"/>
-        <v>1643.6163691403722</v>
+        <f t="shared" si="39"/>
+        <v>1492.8647082694577</v>
       </c>
       <c r="BR15" s="10">
-        <f t="shared" si="43"/>
-        <v>1627.1802054489685</v>
+        <f t="shared" si="39"/>
+        <v>1477.936061186763</v>
       </c>
       <c r="BS15" s="10">
-        <f t="shared" si="43"/>
-        <v>1610.9084033944789</v>
+        <f t="shared" si="39"/>
+        <v>1463.1567005748955</v>
       </c>
       <c r="BT15" s="10">
-        <f t="shared" si="43"/>
-        <v>1594.7993193605341</v>
+        <f t="shared" si="39"/>
+        <v>1448.5251335691464</v>
       </c>
       <c r="BU15" s="10">
-        <f t="shared" si="43"/>
-        <v>1578.8513261669289</v>
+        <f t="shared" si="39"/>
+        <v>1434.039882233455</v>
       </c>
       <c r="BV15" s="10">
-        <f t="shared" si="43"/>
-        <v>1563.0628129052595</v>
+        <f t="shared" si="39"/>
+        <v>1419.6994834111206</v>
       </c>
       <c r="BW15" s="10">
-        <f t="shared" si="43"/>
-        <v>1547.4321847762069</v>
+        <f t="shared" si="39"/>
+        <v>1405.5024885770094</v>
       </c>
       <c r="BX15" s="10">
-        <f t="shared" si="43"/>
-        <v>1531.9578629284449</v>
+        <f t="shared" si="39"/>
+        <v>1391.4474636912394</v>
       </c>
       <c r="BY15" s="10">
-        <f t="shared" si="43"/>
-        <v>1516.6382842991604</v>
+        <f t="shared" si="39"/>
+        <v>1377.5329890543269</v>
       </c>
       <c r="BZ15" s="10">
-        <f t="shared" si="43"/>
-        <v>1501.4719014561688</v>
+        <f t="shared" si="39"/>
+        <v>1363.7576591637837</v>
       </c>
       <c r="CA15" s="10">
-        <f t="shared" si="43"/>
-        <v>1486.4571824416071</v>
+        <f t="shared" si="39"/>
+        <v>1350.120082572146</v>
       </c>
       <c r="CB15" s="10">
-        <f t="shared" si="43"/>
-        <v>1471.592610617191</v>
+        <f t="shared" si="39"/>
+        <v>1336.6188817464244</v>
       </c>
       <c r="CC15" s="10">
-        <f t="shared" si="43"/>
-        <v>1456.876684511019</v>
+        <f t="shared" si="39"/>
+        <v>1323.2526929289602</v>
       </c>
       <c r="CD15" s="10">
-        <f t="shared" si="43"/>
-        <v>1442.3079176659089</v>
+        <f t="shared" si="39"/>
+        <v>1310.0201659996706</v>
       </c>
       <c r="CE15" s="10">
-        <f t="shared" si="43"/>
-        <v>1427.8848384892499</v>
+        <f t="shared" si="39"/>
+        <v>1296.9199643396739</v>
       </c>
       <c r="CF15" s="10">
-        <f t="shared" si="43"/>
-        <v>1413.6059901043575</v>
+        <f t="shared" si="39"/>
+        <v>1283.9507646962772</v>
       </c>
       <c r="CG15" s="10">
-        <f t="shared" si="43"/>
-        <v>1399.4699302033139</v>
+        <f t="shared" si="39"/>
+        <v>1271.1112570493144</v>
       </c>
       <c r="CH15" s="10">
-        <f t="shared" si="43"/>
-        <v>1385.4752309012808</v>
+        <f t="shared" si="39"/>
+        <v>1258.4001444788212</v>
       </c>
       <c r="CI15" s="10">
-        <f t="shared" si="43"/>
-        <v>1371.620478592268</v>
+        <f t="shared" si="39"/>
+        <v>1245.8161430340331</v>
       </c>
       <c r="CJ15" s="10">
-        <f t="shared" si="43"/>
-        <v>1357.9042738063454</v>
+        <f t="shared" si="39"/>
+        <v>1233.3579816036927</v>
       </c>
       <c r="CK15" s="10">
-        <f t="shared" si="43"/>
-        <v>1344.3252310682819</v>
+        <f t="shared" si="39"/>
+        <v>1221.0244017876557</v>
       </c>
       <c r="CL15" s="10">
-        <f t="shared" si="43"/>
-        <v>1330.8819787575992</v>
+        <f t="shared" si="39"/>
+        <v>1208.8141577697793</v>
       </c>
       <c r="CM15" s="10">
-        <f t="shared" si="43"/>
-        <v>1317.5731589700233</v>
+        <f t="shared" si="39"/>
+        <v>1196.7260161920815</v>
       </c>
       <c r="CN15" s="10">
-        <f t="shared" si="43"/>
-        <v>1304.3974273803231</v>
+        <f t="shared" si="39"/>
+        <v>1184.7587560301606</v>
       </c>
       <c r="CO15" s="10">
-        <f t="shared" si="43"/>
-        <v>1291.3534531065197</v>
+        <f t="shared" si="39"/>
+        <v>1172.9111684698589</v>
       </c>
       <c r="CP15" s="10">
-        <f t="shared" si="43"/>
-        <v>1278.4399185754546</v>
+        <f t="shared" si="39"/>
+        <v>1161.1820567851603</v>
       </c>
       <c r="CQ15" s="10">
-        <f t="shared" si="43"/>
-        <v>1265.6555193897</v>
+        <f t="shared" si="39"/>
+        <v>1149.5702362173088</v>
       </c>
       <c r="CR15" s="10">
-        <f t="shared" si="43"/>
-        <v>1252.998964195803</v>
+        <f t="shared" si="39"/>
+        <v>1138.0745338551358</v>
       </c>
       <c r="CS15" s="10">
-        <f t="shared" si="43"/>
-        <v>1240.4689745538449</v>
+        <f t="shared" si="39"/>
+        <v>1126.6937885165844</v>
       </c>
       <c r="CT15" s="10">
-        <f t="shared" si="43"/>
-        <v>1228.0642848083064</v>
+        <f t="shared" si="39"/>
+        <v>1115.4268506314186</v>
       </c>
       <c r="CU15" s="10">
-        <f t="shared" si="43"/>
-        <v>1215.7836419602233</v>
+        <f t="shared" si="39"/>
+        <v>1104.2725821251045</v>
       </c>
       <c r="CV15" s="10">
-        <f t="shared" si="43"/>
-        <v>1203.6258055406211</v>
+        <f t="shared" si="39"/>
+        <v>1093.2298563038535</v>
       </c>
       <c r="CW15" s="10">
-        <f t="shared" si="43"/>
-        <v>1191.5895474852148</v>
+        <f t="shared" si="39"/>
+        <v>1082.2975577408149</v>
       </c>
       <c r="CX15" s="10">
-        <f t="shared" ref="CX15:EN15" si="44">CW15+(CW15*$AN$20)</f>
-        <v>1179.6736520103627</v>
+        <f t="shared" ref="CX15:EN15" si="40">CW15+(CW15*$AN$20)</f>
+        <v>1071.4745821634067</v>
       </c>
       <c r="CY15" s="10">
-        <f t="shared" si="44"/>
-        <v>1167.8769154902591</v>
+        <f t="shared" si="40"/>
+        <v>1060.7598363417726</v>
       </c>
       <c r="CZ15" s="10">
-        <f t="shared" si="44"/>
-        <v>1156.1981463353566</v>
+        <f t="shared" si="40"/>
+        <v>1050.1522379783548</v>
       </c>
       <c r="DA15" s="10">
-        <f t="shared" si="44"/>
-        <v>1144.6361648720031</v>
+        <f t="shared" si="40"/>
+        <v>1039.6507155985712</v>
       </c>
       <c r="DB15" s="10">
-        <f t="shared" si="44"/>
-        <v>1133.189803223283</v>
+        <f t="shared" si="40"/>
+        <v>1029.2542084425854</v>
       </c>
       <c r="DC15" s="10">
-        <f t="shared" si="44"/>
-        <v>1121.8579051910501</v>
+        <f t="shared" si="40"/>
+        <v>1018.9616663581596</v>
       </c>
       <c r="DD15" s="10">
-        <f t="shared" si="44"/>
-        <v>1110.6393261391397</v>
+        <f t="shared" si="40"/>
+        <v>1008.7720496945781</v>
       </c>
       <c r="DE15" s="10">
-        <f t="shared" si="44"/>
-        <v>1099.5329328777484</v>
+        <f t="shared" si="40"/>
+        <v>998.68432919763234</v>
       </c>
       <c r="DF15" s="10">
-        <f t="shared" si="44"/>
-        <v>1088.537603548971</v>
+        <f t="shared" si="40"/>
+        <v>988.69748590565598</v>
       </c>
       <c r="DG15" s="10">
-        <f t="shared" si="44"/>
-        <v>1077.6522275134812</v>
+        <f t="shared" si="40"/>
+        <v>978.81051104659946</v>
       </c>
       <c r="DH15" s="10">
-        <f t="shared" si="44"/>
-        <v>1066.8757052383464</v>
+        <f t="shared" si="40"/>
+        <v>969.02240593613351</v>
       </c>
       <c r="DI15" s="10">
-        <f t="shared" si="44"/>
-        <v>1056.206948185963</v>
+        <f t="shared" si="40"/>
+        <v>959.33218187677221</v>
       </c>
       <c r="DJ15" s="10">
-        <f t="shared" si="44"/>
-        <v>1045.6448787041033</v>
+        <f t="shared" si="40"/>
+        <v>949.73886005800443</v>
       </c>
       <c r="DK15" s="10">
-        <f t="shared" si="44"/>
-        <v>1035.1884299170624</v>
+        <f t="shared" si="40"/>
+        <v>940.24147145742438</v>
       </c>
       <c r="DL15" s="10">
-        <f t="shared" si="44"/>
-        <v>1024.8365456178917</v>
+        <f t="shared" si="40"/>
+        <v>930.83905674285018</v>
       </c>
       <c r="DM15" s="10">
-        <f t="shared" si="44"/>
-        <v>1014.5881801617128</v>
+        <f t="shared" si="40"/>
+        <v>921.53066617542163</v>
       </c>
       <c r="DN15" s="10">
-        <f t="shared" si="44"/>
-        <v>1004.4422983600956</v>
+        <f t="shared" si="40"/>
+        <v>912.31535951366743</v>
       </c>
       <c r="DO15" s="10">
-        <f t="shared" si="44"/>
-        <v>994.39787537649465</v>
+        <f t="shared" si="40"/>
+        <v>903.1922059185307</v>
       </c>
       <c r="DP15" s="10">
-        <f t="shared" si="44"/>
-        <v>984.45389662272976</v>
+        <f t="shared" si="40"/>
+        <v>894.16028385934544</v>
       </c>
       <c r="DQ15" s="10">
-        <f t="shared" si="44"/>
-        <v>974.60935765650243</v>
+        <f t="shared" si="40"/>
+        <v>885.218681020752</v>
       </c>
       <c r="DR15" s="10">
-        <f t="shared" si="44"/>
-        <v>964.86326407993738</v>
+        <f t="shared" si="40"/>
+        <v>876.36649421054449</v>
       </c>
       <c r="DS15" s="10">
-        <f t="shared" si="44"/>
-        <v>955.21463143913797</v>
+        <f t="shared" si="40"/>
+        <v>867.602829268439</v>
       </c>
       <c r="DT15" s="10">
-        <f t="shared" si="44"/>
-        <v>945.66248512474658</v>
+        <f t="shared" si="40"/>
+        <v>858.92680097575465</v>
       </c>
       <c r="DU15" s="10">
-        <f t="shared" si="44"/>
-        <v>936.20586027349907</v>
+        <f t="shared" si="40"/>
+        <v>850.33753296599707</v>
       </c>
       <c r="DV15" s="10">
-        <f t="shared" si="44"/>
-        <v>926.84380167076404</v>
+        <f t="shared" si="40"/>
+        <v>841.83415763633707</v>
       </c>
       <c r="DW15" s="10">
-        <f t="shared" si="44"/>
-        <v>917.57536365405645</v>
+        <f t="shared" si="40"/>
+        <v>833.41581605997374</v>
       </c>
       <c r="DX15" s="10">
-        <f t="shared" si="44"/>
-        <v>908.3996100175159</v>
+        <f t="shared" si="40"/>
+        <v>825.08165789937402</v>
       </c>
       <c r="DY15" s="10">
-        <f t="shared" si="44"/>
-        <v>899.31561391734078</v>
+        <f t="shared" si="40"/>
+        <v>816.83084132038027</v>
       </c>
       <c r="DZ15" s="10">
-        <f t="shared" si="44"/>
-        <v>890.3224577781674</v>
+        <f t="shared" si="40"/>
+        <v>808.66253290717646</v>
       </c>
       <c r="EA15" s="10">
-        <f t="shared" si="44"/>
-        <v>881.41923320038575</v>
+        <f t="shared" si="40"/>
+        <v>800.57590757810465</v>
       </c>
       <c r="EB15" s="10">
-        <f t="shared" si="44"/>
-        <v>872.60504086838193</v>
+        <f t="shared" si="40"/>
+        <v>792.5701485023236</v>
       </c>
       <c r="EC15" s="10">
-        <f t="shared" si="44"/>
-        <v>863.87899045969812</v>
+        <f t="shared" si="40"/>
+        <v>784.64444701730042</v>
       </c>
       <c r="ED15" s="10">
-        <f t="shared" si="44"/>
-        <v>855.24020055510118</v>
+        <f t="shared" si="40"/>
+        <v>776.79800254712745</v>
       </c>
       <c r="EE15" s="10">
-        <f t="shared" si="44"/>
-        <v>846.68779854955017</v>
+        <f t="shared" si="40"/>
+        <v>769.03002252165618</v>
       </c>
       <c r="EF15" s="10">
-        <f t="shared" si="44"/>
-        <v>838.22092056405461</v>
+        <f t="shared" si="40"/>
+        <v>761.33972229643962</v>
       </c>
       <c r="EG15" s="10">
-        <f t="shared" si="44"/>
-        <v>829.83871135841412</v>
+        <f t="shared" si="40"/>
+        <v>753.72632507347521</v>
       </c>
       <c r="EH15" s="10">
-        <f t="shared" si="44"/>
-        <v>821.54032424483</v>
+        <f t="shared" si="40"/>
+        <v>746.18906182274043</v>
       </c>
       <c r="EI15" s="10">
-        <f t="shared" si="44"/>
-        <v>813.32492100238176</v>
+        <f t="shared" si="40"/>
+        <v>738.72717120451307</v>
       </c>
       <c r="EJ15" s="10">
-        <f t="shared" si="44"/>
-        <v>805.19167179235797</v>
+        <f t="shared" si="40"/>
+        <v>731.33989949246791</v>
       </c>
       <c r="EK15" s="10">
-        <f t="shared" si="44"/>
-        <v>797.13975507443433</v>
+        <f t="shared" si="40"/>
+        <v>724.02650049754322</v>
       </c>
       <c r="EL15" s="10">
-        <f t="shared" si="44"/>
-        <v>789.16835752369002</v>
+        <f t="shared" si="40"/>
+        <v>716.78623549256781</v>
       </c>
       <c r="EM15" s="10">
-        <f t="shared" si="44"/>
-        <v>781.27667394845309</v>
+        <f t="shared" si="40"/>
+        <v>709.61837313764215</v>
       </c>
       <c r="EN15" s="10">
-        <f t="shared" si="44"/>
-        <v>773.46390720896852</v>
+        <f t="shared" si="40"/>
+        <v>702.52218940626574</v>
       </c>
     </row>
     <row r="16" spans="1:144" x14ac:dyDescent="0.3">
@@ -3177,16 +3161,16 @@
         <v>246.7</v>
       </c>
       <c r="P16" s="1">
-        <f>246.7</f>
-        <v>246.7</v>
+        <f>242.6</f>
+        <v>242.6</v>
       </c>
       <c r="Q16" s="1">
-        <f>246.7</f>
-        <v>246.7</v>
+        <f>242.6</f>
+        <v>242.6</v>
       </c>
       <c r="R16" s="1">
-        <f>246.7</f>
-        <v>246.7</v>
+        <f>242.6</f>
+        <v>242.6</v>
       </c>
       <c r="T16" s="1">
         <v>255.2</v>
@@ -3204,52 +3188,52 @@
         <v>255.2</v>
       </c>
       <c r="Y16" s="1">
-        <f t="shared" ref="Y16" si="45">247.6</f>
+        <f t="shared" ref="Y16" si="41">247.6</f>
         <v>247.6</v>
       </c>
       <c r="Z16" s="1">
-        <f t="shared" ref="Z16:AJ16" si="46">246.7</f>
-        <v>246.7</v>
+        <f t="shared" ref="Z16:AJ16" si="42">242.6</f>
+        <v>242.6</v>
       </c>
       <c r="AA16" s="1">
-        <f t="shared" si="46"/>
-        <v>246.7</v>
+        <f t="shared" si="42"/>
+        <v>242.6</v>
       </c>
       <c r="AB16" s="1">
-        <f t="shared" si="46"/>
-        <v>246.7</v>
+        <f t="shared" si="42"/>
+        <v>242.6</v>
       </c>
       <c r="AC16" s="1">
-        <f t="shared" si="46"/>
-        <v>246.7</v>
+        <f t="shared" si="42"/>
+        <v>242.6</v>
       </c>
       <c r="AD16" s="1">
-        <f t="shared" si="46"/>
-        <v>246.7</v>
+        <f t="shared" si="42"/>
+        <v>242.6</v>
       </c>
       <c r="AE16" s="1">
-        <f t="shared" si="46"/>
-        <v>246.7</v>
+        <f t="shared" si="42"/>
+        <v>242.6</v>
       </c>
       <c r="AF16" s="1">
-        <f t="shared" si="46"/>
-        <v>246.7</v>
+        <f t="shared" si="42"/>
+        <v>242.6</v>
       </c>
       <c r="AG16" s="1">
-        <f t="shared" si="46"/>
-        <v>246.7</v>
+        <f t="shared" si="42"/>
+        <v>242.6</v>
       </c>
       <c r="AH16" s="1">
-        <f t="shared" si="46"/>
-        <v>246.7</v>
+        <f t="shared" si="42"/>
+        <v>242.6</v>
       </c>
       <c r="AI16" s="1">
-        <f t="shared" si="46"/>
-        <v>246.7</v>
+        <f t="shared" si="42"/>
+        <v>242.6</v>
       </c>
       <c r="AJ16" s="1">
-        <f t="shared" si="46"/>
-        <v>246.7</v>
+        <f t="shared" si="42"/>
+        <v>242.6</v>
       </c>
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.3">
@@ -3257,136 +3241,136 @@
         <v>20</v>
       </c>
       <c r="C17" s="5">
-        <f t="shared" ref="C17:K17" si="47">C15/C16</f>
+        <f t="shared" ref="C17:K17" si="43">C15/C16</f>
         <v>0.95924764890282177</v>
       </c>
       <c r="D17" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>-2.6371473354231973</v>
       </c>
       <c r="E17" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>1.1383228840125397</v>
       </c>
       <c r="F17" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>0.9768808777429463</v>
       </c>
       <c r="G17" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>-4.3103448275861239E-2</v>
       </c>
       <c r="H17" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>1.0740595611285269</v>
       </c>
       <c r="I17" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>1.4177115987460809</v>
       </c>
       <c r="J17" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>1.4157523510971792</v>
       </c>
       <c r="K17" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="43"/>
         <v>1.2276645768025065</v>
       </c>
       <c r="L17" s="5">
-        <f t="shared" ref="L17:N17" si="48">L15/L16</f>
+        <f t="shared" ref="L17:N17" si="44">L15/L16</f>
         <v>1.4728773584905663</v>
       </c>
       <c r="M17" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>1.238506876227897</v>
       </c>
       <c r="N17" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="44"/>
         <v>2.2907915993537968</v>
       </c>
       <c r="O17" s="5">
-        <f t="shared" ref="O17:R17" si="49">O15/O16</f>
+        <f t="shared" ref="O17:R17" si="45">O15/O16</f>
         <v>1.2395622213214426</v>
       </c>
       <c r="P17" s="5">
-        <f t="shared" si="49"/>
-        <v>1.4313378427239574</v>
+        <f t="shared" si="45"/>
+        <v>0.99629018961253135</v>
       </c>
       <c r="Q17" s="5">
-        <f t="shared" si="49"/>
-        <v>1.6232492063234698</v>
+        <f t="shared" si="45"/>
+        <v>1.3664916735366857</v>
       </c>
       <c r="R17" s="5">
-        <f t="shared" si="49"/>
-        <v>1.5979788638021881</v>
+        <f t="shared" si="45"/>
+        <v>1.1333345424567189</v>
       </c>
       <c r="T17" s="5">
-        <f t="shared" ref="T17:Y17" si="50">T15/T16</f>
+        <f t="shared" ref="T17:Y17" si="46">T15/T16</f>
         <v>1.6869122257053271</v>
       </c>
       <c r="U17" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>2.2907523510971801</v>
       </c>
       <c r="V17" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>3.7833072100313463</v>
       </c>
       <c r="W17" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>0.43730407523510789</v>
       </c>
       <c r="X17" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>3.8644200626959222</v>
       </c>
       <c r="Y17" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="46"/>
         <v>6.3424878836833578</v>
       </c>
       <c r="Z17" s="5">
-        <f t="shared" ref="Z17" si="51">Z15/Z16</f>
-        <v>6.4174623862991496</v>
+        <f t="shared" ref="Z17" si="47">Z15/Z16</f>
+        <v>2.5737009068425376</v>
       </c>
       <c r="AA17" s="5">
-        <f t="shared" ref="AA17" si="52">AA15/AA16</f>
-        <v>7.360645859308879</v>
+        <f t="shared" ref="AA17" si="48">AA15/AA16</f>
+        <v>7.1221429447650459</v>
       </c>
       <c r="AB17" s="5">
-        <f t="shared" ref="AB17" si="53">AB15/AB16</f>
-        <v>7.9401157635654149</v>
+        <f t="shared" ref="AB17" si="49">AB15/AB16</f>
+        <v>7.3284678625803812</v>
       </c>
       <c r="AC17" s="5">
-        <f t="shared" ref="AC17" si="54">AC15/AC16</f>
-        <v>8.1711111042132103</v>
+        <f t="shared" ref="AC17" si="50">AC15/AC16</f>
+        <v>7.5384485132095627</v>
       </c>
       <c r="AD17" s="5">
-        <f t="shared" ref="AD17" si="55">AD15/AD16</f>
-        <v>8.4063161774975441</v>
+        <f t="shared" ref="AD17" si="51">AD15/AD16</f>
+        <v>7.7521696830510365</v>
       </c>
       <c r="AE17" s="5">
-        <f t="shared" ref="AE17" si="56">AE15/AE16</f>
-        <v>8.5485424418507918</v>
+        <f t="shared" ref="AE17" si="52">AE15/AE16</f>
+        <v>7.8855116849829585</v>
       </c>
       <c r="AF17" s="5">
-        <f t="shared" ref="AF17" si="57">AF15/AF16</f>
-        <v>8.6922540550221186</v>
+        <f t="shared" ref="AF17" si="53">AF15/AF16</f>
+        <v>8.0202430249648877</v>
       </c>
       <c r="AG17" s="5">
-        <f t="shared" ref="AG17" si="58">AG15/AG16</f>
-        <v>8.8374830826434536</v>
+        <f t="shared" ref="AG17" si="54">AG15/AG16</f>
+        <v>8.1563950632252631</v>
       </c>
       <c r="AH17" s="5">
-        <f t="shared" ref="AH17" si="59">AH15/AH16</f>
-        <v>8.9842622522097493</v>
+        <f t="shared" ref="AH17" si="55">AH15/AH16</f>
+        <v>8.2939998219979891</v>
       </c>
       <c r="AI17" s="5">
-        <f t="shared" ref="AI17" si="60">AI15/AI16</f>
-        <v>9.1326249712862122</v>
+        <f t="shared" ref="AI17" si="56">AI15/AI16</f>
+        <v>8.4330900039476724</v>
       </c>
       <c r="AJ17" s="5">
-        <f t="shared" ref="AJ17" si="61">AJ15/AJ16</f>
-        <v>9.2826053462239084</v>
+        <f t="shared" ref="AJ17" si="57">AJ15/AJ16</f>
+        <v>8.5736990111113691</v>
       </c>
     </row>
     <row r="19" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3399,111 +3383,111 @@
         <v>6.311737698835973E-2</v>
       </c>
       <c r="H19" s="8">
-        <f t="shared" ref="H19:N19" si="62">H3/D3-1</f>
+        <f t="shared" ref="H19:N19" si="58">H3/D3-1</f>
         <v>7.5233460476127778E-2</v>
       </c>
       <c r="I19" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>8.3267699308654741E-2</v>
       </c>
       <c r="J19" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>8.0248557478917126E-2</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>5.5749432908741792E-2</v>
       </c>
       <c r="L19" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>4.7420998980632012E-2</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>5.0854303833259396E-2</v>
       </c>
       <c r="N19" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="58"/>
         <v>3.3527816583120984E-2</v>
       </c>
       <c r="O19" s="8">
-        <f t="shared" ref="O19" si="63">O3/K3-1</f>
+        <f t="shared" ref="O19" si="59">O3/K3-1</f>
         <v>-3.346830840426418E-3</v>
       </c>
       <c r="P19" s="8">
-        <f t="shared" ref="P19" si="64">P3/L3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="P19" si="60">P3/L3-1</f>
+        <v>-0.238282466521333</v>
       </c>
       <c r="Q19" s="8">
-        <f t="shared" ref="Q19" si="65">Q3/M3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="Q19" si="61">Q3/M3-1</f>
+        <v>-0.24238929889298888</v>
       </c>
       <c r="R19" s="8">
-        <f t="shared" ref="R19" si="66">R3/N3-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="R19" si="62">R3/N3-1</f>
+        <v>-0.20489782937107426</v>
       </c>
       <c r="U19" s="8">
         <f>U3/T3-1</f>
         <v>0.51134998676683185</v>
       </c>
       <c r="V19" s="8">
-        <f t="shared" ref="V19:AJ19" si="67">V3/U3-1</f>
+        <f t="shared" ref="V19:AJ19" si="63">V3/U3-1</f>
         <v>0.14820302818039743</v>
       </c>
       <c r="W19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>5.3004528496680026E-2</v>
       </c>
       <c r="X19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>7.562725611658272E-2</v>
       </c>
       <c r="Y19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>4.6776599270798913E-2</v>
       </c>
       <c r="Z19" s="8">
-        <f t="shared" si="67"/>
-        <v>6.8036809815950061E-3</v>
+        <f t="shared" si="63"/>
+        <v>-0.17476746487235317</v>
       </c>
       <c r="AA19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ19" s="8">
-        <f t="shared" si="67"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -3512,19 +3496,19 @@
         <v>37</v>
       </c>
       <c r="C20" s="9">
-        <f t="shared" ref="C20:F20" si="68">C5/C3</f>
+        <f t="shared" ref="C20:F20" si="64">C5/C3</f>
         <v>0.55609145295181561</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>0.57810513393835772</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>0.59254397479653453</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="64"/>
         <v>0.58814913448735018</v>
       </c>
       <c r="G20" s="9">
@@ -3532,116 +3516,116 @@
         <v>0.58654685046239752</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" ref="H20:N20" si="69">H5/H3</f>
+        <f t="shared" ref="H20:N20" si="65">H5/H3</f>
         <v>0.61590214067278293</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>0.63020559841660939</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>0.62104527898759143</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>0.61887447318403432</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>0.63465431329803801</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>0.63603167281672812</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>0.621412101455037</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" ref="O20:R20" si="70">O5/O3</f>
+        <f t="shared" ref="O20:R20" si="66">O5/O3</f>
         <v>0.61809211890054305</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="70"/>
-        <v>0.63</v>
+        <f t="shared" si="66"/>
+        <v>0.74508100373077124</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="66"/>
+        <v>0.75</v>
+      </c>
+      <c r="R20" s="9">
+        <f t="shared" si="66"/>
+        <v>0.72</v>
+      </c>
+      <c r="T20" s="9">
+        <f t="shared" ref="T20:AJ20" si="67">T5/T3</f>
+        <v>0.57780085099452339</v>
+      </c>
+      <c r="U20" s="9">
+        <f t="shared" si="67"/>
+        <v>0.50823050810927317</v>
+      </c>
+      <c r="V20" s="9">
+        <f t="shared" si="67"/>
+        <v>0.55727492432952441</v>
+      </c>
+      <c r="W20" s="9">
+        <f t="shared" si="67"/>
+        <v>0.57901421631980032</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" si="67"/>
+        <v>0.6138962545575074</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" si="67"/>
+        <v>0.6279339006530773</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" si="67"/>
         <v>0.64</v>
       </c>
-      <c r="R20" s="9">
-        <f t="shared" si="70"/>
-        <v>0.62</v>
-      </c>
-      <c r="T20" s="9">
-        <f t="shared" ref="T20:AJ20" si="71">T5/T3</f>
-        <v>0.57780085099452339</v>
-      </c>
-      <c r="U20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.50823050810927317</v>
-      </c>
-      <c r="V20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.55727492432952441</v>
-      </c>
-      <c r="W20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.57901421631980032</v>
-      </c>
-      <c r="X20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.6138962545575074</v>
-      </c>
-      <c r="Y20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.6279339006530773</v>
-      </c>
-      <c r="Z20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.64</v>
-      </c>
       <c r="AA20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.65</v>
+        <f t="shared" si="67"/>
+        <v>0.75</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.65</v>
+        <f t="shared" si="67"/>
+        <v>0.75</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.65</v>
+        <f t="shared" si="67"/>
+        <v>0.75</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.65</v>
+        <f t="shared" si="67"/>
+        <v>0.75</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.65</v>
+        <f t="shared" si="67"/>
+        <v>0.75</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.65</v>
+        <f t="shared" si="67"/>
+        <v>0.75</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.65</v>
+        <f t="shared" si="67"/>
+        <v>0.75</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.65</v>
+        <f t="shared" si="67"/>
+        <v>0.75</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.65</v>
+        <f t="shared" si="67"/>
+        <v>0.75</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" si="71"/>
-        <v>0.65</v>
+        <f t="shared" si="67"/>
+        <v>0.75</v>
       </c>
       <c r="AM20" t="s">
         <v>40</v>
@@ -3655,19 +3639,19 @@
         <v>38</v>
       </c>
       <c r="C21" s="9">
-        <f t="shared" ref="C21:F21" si="72">C6/C3</f>
+        <f t="shared" ref="C21:F21" si="68">C6/C3</f>
         <v>0.38171868478412091</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="68"/>
         <v>0.37844710421324917</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="68"/>
         <v>0.40203027916338491</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="68"/>
         <v>0.40812250332889483</v>
       </c>
       <c r="G21" s="9">
@@ -3675,116 +3659,116 @@
         <v>0.45502530099459076</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" ref="H21:N21" si="73">H6/H3</f>
+        <f t="shared" ref="H21:N21" si="69">H6/H3</f>
         <v>0.4132517838939857</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="69"/>
         <v>0.4047340146221271</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="69"/>
         <v>0.41712548278412359</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="69"/>
         <v>0.43198909181059419</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="69"/>
         <v>0.41174867642478979</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="69"/>
         <v>0.45318265682656828</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="69"/>
         <v>0.39878349367893773</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" ref="O21:R21" si="74">O6/O3</f>
+        <f t="shared" ref="O21:R21" si="70">O6/O3</f>
         <v>0.42452634633721653</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="74"/>
-        <v>0.42</v>
+        <f t="shared" si="70"/>
+        <v>0.52690754842336585</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="74"/>
-        <v>0.42</v>
+        <f t="shared" si="70"/>
+        <v>0.53</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="74"/>
-        <v>0.39</v>
+        <f t="shared" si="70"/>
+        <v>0.53</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" ref="T21:AJ21" si="75">T6/T3</f>
+        <f t="shared" ref="T21:AJ21" si="71">T6/T3</f>
         <v>0.41668193570716022</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>0.387803760978501</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>0.39785072385555742</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>0.39268683987699987</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>0.42196304275770635</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="71"/>
         <v>0.42403522659806059</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="75"/>
-        <v>0.41358229257147933</v>
+        <f t="shared" si="71"/>
+        <v>0.49876855560085381</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="75"/>
-        <v>0.4</v>
+        <f t="shared" si="71"/>
+        <v>0.47999999999999993</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="75"/>
-        <v>0.38999999999999996</v>
+        <f t="shared" si="71"/>
+        <v>0.48</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="75"/>
-        <v>0.39</v>
+        <f t="shared" si="71"/>
+        <v>0.47999999999999993</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="75"/>
-        <v>0.39</v>
+        <f t="shared" si="71"/>
+        <v>0.48</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="75"/>
-        <v>0.39</v>
+        <f t="shared" si="71"/>
+        <v>0.47999999999999993</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="75"/>
-        <v>0.38999999999999996</v>
+        <f t="shared" si="71"/>
+        <v>0.48</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="75"/>
-        <v>0.39</v>
+        <f t="shared" si="71"/>
+        <v>0.48</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="75"/>
-        <v>0.39000000000000007</v>
+        <f t="shared" si="71"/>
+        <v>0.48000000000000004</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="75"/>
-        <v>0.39</v>
+        <f t="shared" si="71"/>
+        <v>0.47999999999999993</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="75"/>
-        <v>0.39</v>
+        <f t="shared" si="71"/>
+        <v>0.48</v>
       </c>
       <c r="AM21" t="s">
         <v>41</v>
@@ -3798,19 +3782,19 @@
         <v>39</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:F22" si="76">C7/C3</f>
+        <f t="shared" ref="C22:F22" si="72">C7/C3</f>
         <v>0.1743727681676947</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.19965802972510854</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.1905136956331496</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="72"/>
         <v>0.18002663115845535</v>
       </c>
       <c r="G22" s="9">
@@ -3818,123 +3802,123 @@
         <v>0.13152154946780675</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22:N22" si="77">H7/H3</f>
+        <f t="shared" ref="H22:N22" si="73">H7/H3</f>
         <v>0.20265035677879714</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="73"/>
         <v>0.22547158379448232</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="73"/>
         <v>0.2039197962034679</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="73"/>
         <v>0.1868853813734401</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="73"/>
         <v>0.22290563687324824</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="73"/>
         <v>0.18284901599015985</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="73"/>
         <v>0.22262860777609927</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22:R22" si="78">O7/O3</f>
+        <f t="shared" ref="O22:R22" si="74">O7/O3</f>
         <v>0.19356577256332652</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="78"/>
-        <v>0.21000000000000008</v>
+        <f t="shared" si="74"/>
+        <v>0.21817345530740537</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="78"/>
-        <v>0.22000000000000003</v>
+        <f t="shared" si="74"/>
+        <v>0.21999999999999995</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="78"/>
-        <v>0.22999999999999993</v>
+        <f t="shared" si="74"/>
+        <v>0.19</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22:AJ22" si="79">T7/T3</f>
+        <f t="shared" ref="T22:AJ22" si="75">T7/T3</f>
         <v>0.16111891528736325</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.12042674713077219</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.15942420047396699</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.18632737644280042</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.19193321179980105</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="75"/>
         <v>0.20389867405501677</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" si="79"/>
-        <v>0.22641770742852069</v>
+        <f t="shared" si="75"/>
+        <v>0.14123144439914623</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="79"/>
-        <v>0.25</v>
+        <f t="shared" si="75"/>
+        <v>0.27000000000000007</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="79"/>
-        <v>0.26000000000000006</v>
+        <f t="shared" si="75"/>
+        <v>0.27000000000000007</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="79"/>
-        <v>0.26</v>
+        <f t="shared" si="75"/>
+        <v>0.27</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="79"/>
-        <v>0.26</v>
+        <f t="shared" si="75"/>
+        <v>0.27</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="79"/>
-        <v>0.26000000000000006</v>
+        <f t="shared" si="75"/>
+        <v>0.27000000000000013</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="79"/>
-        <v>0.26000000000000006</v>
+        <f t="shared" si="75"/>
+        <v>0.26999999999999996</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="79"/>
-        <v>0.26</v>
+        <f t="shared" si="75"/>
+        <v>0.27</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="79"/>
-        <v>0.26</v>
+        <f t="shared" si="75"/>
+        <v>0.26999999999999996</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="79"/>
-        <v>0.25999999999999995</v>
+        <f t="shared" si="75"/>
+        <v>0.27000000000000007</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="79"/>
-        <v>0.26</v>
+        <f t="shared" si="75"/>
+        <v>0.27</v>
       </c>
       <c r="AM22" t="s">
         <v>42</v>
       </c>
       <c r="AN22" s="1">
         <f>NPV(AN21,Z15:EN15)</f>
-        <v>25166.162395609612</v>
+        <v>22163.088080340272</v>
       </c>
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.3">
@@ -3942,19 +3926,19 @@
         <v>18</v>
       </c>
       <c r="C23" s="9">
-        <f t="shared" ref="C23:F23" si="80">C12/C11</f>
+        <f t="shared" ref="C23:F23" si="76">C12/C11</f>
         <v>0.18354430379746831</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="76"/>
         <v>-8.4331576425491148E-2</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="76"/>
         <v>5.2631578947368404E-2</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="76"/>
         <v>0.16100543478260873</v>
       </c>
       <c r="G23" s="9">
@@ -3962,115 +3946,115 @@
         <v>0.57090909090909314</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ref="H23:N23" si="81">H12/H11</f>
+        <f t="shared" ref="H23:N23" si="77">H12/H11</f>
         <v>0.39207650273224037</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>0.14097654380086172</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>2.5278608317477566E-2</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>5.9490953695185582E-2</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>0.17338979273456648</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>0.15302585977072788</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="77"/>
         <v>0.19543747391848657</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" ref="O23:R23" si="82">O12/O11</f>
+        <f t="shared" ref="O23:R23" si="78">O12/O11</f>
         <v>0.1661947904869763</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="78"/>
+        <v>0.38099838969404171</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" si="78"/>
         <v>0.16</v>
       </c>
-      <c r="Q23" s="9">
-        <f t="shared" si="82"/>
+      <c r="R23" s="9">
+        <f t="shared" si="78"/>
         <v>0.16</v>
       </c>
-      <c r="R23" s="9">
-        <f t="shared" si="82"/>
-        <v>0.16</v>
-      </c>
       <c r="T23" s="9">
-        <f t="shared" ref="T23:AJ23" si="83">T12/T11</f>
+        <f t="shared" ref="T23:AJ23" si="79">T12/T11</f>
         <v>0.12010040548368425</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.12994445379565719</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.16179990426041174</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.74286987522281789</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.17864774767074121</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.15790881849315075</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="83"/>
-        <v>0.15001398204512492</v>
+        <f t="shared" si="79"/>
+        <v>0.37103168314682372</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.17</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.17</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.17</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.17</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.17</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.17</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.17</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.17</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.17</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="79"/>
         <v>0.17</v>
       </c>
       <c r="AM23" t="s">
@@ -4078,7 +4062,7 @@
       </c>
       <c r="AN23" s="1">
         <f>Main!D8</f>
-        <v>-14026.8</v>
+        <v>-14035.5</v>
       </c>
     </row>
     <row r="24" spans="1:40" x14ac:dyDescent="0.3">
@@ -4090,139 +4074,139 @@
         <v>2.2724110745258081E-3</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" ref="D24:N24" si="84">D14/D3</f>
+        <f t="shared" ref="D24:N24" si="80">D14/D3</f>
         <v>3.4635450918497086E-3</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>4.2443335958694314E-3</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>4.1278295605858854E-3</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>2.879078694817658E-3</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>4.1182466870540264E-3</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>5.9781072020034746E-3</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>4.5607691675569068E-3</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>4.0492521279233131E-3</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>5.6446589847399557E-3</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>7.0725707257072567E-3</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="80"/>
         <v>1.2363838753279796E-2</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" ref="O24:R24" si="85">O14/O3</f>
+        <f t="shared" ref="O24:R24" si="81">O14/O3</f>
         <v>2.9020355706645662E-3</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="85"/>
-        <v>7.3347560674784434E-3</v>
+        <f t="shared" si="81"/>
+        <v>-1.5076404149844125E-2</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="85"/>
-        <v>8.2133151876073208E-3</v>
+        <f t="shared" si="81"/>
+        <v>-1.5220700152207001E-2</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="85"/>
-        <v>8.362531912330929E-3</v>
+        <f t="shared" si="81"/>
+        <v>-1.4999999999999999E-2</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" ref="T24:AJ24" si="86">T14/T3</f>
+        <f t="shared" ref="T24:AJ24" si="82">T14/T3</f>
         <v>7.8788248946436226E-3</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>2.7749339942884856E-3</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>2.6279358971350807E-3</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>3.5429386336289495E-3</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>4.412495856811402E-3</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>7.3025925192954696E-3</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="86"/>
-        <v>6.7674178491517935E-3</v>
+        <f t="shared" si="82"/>
+        <v>-9.8923235569198312E-3</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="86"/>
-        <v>6.6031601343665546E-3</v>
+        <f t="shared" si="82"/>
+        <v>-9.6522186162178933E-3</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="86"/>
-        <v>6.5060548382729283E-3</v>
+        <f t="shared" si="82"/>
+        <v>-9.5102742248029219E-3</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="86"/>
-        <v>6.410377561239502E-3</v>
+        <f t="shared" si="82"/>
+        <v>-9.3704172509087615E-3</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="86"/>
-        <v>6.3161073029859788E-3</v>
+        <f t="shared" si="82"/>
+        <v>-9.2326169972189245E-3</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="86"/>
-        <v>6.2848394450504049E-3</v>
+        <f t="shared" si="82"/>
+        <v>-9.1869109724802157E-3</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="86"/>
-        <v>6.2537263784907485E-3</v>
+        <f t="shared" si="82"/>
+        <v>-9.1414312151907092E-3</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="86"/>
-        <v>6.2227673370130717E-3</v>
+        <f t="shared" si="82"/>
+        <v>-9.0961766052145166E-3</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="86"/>
-        <v>6.1919615581169669E-3</v>
+        <f t="shared" si="82"/>
+        <v>-9.0511460279609785E-3</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="86"/>
-        <v>6.1613082830767833E-3</v>
+        <f t="shared" si="82"/>
+        <v>-9.0063383743572093E-3</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="86"/>
-        <v>6.1308067569229366E-3</v>
+        <f t="shared" si="82"/>
+        <v>-8.9617525408207874E-3</v>
       </c>
       <c r="AM24" t="s">
         <v>44</v>
       </c>
       <c r="AN24" s="1">
         <f>AN22+AN23</f>
-        <v>11139.362395609613</v>
+        <v>8127.5880803402724</v>
       </c>
     </row>
     <row r="25" spans="1:40" x14ac:dyDescent="0.3">
@@ -4234,139 +4218,139 @@
         <v>0.11352780225386082</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" ref="D25:N25" si="87">D15/D3</f>
+        <f t="shared" ref="D25:N25" si="83">D15/D3</f>
         <v>-0.29505896795124725</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.1271112277938217</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.11065246338215708</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>-4.7984644913626716E-3</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.11176350662589196</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.14614048551924702</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.14845098200345144</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.1294521113957523</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.14586577390221117</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.12115621156211556</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="87"/>
+        <f t="shared" si="83"/>
         <v>0.22549097559036338</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" ref="O25:R25" si="88">O15/O3</f>
+        <f t="shared" ref="O25:R25" si="84">O15/O3</f>
         <v>0.12677749678703198</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="88"/>
-        <v>0.13610047369654446</v>
+        <f t="shared" si="84"/>
+        <v>0.12352430111923141</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="88"/>
-        <v>0.15240262625893586</v>
+        <f t="shared" si="84"/>
+        <v>0.16819425672247587</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="88"/>
-        <v>0.15517142548436277</v>
+        <f t="shared" si="84"/>
+        <v>0.13747347999999998</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" ref="T25:AJ25" si="89">T15/T3</f>
+        <f t="shared" ref="T25:AJ25" si="85">T15/T3</f>
         <v>8.7644292432663418E-2</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="85"/>
         <v>7.8748855002963566E-2</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="85"/>
         <v>0.11327107628053211</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="85"/>
         <v>1.2433709167075127E-2</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="85"/>
         <v>0.10215031488233337</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="85"/>
         <v>0.15539283593904604</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="89"/>
-        <v>0.15559957010279754</v>
+        <f t="shared" si="85"/>
+        <v>7.4867483632700987E-2</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="89"/>
-        <v>0.17327015317476976</v>
+        <f t="shared" si="85"/>
+        <v>0.20114471306964829</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="89"/>
-        <v>0.18324599803149871</v>
+        <f t="shared" si="85"/>
+        <v>0.20291350467856481</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="89"/>
-        <v>0.18487943633242393</v>
+        <f t="shared" si="85"/>
+        <v>0.20463483494048068</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="89"/>
-        <v>0.18647174780910006</v>
+        <f t="shared" si="85"/>
+        <v>0.20631019566441974</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="89"/>
-        <v>0.18774916722257701</v>
+        <f t="shared" si="85"/>
+        <v>0.20778104521758489</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="89"/>
-        <v>0.18901531074425762</v>
+        <f t="shared" si="85"/>
+        <v>0.20923879074011997</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="89"/>
-        <v>0.19027064701095384</v>
+        <f t="shared" si="85"/>
+        <v>0.21068399870890051</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="89"/>
-        <v>0.19151564008926739</v>
+        <f t="shared" si="85"/>
+        <v>0.21211723011124808</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="89"/>
-        <v>0.19275074965703357</v>
+        <f t="shared" si="85"/>
+        <v>0.21353904066481519</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="89"/>
-        <v>0.19397643118295341</v>
+        <f t="shared" si="85"/>
+        <v>0.21494998103528717</v>
       </c>
       <c r="AM25" t="s">
         <v>45</v>
       </c>
       <c r="AN25" s="11">
         <f>AN24/AJ16</f>
-        <v>45.153475458490526</v>
+        <v>33.502011872795848</v>
       </c>
     </row>
     <row r="26" spans="1:40" x14ac:dyDescent="0.3">
@@ -4375,7 +4359,7 @@
       </c>
       <c r="AN26" s="11">
         <f>Main!D3</f>
-        <v>75</v>
+        <v>82.74</v>
       </c>
     </row>
     <row r="27" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4399,7 +4383,7 @@
       </c>
       <c r="AN27" s="8">
         <f>AN25/AN26-1</f>
-        <v>-0.39795366055345971</v>
+        <v>-0.59509291911051676</v>
       </c>
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.3">
@@ -5155,7 +5139,7 @@
     </row>
     <row r="71" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B71" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="O71" s="7">
         <f>O69-O70</f>

--- a/Financial Analysis/GPN.xlsx
+++ b/Financial Analysis/GPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECA56C7-CBFB-47C4-AA1D-EEE2F37576D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA139F9-34A0-4434-9566-D717CA51358C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AC685D6A-8DC8-48D8-9A0E-762C4546B5AC}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="89">
   <si>
     <t>Price</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>Heavily overvalued</t>
+  </si>
+  <si>
+    <t>GPN</t>
   </si>
 </sst>
 </file>
@@ -406,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -425,6 +428,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,14 +450,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>54</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
@@ -470,7 +474,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10462260" y="15240"/>
+          <a:off x="11064240" y="15240"/>
           <a:ext cx="0" cy="10012680"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -844,7 +848,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0BE2981-9185-411C-AB0F-A5F42B1AF254}">
-  <dimension ref="C2:I12"/>
+  <dimension ref="B2:I12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="11.88671875" style="13" bestFit="1" customWidth="1"/>
@@ -852,7 +856,7 @@
     <col min="8" max="8" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
@@ -863,88 +867,90 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="6" t="s">
+        <v>88</v>
+      </c>
       <c r="C3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>82.74</v>
+        <v>80.349999999999994</v>
       </c>
       <c r="E3" s="3">
-        <v>45875</v>
+        <v>45965</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45875</v>
+        <v>45965</v>
       </c>
       <c r="G3" s="3">
-        <v>45965</v>
-      </c>
-    </row>
-    <row r="4" spans="3:9" x14ac:dyDescent="0.3">
+        <v>46071</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <f>242.6</f>
-        <v>242.6</v>
+        <v>236.7</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>20072.723999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
+        <v>19018.844999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1">
-        <f>2611.7</f>
-        <v>2611.6999999999998</v>
+        <f>2603</f>
+        <v>2603</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="1">
-        <f>627.9+1868.3+14151</f>
-        <v>16647.2</v>
+      <c r="D7" s="14">
+        <f>973.2+1903.4+13322.8</f>
+        <v>16199.4</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
         <v>5</v>
       </c>
       <c r="D8" s="1">
         <f>D6-D7</f>
-        <v>-14035.5</v>
-      </c>
-    </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.3">
+        <v>-13596.4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>34108.224000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
+        <v>32615.244999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="I12" t="s">
         <v>49</v>
       </c>
@@ -1114,10 +1120,10 @@
         <v>1956.7</v>
       </c>
       <c r="Q3" s="7">
-        <v>1971</v>
+        <v>2007.6</v>
       </c>
       <c r="R3" s="7">
-        <v>2000</v>
+        <v>2050</v>
       </c>
       <c r="T3" s="7">
         <v>4911.8999999999996</v>
@@ -1142,47 +1148,47 @@
       </c>
       <c r="Z3" s="7">
         <f>SUM(O3:R3)</f>
-        <v>8339.7999999999993</v>
+        <v>8426.4</v>
       </c>
       <c r="AA3" s="7">
-        <f>Z3*1.03</f>
-        <v>8589.9939999999988</v>
+        <f>Z3*1.04</f>
+        <v>8763.4560000000001</v>
       </c>
       <c r="AB3" s="7">
-        <f>AA3*1.02</f>
-        <v>8761.7938799999993</v>
+        <f>AA3*1.03</f>
+        <v>9026.3596799999996</v>
       </c>
       <c r="AC3" s="7">
         <f t="shared" ref="AC3:AD3" si="0">AB3*1.02</f>
-        <v>8937.0297575999994</v>
+        <v>9206.8868736000004</v>
       </c>
       <c r="AD3" s="7">
         <f t="shared" si="0"/>
-        <v>9115.7703527519989</v>
+        <v>9391.024611072</v>
       </c>
       <c r="AE3" s="7">
-        <f>AD3*1.01</f>
-        <v>9206.9280562795193</v>
+        <f t="shared" ref="AE3" si="1">AD3*1.02</f>
+        <v>9578.8451032934408</v>
       </c>
       <c r="AF3" s="7">
-        <f t="shared" ref="AF3:AJ3" si="1">AE3*1.01</f>
-        <v>9298.9973368423143</v>
+        <f t="shared" ref="AF3" si="2">AE3*1.02</f>
+        <v>9770.422005359309</v>
       </c>
       <c r="AG3" s="7">
-        <f t="shared" si="1"/>
-        <v>9391.9873102107376</v>
+        <f t="shared" ref="AG3" si="3">AF3*1.02</f>
+        <v>9965.8304454664958</v>
       </c>
       <c r="AH3" s="7">
-        <f t="shared" si="1"/>
-        <v>9485.9071833128455</v>
+        <f t="shared" ref="AH3" si="4">AG3*1.02</f>
+        <v>10165.147054375826</v>
       </c>
       <c r="AI3" s="7">
-        <f t="shared" si="1"/>
-        <v>9580.7662551459744</v>
+        <f t="shared" ref="AI3" si="5">AH3*1.02</f>
+        <v>10368.449995463343</v>
       </c>
       <c r="AJ3" s="7">
-        <f t="shared" si="1"/>
-        <v>9676.5739176974348</v>
+        <f t="shared" ref="AJ3" si="6">AI3*1.02</f>
+        <v>10575.818995372611</v>
       </c>
     </row>
     <row r="4" spans="1:144" x14ac:dyDescent="0.3">
@@ -1232,12 +1238,11 @@
         <v>498.8</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" ref="P4:R4" si="2">Q3-Q5</f>
-        <v>492.75</v>
+        <v>556.70000000000005</v>
       </c>
       <c r="R4" s="1">
-        <f t="shared" si="2"/>
-        <v>560</v>
+        <f t="shared" ref="Q4:R4" si="7">R3-R5</f>
+        <v>553.5</v>
       </c>
       <c r="T4" s="1">
         <v>2073.8000000000002</v>
@@ -1262,47 +1267,47 @@
       </c>
       <c r="Z4" s="1">
         <f>SUM(O4:R4)</f>
-        <v>2472.75</v>
+        <v>2530.1999999999998</v>
       </c>
       <c r="AA4" s="1">
-        <f t="shared" ref="AA4:AJ4" si="3">AA3-AA5</f>
-        <v>2147.4984999999997</v>
+        <f t="shared" ref="AA4:AJ4" si="8">AA3-AA5</f>
+        <v>2366.1331200000004</v>
       </c>
       <c r="AB4" s="1">
-        <f t="shared" si="3"/>
-        <v>2190.4484699999994</v>
+        <f t="shared" si="8"/>
+        <v>2437.1171136000003</v>
       </c>
       <c r="AC4" s="1">
-        <f t="shared" si="3"/>
-        <v>2234.2574394000003</v>
+        <f t="shared" si="8"/>
+        <v>2485.8594558720006</v>
       </c>
       <c r="AD4" s="1">
-        <f t="shared" si="3"/>
-        <v>2278.9425881879997</v>
+        <f t="shared" si="8"/>
+        <v>2535.57664498944</v>
       </c>
       <c r="AE4" s="1">
-        <f t="shared" si="3"/>
-        <v>2301.7320140698794</v>
+        <f t="shared" si="8"/>
+        <v>2586.2881778892288</v>
       </c>
       <c r="AF4" s="1">
-        <f t="shared" si="3"/>
-        <v>2324.749334210579</v>
+        <f t="shared" si="8"/>
+        <v>2638.0139414470132</v>
       </c>
       <c r="AG4" s="1">
-        <f t="shared" si="3"/>
-        <v>2347.9968275526844</v>
+        <f t="shared" si="8"/>
+        <v>2690.7742202759537</v>
       </c>
       <c r="AH4" s="1">
-        <f t="shared" si="3"/>
-        <v>2371.4767958282118</v>
+        <f t="shared" si="8"/>
+        <v>2744.5897046814734</v>
       </c>
       <c r="AI4" s="1">
-        <f t="shared" si="3"/>
-        <v>2395.1915637864931</v>
+        <f t="shared" si="8"/>
+        <v>2799.4814987751024</v>
       </c>
       <c r="AJ4" s="1">
-        <f t="shared" si="3"/>
-        <v>2419.1434794243587</v>
+        <f t="shared" si="8"/>
+        <v>2855.4711287506052</v>
       </c>
     </row>
     <row r="5" spans="1:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1311,136 +1316,136 @@
         <v>33</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:P5" si="4">C3-C4</f>
+        <f t="shared" ref="C5:Q5" si="9">C3-C4</f>
         <v>1199.1000000000001</v>
       </c>
       <c r="D5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1318.6000000000001</v>
       </c>
       <c r="E5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1354.2</v>
       </c>
       <c r="F5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1325.1</v>
       </c>
       <c r="G5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1344.6000000000001</v>
       </c>
       <c r="H5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1510.5</v>
       </c>
       <c r="I5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1560.1999999999998</v>
       </c>
       <c r="J5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1511.5000000000002</v>
       </c>
       <c r="K5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1497.7999999999997</v>
       </c>
       <c r="L5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1630.3000000000002</v>
       </c>
       <c r="M5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1654.6999999999998</v>
       </c>
       <c r="N5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1563.1000000000001</v>
       </c>
       <c r="O5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1490.8999999999999</v>
       </c>
       <c r="P5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>1457.9</v>
       </c>
       <c r="Q5" s="7">
-        <f>Q3*0.75</f>
-        <v>1478.25</v>
+        <f t="shared" si="9"/>
+        <v>1450.8999999999999</v>
       </c>
       <c r="R5" s="7">
-        <f>R3*0.72</f>
-        <v>1440</v>
+        <f>R3*0.73</f>
+        <v>1496.5</v>
       </c>
       <c r="T5" s="7">
-        <f t="shared" ref="T5:Y5" si="5">T3-T4</f>
+        <f t="shared" ref="T5:Y5" si="10">T3-T4</f>
         <v>2838.0999999999995</v>
       </c>
       <c r="U5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>3772.9000000000005</v>
       </c>
       <c r="V5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>4750.0999999999995</v>
       </c>
       <c r="W5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5197</v>
       </c>
       <c r="X5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>5926.7999999999993</v>
       </c>
       <c r="Y5" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>6345.9</v>
       </c>
       <c r="Z5" s="7">
         <f>Z3*0.64</f>
-        <v>5337.4719999999998</v>
+        <v>5392.8959999999997</v>
       </c>
       <c r="AA5" s="7">
-        <f>AA3*0.75</f>
-        <v>6442.4954999999991</v>
+        <f>AA3*0.73</f>
+        <v>6397.3228799999997</v>
       </c>
       <c r="AB5" s="7">
-        <f t="shared" ref="AB5:AJ5" si="6">AB3*0.75</f>
-        <v>6571.3454099999999</v>
+        <f t="shared" ref="AB5:AJ5" si="11">AB3*0.73</f>
+        <v>6589.2425663999993</v>
       </c>
       <c r="AC5" s="7">
-        <f t="shared" si="6"/>
-        <v>6702.7723181999991</v>
+        <f t="shared" si="11"/>
+        <v>6721.0274177279998</v>
       </c>
       <c r="AD5" s="7">
-        <f t="shared" si="6"/>
-        <v>6836.8277645639992</v>
+        <f t="shared" si="11"/>
+        <v>6855.44796608256</v>
       </c>
       <c r="AE5" s="7">
-        <f t="shared" si="6"/>
-        <v>6905.1960422096399</v>
+        <f t="shared" si="11"/>
+        <v>6992.5569254042121</v>
       </c>
       <c r="AF5" s="7">
-        <f t="shared" si="6"/>
-        <v>6974.2480026317353</v>
+        <f t="shared" si="11"/>
+        <v>7132.4080639122958</v>
       </c>
       <c r="AG5" s="7">
-        <f t="shared" si="6"/>
-        <v>7043.9904826580532</v>
+        <f t="shared" si="11"/>
+        <v>7275.0562251905421</v>
       </c>
       <c r="AH5" s="7">
-        <f t="shared" si="6"/>
-        <v>7114.4303874846337</v>
+        <f t="shared" si="11"/>
+        <v>7420.5573496943525</v>
       </c>
       <c r="AI5" s="7">
-        <f t="shared" si="6"/>
-        <v>7185.5746913594812</v>
+        <f t="shared" si="11"/>
+        <v>7568.9684966882405</v>
       </c>
       <c r="AJ5" s="7">
-        <f t="shared" si="6"/>
-        <v>7257.4304382730761</v>
+        <f t="shared" si="11"/>
+        <v>7720.3478666220053</v>
       </c>
     </row>
     <row r="6" spans="1:144" x14ac:dyDescent="0.3">
@@ -1490,12 +1495,11 @@
         <v>1031</v>
       </c>
       <c r="Q6" s="1">
-        <f>Q3*0.53</f>
-        <v>1044.6300000000001</v>
+        <v>1016.8</v>
       </c>
       <c r="R6" s="1">
         <f>R3*0.53</f>
-        <v>1060</v>
+        <v>1086.5</v>
       </c>
       <c r="T6" s="1">
         <v>2046.7</v>
@@ -1520,47 +1524,47 @@
       </c>
       <c r="Z6" s="1">
         <f>SUM(O6:R6)</f>
-        <v>4159.63</v>
+        <v>4158.3</v>
       </c>
       <c r="AA6" s="1">
-        <f>AA3*0.48</f>
-        <v>4123.1971199999989</v>
+        <f>AA3*0.49</f>
+        <v>4294.0934399999996</v>
       </c>
       <c r="AB6" s="1">
-        <f t="shared" ref="AB6:AJ6" si="7">AB3*0.48</f>
-        <v>4205.6610623999995</v>
+        <f>AB3*0.48</f>
+        <v>4332.6526463999999</v>
       </c>
       <c r="AC6" s="1">
-        <f t="shared" si="7"/>
-        <v>4289.7742836479993</v>
+        <f t="shared" ref="AC6:AJ6" si="12">AC3*0.48</f>
+        <v>4419.3056993279997</v>
       </c>
       <c r="AD6" s="1">
-        <f t="shared" si="7"/>
-        <v>4375.5697693209595</v>
+        <f t="shared" si="12"/>
+        <v>4507.69181331456</v>
       </c>
       <c r="AE6" s="1">
-        <f t="shared" si="7"/>
-        <v>4419.3254670141687</v>
+        <f t="shared" si="12"/>
+        <v>4597.8456495808514</v>
       </c>
       <c r="AF6" s="1">
-        <f t="shared" si="7"/>
-        <v>4463.5187216843105</v>
+        <f t="shared" si="12"/>
+        <v>4689.8025625724686</v>
       </c>
       <c r="AG6" s="1">
-        <f t="shared" si="7"/>
-        <v>4508.153908901154</v>
+        <f t="shared" si="12"/>
+        <v>4783.5986138239177</v>
       </c>
       <c r="AH6" s="1">
-        <f t="shared" si="7"/>
-        <v>4553.235447990166</v>
+        <f t="shared" si="12"/>
+        <v>4879.270586100396</v>
       </c>
       <c r="AI6" s="1">
-        <f t="shared" si="7"/>
-        <v>4598.7678024700672</v>
+        <f t="shared" si="12"/>
+        <v>4976.8559978224048</v>
       </c>
       <c r="AJ6" s="1">
-        <f t="shared" si="7"/>
-        <v>4644.7554804947686</v>
+        <f t="shared" si="12"/>
+        <v>5076.3931177788527</v>
       </c>
     </row>
     <row r="7" spans="1:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -1569,136 +1573,136 @@
         <v>14</v>
       </c>
       <c r="C7" s="7">
-        <f t="shared" ref="C7:K7" si="8">C5-C6</f>
+        <f t="shared" ref="C7:K7" si="13">C5-C6</f>
         <v>376.00000000000011</v>
       </c>
       <c r="D7" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>455.40000000000009</v>
       </c>
       <c r="E7" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>435.40000000000009</v>
       </c>
       <c r="F7" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>405.59999999999991</v>
       </c>
       <c r="G7" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>301.50000000000023</v>
       </c>
       <c r="H7" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>497</v>
       </c>
       <c r="I7" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>558.19999999999982</v>
       </c>
       <c r="J7" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>496.30000000000018</v>
       </c>
       <c r="K7" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="13"/>
         <v>452.29999999999973</v>
       </c>
       <c r="L7" s="7">
-        <f t="shared" ref="L7:R7" si="9">L5-L6</f>
+        <f t="shared" ref="L7:R7" si="14">L5-L6</f>
         <v>572.60000000000014</v>
       </c>
       <c r="M7" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>475.69999999999982</v>
       </c>
       <c r="N7" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>560.00000000000011</v>
       </c>
       <c r="O7" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>466.89999999999986</v>
       </c>
       <c r="P7" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="14"/>
         <v>426.90000000000009</v>
       </c>
       <c r="Q7" s="7">
-        <f t="shared" si="9"/>
-        <v>433.61999999999989</v>
+        <f t="shared" si="14"/>
+        <v>434.09999999999991</v>
       </c>
       <c r="R7" s="7">
-        <f t="shared" si="9"/>
-        <v>380</v>
+        <f t="shared" si="14"/>
+        <v>410</v>
       </c>
       <c r="T7" s="7">
-        <f t="shared" ref="T7:Y7" si="10">T5-T6</f>
+        <f t="shared" ref="T7:Y7" si="15">T5-T6</f>
         <v>791.39999999999941</v>
       </c>
       <c r="U7" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>894.00000000000045</v>
       </c>
       <c r="V7" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>1358.8999999999996</v>
       </c>
       <c r="W7" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>1672.3999999999996</v>
       </c>
       <c r="X7" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>1852.9999999999991</v>
       </c>
       <c r="Y7" s="7">
-        <f t="shared" si="10"/>
+        <f t="shared" si="15"/>
         <v>2060.5999999999995</v>
       </c>
       <c r="Z7" s="7">
-        <f t="shared" ref="Z7:AJ7" si="11">Z5-Z6</f>
-        <v>1177.8419999999996</v>
+        <f t="shared" ref="Z7:AJ7" si="16">Z5-Z6</f>
+        <v>1234.5959999999995</v>
       </c>
       <c r="AA7" s="7">
-        <f t="shared" si="11"/>
-        <v>2319.2983800000002</v>
+        <f t="shared" si="16"/>
+        <v>2103.2294400000001</v>
       </c>
       <c r="AB7" s="7">
-        <f t="shared" si="11"/>
-        <v>2365.6843476000004</v>
+        <f t="shared" si="16"/>
+        <v>2256.5899199999994</v>
       </c>
       <c r="AC7" s="7">
-        <f t="shared" si="11"/>
-        <v>2412.9980345519998</v>
+        <f t="shared" si="16"/>
+        <v>2301.7217184000001</v>
       </c>
       <c r="AD7" s="7">
-        <f t="shared" si="11"/>
-        <v>2461.2579952430397</v>
+        <f t="shared" si="16"/>
+        <v>2347.756152768</v>
       </c>
       <c r="AE7" s="7">
-        <f t="shared" si="11"/>
-        <v>2485.8705751954712</v>
+        <f t="shared" si="16"/>
+        <v>2394.7112758233607</v>
       </c>
       <c r="AF7" s="7">
-        <f t="shared" si="11"/>
-        <v>2510.7292809474247</v>
+        <f t="shared" si="16"/>
+        <v>2442.6055013398272</v>
       </c>
       <c r="AG7" s="7">
-        <f t="shared" si="11"/>
-        <v>2535.8365737568993</v>
+        <f t="shared" si="16"/>
+        <v>2491.4576113666244</v>
       </c>
       <c r="AH7" s="7">
-        <f t="shared" si="11"/>
-        <v>2561.1949394944677</v>
+        <f t="shared" si="16"/>
+        <v>2541.2867635939565</v>
       </c>
       <c r="AI7" s="7">
-        <f t="shared" si="11"/>
-        <v>2586.806888889414</v>
+        <f t="shared" si="16"/>
+        <v>2592.1124988658357</v>
       </c>
       <c r="AJ7" s="7">
-        <f t="shared" si="11"/>
-        <v>2612.6749577783075</v>
+        <f t="shared" si="16"/>
+        <v>2643.9547488431526</v>
       </c>
     </row>
     <row r="8" spans="1:144" x14ac:dyDescent="0.3">
@@ -1749,7 +1753,7 @@
         <v>-0.3</v>
       </c>
       <c r="Q8" s="1">
-        <v>0</v>
+        <v>-343.9</v>
       </c>
       <c r="R8" s="1">
         <v>0</v>
@@ -1777,7 +1781,7 @@
       </c>
       <c r="Z8" s="1">
         <f>SUM(O8:R8)</f>
-        <v>-4.3</v>
+        <v>-348.2</v>
       </c>
       <c r="AA8" s="1">
         <v>0</v>
@@ -1857,11 +1861,10 @@
         <v>-35.5</v>
       </c>
       <c r="Q9" s="1">
-        <f t="shared" ref="P9:R9" si="12">M9*1.01</f>
-        <v>-55.852999999999994</v>
+        <v>-21.5</v>
       </c>
       <c r="R9" s="1">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="Q9:R9" si="17">N9*1.01</f>
         <v>-43.026000000000003</v>
       </c>
       <c r="T9" s="1">
@@ -1887,47 +1890,47 @@
       </c>
       <c r="Z9" s="1">
         <f>SUM(O9:R9)</f>
-        <v>-173.779</v>
+        <v>-139.42600000000002</v>
       </c>
       <c r="AA9" s="1">
         <f>Z9*1.03</f>
-        <v>-178.99236999999999</v>
+        <v>-143.60878000000002</v>
       </c>
       <c r="AB9" s="1">
-        <f t="shared" ref="AB9:AJ9" si="13">AA9*1.03</f>
-        <v>-184.3621411</v>
+        <f t="shared" ref="AB9:AJ9" si="18">AA9*1.03</f>
+        <v>-147.91704340000004</v>
       </c>
       <c r="AC9" s="1">
-        <f t="shared" si="13"/>
-        <v>-189.89300533300002</v>
+        <f t="shared" si="18"/>
+        <v>-152.35455470200006</v>
       </c>
       <c r="AD9" s="1">
-        <f t="shared" si="13"/>
-        <v>-195.58979549299002</v>
+        <f t="shared" si="18"/>
+        <v>-156.92519134306008</v>
       </c>
       <c r="AE9" s="1">
-        <f t="shared" si="13"/>
-        <v>-201.45748935777974</v>
+        <f t="shared" si="18"/>
+        <v>-161.63294708335189</v>
       </c>
       <c r="AF9" s="1">
-        <f t="shared" si="13"/>
-        <v>-207.50121403851313</v>
+        <f t="shared" si="18"/>
+        <v>-166.48193549585247</v>
       </c>
       <c r="AG9" s="1">
-        <f t="shared" si="13"/>
-        <v>-213.72625045966853</v>
+        <f t="shared" si="18"/>
+        <v>-171.47639356072804</v>
       </c>
       <c r="AH9" s="1">
-        <f t="shared" si="13"/>
-        <v>-220.13803797345861</v>
+        <f t="shared" si="18"/>
+        <v>-176.6206853675499</v>
       </c>
       <c r="AI9" s="1">
-        <f t="shared" si="13"/>
-        <v>-226.74217911266237</v>
+        <f t="shared" si="18"/>
+        <v>-181.91930592857639</v>
       </c>
       <c r="AJ9" s="1">
-        <f t="shared" si="13"/>
-        <v>-233.54444448604224</v>
+        <f t="shared" si="18"/>
+        <v>-187.37688510643369</v>
       </c>
     </row>
     <row r="10" spans="1:144" x14ac:dyDescent="0.3">
@@ -1977,11 +1980,10 @@
         <v>152.19999999999999</v>
       </c>
       <c r="Q10" s="1">
-        <f t="shared" ref="P10:R10" si="14">M10*0.99</f>
-        <v>154.34100000000001</v>
+        <v>143.80000000000001</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="Q10:R10" si="19">N10*0.99</f>
         <v>155.232</v>
       </c>
       <c r="T10" s="1">
@@ -2007,47 +2009,47 @@
       </c>
       <c r="Z10" s="1">
         <f>SUM(O10:R10)</f>
-        <v>618.87299999999993</v>
+        <v>608.33199999999999</v>
       </c>
       <c r="AA10" s="1">
-        <f t="shared" ref="AA10:AJ10" si="15">Z10*0.99</f>
-        <v>612.68426999999997</v>
+        <f t="shared" ref="AA10:AJ10" si="20">Z10*0.99</f>
+        <v>602.24868000000004</v>
       </c>
       <c r="AB10" s="1">
-        <f t="shared" si="15"/>
-        <v>606.55742729999997</v>
+        <f t="shared" si="20"/>
+        <v>596.22619320000001</v>
       </c>
       <c r="AC10" s="1">
-        <f t="shared" si="15"/>
-        <v>600.49185302699993</v>
+        <f t="shared" si="20"/>
+        <v>590.26393126799996</v>
       </c>
       <c r="AD10" s="1">
-        <f t="shared" si="15"/>
-        <v>594.48693449672987</v>
+        <f t="shared" si="20"/>
+        <v>584.36129195531998</v>
       </c>
       <c r="AE10" s="1">
-        <f t="shared" si="15"/>
-        <v>588.54206515176259</v>
+        <f t="shared" si="20"/>
+        <v>578.51767903576683</v>
       </c>
       <c r="AF10" s="1">
-        <f t="shared" si="15"/>
-        <v>582.65664450024497</v>
+        <f t="shared" si="20"/>
+        <v>572.73250224540914</v>
       </c>
       <c r="AG10" s="1">
-        <f t="shared" si="15"/>
-        <v>576.83007805524255</v>
+        <f t="shared" si="20"/>
+        <v>567.00517722295501</v>
       </c>
       <c r="AH10" s="1">
-        <f t="shared" si="15"/>
-        <v>571.06177727469014</v>
+        <f t="shared" si="20"/>
+        <v>561.33512545072551</v>
       </c>
       <c r="AI10" s="1">
-        <f t="shared" si="15"/>
-        <v>565.35115950194324</v>
+        <f t="shared" si="20"/>
+        <v>555.72177419621823</v>
       </c>
       <c r="AJ10" s="1">
-        <f t="shared" si="15"/>
-        <v>559.69764790692386</v>
+        <f t="shared" si="20"/>
+        <v>550.16455645425606</v>
       </c>
     </row>
     <row r="11" spans="1:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2056,136 +2058,136 @@
         <v>17</v>
       </c>
       <c r="C11" s="7">
-        <f t="shared" ref="C11:K11" si="16">C7-C8-C9-C10</f>
+        <f t="shared" ref="C11:K11" si="21">C7-C8-C9-C10</f>
         <v>284.40000000000009</v>
       </c>
       <c r="D11" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>-626.09999999999991</v>
       </c>
       <c r="E11" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>271.7000000000001</v>
       </c>
       <c r="F11" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>294.39999999999992</v>
       </c>
       <c r="G11" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>-54.999999999999787</v>
       </c>
       <c r="H11" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>439.20000000000005</v>
       </c>
       <c r="I11" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>417.79999999999984</v>
       </c>
       <c r="J11" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>367.90000000000015</v>
       </c>
       <c r="K11" s="7">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>326.09999999999968</v>
       </c>
       <c r="L11" s="7">
-        <f t="shared" ref="L11:R11" si="17">L7-L8-L9-L10</f>
+        <f t="shared" ref="L11:R11" si="22">L7-L8-L9-L10</f>
         <v>448.7000000000001</v>
       </c>
       <c r="M11" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>375.0999999999998</v>
       </c>
       <c r="N11" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>718.90000000000009</v>
       </c>
       <c r="O11" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>353.19999999999982</v>
       </c>
       <c r="P11" s="7">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>310.50000000000011</v>
       </c>
       <c r="Q11" s="7">
-        <f t="shared" si="17"/>
-        <v>335.13199999999989</v>
+        <f t="shared" si="22"/>
+        <v>655.69999999999982</v>
       </c>
       <c r="R11" s="7">
-        <f t="shared" si="17"/>
-        <v>267.79399999999998</v>
+        <f t="shared" si="22"/>
+        <v>297.79399999999998</v>
       </c>
       <c r="T11" s="7">
-        <f t="shared" ref="T11:Z11" si="18">T7-T8-T9-T10</f>
+        <f t="shared" ref="T11:Z11" si="23">T7-T8-T9-T10</f>
         <v>517.89999999999941</v>
       </c>
       <c r="U11" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>594.10000000000048</v>
       </c>
       <c r="V11" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>1044.4999999999995</v>
       </c>
       <c r="W11" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>224.39999999999952</v>
       </c>
       <c r="X11" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>1169.8999999999992</v>
       </c>
       <c r="Y11" s="7">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>1868.7999999999993</v>
       </c>
       <c r="Z11" s="7">
-        <f t="shared" si="18"/>
-        <v>737.04799999999966</v>
+        <f t="shared" si="23"/>
+        <v>1113.8899999999994</v>
       </c>
       <c r="AA11" s="7">
-        <f t="shared" ref="AA11:AJ11" si="19">AA7-AA8-AA9-AA10</f>
-        <v>1885.6064800000001</v>
+        <f t="shared" ref="AA11:AJ11" si="24">AA7-AA8-AA9-AA10</f>
+        <v>1644.5895399999999</v>
       </c>
       <c r="AB11" s="7">
-        <f t="shared" si="19"/>
-        <v>1943.4890614000003</v>
+        <f t="shared" si="24"/>
+        <v>1808.2807701999996</v>
       </c>
       <c r="AC11" s="7">
-        <f t="shared" si="19"/>
-        <v>2002.3991868579999</v>
+        <f t="shared" si="24"/>
+        <v>1863.8123418340001</v>
       </c>
       <c r="AD11" s="7">
-        <f t="shared" si="19"/>
-        <v>2062.3608562393001</v>
+        <f t="shared" si="24"/>
+        <v>1920.3200521557399</v>
       </c>
       <c r="AE11" s="7">
-        <f t="shared" si="19"/>
-        <v>2098.7859994014884</v>
+        <f t="shared" si="24"/>
+        <v>1977.8265438709459</v>
       </c>
       <c r="AF11" s="7">
-        <f t="shared" si="19"/>
-        <v>2135.5738504856931</v>
+        <f t="shared" si="24"/>
+        <v>2036.3549345902707</v>
       </c>
       <c r="AG11" s="7">
-        <f t="shared" si="19"/>
-        <v>2172.7327461613249</v>
+        <f t="shared" si="24"/>
+        <v>2095.9288277043975</v>
       </c>
       <c r="AH11" s="7">
-        <f t="shared" si="19"/>
-        <v>2210.2712001932364</v>
+        <f t="shared" si="24"/>
+        <v>2156.5723235107807</v>
       </c>
       <c r="AI11" s="7">
-        <f t="shared" si="19"/>
-        <v>2248.1979085001335</v>
+        <f t="shared" si="24"/>
+        <v>2218.3100305981939</v>
       </c>
       <c r="AJ11" s="7">
-        <f t="shared" si="19"/>
-        <v>2286.5217543574258</v>
+        <f t="shared" si="24"/>
+        <v>2281.1670774953304</v>
       </c>
     </row>
     <row r="12" spans="1:144" x14ac:dyDescent="0.3">
@@ -2235,12 +2237,11 @@
         <v>118.3</v>
       </c>
       <c r="Q12" s="1">
-        <f t="shared" ref="P12:R12" si="20">Q11*0.16</f>
-        <v>53.621119999999983</v>
+        <v>199.3</v>
       </c>
       <c r="R12" s="1">
-        <f t="shared" si="20"/>
-        <v>42.84704</v>
+        <f t="shared" ref="Q12:R12" si="25">R11*0.16</f>
+        <v>47.647039999999997</v>
       </c>
       <c r="T12" s="1">
         <v>62.2</v>
@@ -2265,47 +2266,47 @@
       </c>
       <c r="Z12" s="1">
         <f>SUM(O12:R12)</f>
-        <v>273.46816000000001</v>
+        <v>423.94704000000002</v>
       </c>
       <c r="AA12" s="1">
-        <f t="shared" ref="AA12:AJ12" si="21">AA11*0.17</f>
-        <v>320.55310160000005</v>
+        <f>AA11*0.25</f>
+        <v>411.14738499999999</v>
       </c>
       <c r="AB12" s="1">
-        <f t="shared" si="21"/>
-        <v>330.3931404380001</v>
+        <f t="shared" ref="AB12:AJ12" si="26">AB11*0.25</f>
+        <v>452.07019254999989</v>
       </c>
       <c r="AC12" s="1">
-        <f t="shared" si="21"/>
-        <v>340.40786176585999</v>
+        <f t="shared" si="26"/>
+        <v>465.95308545850003</v>
       </c>
       <c r="AD12" s="1">
-        <f t="shared" si="21"/>
-        <v>350.60134556068107</v>
+        <f t="shared" si="26"/>
+        <v>480.08001303893496</v>
       </c>
       <c r="AE12" s="1">
-        <f t="shared" si="21"/>
-        <v>356.79361989825304</v>
+        <f t="shared" si="26"/>
+        <v>494.45663596773647</v>
       </c>
       <c r="AF12" s="1">
-        <f t="shared" si="21"/>
-        <v>363.04755458256784</v>
+        <f t="shared" si="26"/>
+        <v>509.08873364756766</v>
       </c>
       <c r="AG12" s="1">
-        <f t="shared" si="21"/>
-        <v>369.36456684742529</v>
+        <f t="shared" si="26"/>
+        <v>523.98220692609937</v>
       </c>
       <c r="AH12" s="1">
-        <f t="shared" si="21"/>
-        <v>375.74610403285021</v>
+        <f t="shared" si="26"/>
+        <v>539.14308087769518</v>
       </c>
       <c r="AI12" s="1">
-        <f t="shared" si="21"/>
-        <v>382.1936444450227</v>
+        <f t="shared" si="26"/>
+        <v>554.57750764954847</v>
       </c>
       <c r="AJ12" s="1">
-        <f t="shared" si="21"/>
-        <v>388.70869824076243</v>
+        <f t="shared" si="26"/>
+        <v>570.29176937383261</v>
       </c>
     </row>
     <row r="13" spans="1:144" x14ac:dyDescent="0.3">
@@ -2355,7 +2356,7 @@
         <v>-20</v>
       </c>
       <c r="Q13" s="1">
-        <v>-20</v>
+        <v>-16.899999999999999</v>
       </c>
       <c r="R13" s="1">
         <v>-20</v>
@@ -2383,47 +2384,37 @@
       </c>
       <c r="Z13" s="1">
         <f>SUM(O13:R13)</f>
-        <v>-78.3</v>
+        <v>-75.199999999999989</v>
       </c>
       <c r="AA13" s="1">
-        <f>Z13*1.02</f>
-        <v>-79.866</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="1">
-        <f t="shared" ref="AB13:AJ13" si="22">AA13*1.02</f>
-        <v>-81.463319999999996</v>
+        <v>0</v>
       </c>
       <c r="AC13" s="1">
-        <f t="shared" si="22"/>
-        <v>-83.092586400000002</v>
+        <v>0</v>
       </c>
       <c r="AD13" s="1">
-        <f t="shared" si="22"/>
-        <v>-84.754438128000004</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="1">
-        <f t="shared" si="22"/>
-        <v>-86.449526890560008</v>
+        <v>0</v>
       </c>
       <c r="AF13" s="1">
-        <f t="shared" si="22"/>
-        <v>-88.178517428371208</v>
+        <v>0</v>
       </c>
       <c r="AG13" s="1">
-        <f t="shared" si="22"/>
-        <v>-89.942087776938635</v>
+        <v>0</v>
       </c>
       <c r="AH13" s="1">
-        <f t="shared" si="22"/>
-        <v>-91.740929532477409</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="1">
-        <f t="shared" si="22"/>
-        <v>-93.575748123126957</v>
+        <v>0</v>
       </c>
       <c r="AJ13" s="1">
-        <f t="shared" si="22"/>
-        <v>-95.447263085589498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:144" x14ac:dyDescent="0.3">
@@ -2474,7 +2465,7 @@
         <v>-29.5</v>
       </c>
       <c r="Q14" s="1">
-        <v>-30</v>
+        <v>25.4</v>
       </c>
       <c r="R14" s="1">
         <v>-30</v>
@@ -2502,47 +2493,47 @@
       </c>
       <c r="Z14" s="1">
         <f>SUM(O14:R14)</f>
-        <v>-82.5</v>
+        <v>-27.1</v>
       </c>
       <c r="AA14" s="1">
-        <f t="shared" ref="AA14:AJ14" si="23">Z14*1.005</f>
-        <v>-82.912499999999994</v>
+        <f t="shared" ref="AA14:AJ14" si="27">Z14*1.005</f>
+        <v>-27.235499999999998</v>
       </c>
       <c r="AB14" s="1">
-        <f t="shared" si="23"/>
-        <v>-83.327062499999982</v>
+        <f t="shared" si="27"/>
+        <v>-27.371677499999997</v>
       </c>
       <c r="AC14" s="1">
-        <f t="shared" si="23"/>
-        <v>-83.743697812499974</v>
+        <f t="shared" si="27"/>
+        <v>-27.508535887499995</v>
       </c>
       <c r="AD14" s="1">
-        <f t="shared" si="23"/>
-        <v>-84.162416301562459</v>
+        <f t="shared" si="27"/>
+        <v>-27.646078566937494</v>
       </c>
       <c r="AE14" s="1">
-        <f t="shared" si="23"/>
-        <v>-84.583228383070264</v>
+        <f t="shared" si="27"/>
+        <v>-27.784308959772179</v>
       </c>
       <c r="AF14" s="1">
-        <f t="shared" si="23"/>
-        <v>-85.006144524985601</v>
+        <f t="shared" si="27"/>
+        <v>-27.923230504571038</v>
       </c>
       <c r="AG14" s="1">
-        <f t="shared" si="23"/>
-        <v>-85.431175247610526</v>
+        <f t="shared" si="27"/>
+        <v>-28.062846657093889</v>
       </c>
       <c r="AH14" s="1">
-        <f t="shared" si="23"/>
-        <v>-85.858331123848572</v>
+        <f t="shared" si="27"/>
+        <v>-28.203160890379355</v>
       </c>
       <c r="AI14" s="1">
-        <f t="shared" si="23"/>
-        <v>-86.28762277946781</v>
+        <f t="shared" si="27"/>
+        <v>-28.344176694831248</v>
       </c>
       <c r="AJ14" s="1">
-        <f t="shared" si="23"/>
-        <v>-86.719060893365139</v>
+        <f t="shared" si="27"/>
+        <v>-28.485897578305401</v>
       </c>
     </row>
     <row r="15" spans="1:144" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -2551,568 +2542,568 @@
         <v>19</v>
       </c>
       <c r="C15" s="7">
-        <f t="shared" ref="C15:K15" si="24">C11-C12-C13-C14</f>
+        <f t="shared" ref="C15:K15" si="28">C11-C12-C13-C14</f>
         <v>244.8000000000001</v>
       </c>
       <c r="D15" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>-672.99999999999989</v>
       </c>
       <c r="E15" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>290.50000000000011</v>
       </c>
       <c r="F15" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>249.2999999999999</v>
       </c>
       <c r="G15" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>-10.999999999999789</v>
       </c>
       <c r="H15" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>274.10000000000002</v>
       </c>
       <c r="I15" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>361.79999999999984</v>
       </c>
       <c r="J15" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>361.30000000000013</v>
       </c>
       <c r="K15" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v>313.29999999999967</v>
       </c>
       <c r="L15" s="7">
-        <f t="shared" ref="L15:N15" si="25">L11-L12-L13-L14</f>
+        <f t="shared" ref="L15:N15" si="29">L11-L12-L13-L14</f>
         <v>374.7000000000001</v>
       </c>
       <c r="M15" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>315.19999999999982</v>
       </c>
       <c r="N15" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v>567.20000000000005</v>
       </c>
       <c r="O15" s="7">
-        <f t="shared" ref="O15:R15" si="26">O11-O12-O13-O14</f>
+        <f t="shared" ref="O15:R15" si="30">O11-O12-O13-O14</f>
         <v>305.79999999999984</v>
       </c>
       <c r="P15" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v>241.7000000000001</v>
       </c>
       <c r="Q15" s="7">
-        <f t="shared" si="26"/>
-        <v>331.51087999999993</v>
+        <f t="shared" si="30"/>
+        <v>447.89999999999981</v>
       </c>
       <c r="R15" s="7">
-        <f t="shared" si="26"/>
-        <v>274.94695999999999</v>
+        <f t="shared" si="30"/>
+        <v>300.14695999999998</v>
       </c>
       <c r="T15" s="7">
-        <f t="shared" ref="T15:Y15" si="27">T11-T12-T13-T14</f>
+        <f t="shared" ref="T15:Y15" si="31">T11-T12-T13-T14</f>
         <v>430.49999999999943</v>
       </c>
       <c r="U15" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>584.60000000000036</v>
       </c>
       <c r="V15" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>965.49999999999955</v>
       </c>
       <c r="W15" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>111.59999999999953</v>
       </c>
       <c r="X15" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>986.19999999999925</v>
       </c>
       <c r="Y15" s="7">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v>1570.3999999999994</v>
       </c>
       <c r="Z15" s="7">
-        <f t="shared" ref="Z15" si="28">Z11-Z12-Z13-Z14</f>
-        <v>624.3798399999996</v>
+        <f t="shared" ref="Z15" si="32">Z11-Z12-Z13-Z14</f>
+        <v>792.24295999999947</v>
       </c>
       <c r="AA15" s="7">
-        <f t="shared" ref="AA15" si="29">AA11-AA12-AA13-AA14</f>
-        <v>1727.8318784000001</v>
+        <f t="shared" ref="AA15" si="33">AA11-AA12-AA13-AA14</f>
+        <v>1260.677655</v>
       </c>
       <c r="AB15" s="7">
-        <f t="shared" ref="AB15" si="30">AB11-AB12-AB13-AB14</f>
-        <v>1777.8863034620003</v>
+        <f t="shared" ref="AB15" si="34">AB11-AB12-AB13-AB14</f>
+        <v>1383.5822551499998</v>
       </c>
       <c r="AC15" s="7">
-        <f t="shared" ref="AC15" si="31">AC11-AC12-AC13-AC14</f>
-        <v>1828.82760930464</v>
+        <f t="shared" ref="AC15" si="35">AC11-AC12-AC13-AC14</f>
+        <v>1425.3677922630002</v>
       </c>
       <c r="AD15" s="7">
-        <f t="shared" ref="AD15" si="32">AD11-AD12-AD13-AD14</f>
-        <v>1880.6763651081815</v>
+        <f t="shared" ref="AD15" si="36">AD11-AD12-AD13-AD14</f>
+        <v>1467.8861176837424</v>
       </c>
       <c r="AE15" s="7">
-        <f t="shared" ref="AE15" si="33">AE11-AE12-AE13-AE14</f>
-        <v>1913.0251347768658</v>
+        <f t="shared" ref="AE15" si="37">AE11-AE12-AE13-AE14</f>
+        <v>1511.1542168629817</v>
       </c>
       <c r="AF15" s="7">
-        <f t="shared" ref="AF15" si="34">AF11-AF12-AF13-AF14</f>
-        <v>1945.7109578564819</v>
+        <f t="shared" ref="AF15" si="38">AF11-AF12-AF13-AF14</f>
+        <v>1555.189431447274</v>
       </c>
       <c r="AG15" s="7">
-        <f t="shared" ref="AG15" si="35">AG11-AG12-AG13-AG14</f>
-        <v>1978.7414423384489</v>
+        <f t="shared" ref="AG15" si="39">AG11-AG12-AG13-AG14</f>
+        <v>1600.0094674353918</v>
       </c>
       <c r="AH15" s="7">
-        <f t="shared" ref="AH15" si="36">AH11-AH12-AH13-AH14</f>
-        <v>2012.124356816712</v>
+        <f t="shared" ref="AH15" si="40">AH11-AH12-AH13-AH14</f>
+        <v>1645.632403523465</v>
       </c>
       <c r="AI15" s="7">
-        <f t="shared" ref="AI15" si="37">AI11-AI12-AI13-AI14</f>
-        <v>2045.8676349577054</v>
+        <f t="shared" ref="AI15" si="41">AI11-AI12-AI13-AI14</f>
+        <v>1692.0766996434768</v>
       </c>
       <c r="AJ15" s="7">
-        <f t="shared" ref="AJ15" si="38">AJ11-AJ12-AJ13-AJ14</f>
-        <v>2079.9793800956181</v>
+        <f t="shared" ref="AJ15" si="42">AJ11-AJ12-AJ13-AJ14</f>
+        <v>1739.3612056998031</v>
       </c>
       <c r="AK15" s="10">
         <f>AJ15+(AJ15*$AN$20)</f>
-        <v>2059.1795862946619</v>
+        <v>1721.967593642805</v>
       </c>
       <c r="AL15" s="10">
-        <f t="shared" ref="AL15:CW15" si="39">AK15+(AK15*$AN$20)</f>
-        <v>2038.5877904317153</v>
+        <f t="shared" ref="AL15:CW15" si="43">AK15+(AK15*$AN$20)</f>
+        <v>1704.7479177063769</v>
       </c>
       <c r="AM15" s="10">
-        <f t="shared" si="39"/>
-        <v>2018.2019125273982</v>
+        <f t="shared" si="43"/>
+        <v>1687.7004385293133</v>
       </c>
       <c r="AN15" s="10">
-        <f t="shared" si="39"/>
-        <v>1998.0198934021244</v>
+        <f t="shared" si="43"/>
+        <v>1670.8234341440202</v>
       </c>
       <c r="AO15" s="10">
-        <f t="shared" si="39"/>
-        <v>1978.0396944681031</v>
+        <f t="shared" si="43"/>
+        <v>1654.11519980258</v>
       </c>
       <c r="AP15" s="10">
-        <f t="shared" si="39"/>
-        <v>1958.259297523422</v>
+        <f t="shared" si="43"/>
+        <v>1637.5740478045543</v>
       </c>
       <c r="AQ15" s="10">
-        <f t="shared" si="39"/>
-        <v>1938.6767045481877</v>
+        <f t="shared" si="43"/>
+        <v>1621.1983073265087</v>
       </c>
       <c r="AR15" s="10">
-        <f t="shared" si="39"/>
-        <v>1919.2899375027057</v>
+        <f t="shared" si="43"/>
+        <v>1604.9863242532435</v>
       </c>
       <c r="AS15" s="10">
-        <f t="shared" si="39"/>
-        <v>1900.0970381276786</v>
+        <f t="shared" si="43"/>
+        <v>1588.9364610107111</v>
       </c>
       <c r="AT15" s="10">
-        <f t="shared" si="39"/>
-        <v>1881.0960677464018</v>
+        <f t="shared" si="43"/>
+        <v>1573.047096400604</v>
       </c>
       <c r="AU15" s="10">
-        <f t="shared" si="39"/>
-        <v>1862.2851070689378</v>
+        <f t="shared" si="43"/>
+        <v>1557.3166254365979</v>
       </c>
       <c r="AV15" s="10">
-        <f t="shared" si="39"/>
-        <v>1843.6622559982484</v>
+        <f t="shared" si="43"/>
+        <v>1541.7434591822318</v>
       </c>
       <c r="AW15" s="10">
-        <f t="shared" si="39"/>
-        <v>1825.225633438266</v>
+        <f t="shared" si="43"/>
+        <v>1526.3260245904096</v>
       </c>
       <c r="AX15" s="10">
-        <f t="shared" si="39"/>
-        <v>1806.9733771038832</v>
+        <f t="shared" si="43"/>
+        <v>1511.0627643445055</v>
       </c>
       <c r="AY15" s="10">
-        <f t="shared" si="39"/>
-        <v>1788.9036433328445</v>
+        <f t="shared" si="43"/>
+        <v>1495.9521367010605</v>
       </c>
       <c r="AZ15" s="10">
-        <f t="shared" si="39"/>
-        <v>1771.0146068995159</v>
+        <f t="shared" si="43"/>
+        <v>1480.9926153340498</v>
       </c>
       <c r="BA15" s="10">
-        <f t="shared" si="39"/>
-        <v>1753.3044608305208</v>
+        <f t="shared" si="43"/>
+        <v>1466.1826891807093</v>
       </c>
       <c r="BB15" s="10">
-        <f t="shared" si="39"/>
-        <v>1735.7714162222155</v>
+        <f t="shared" si="43"/>
+        <v>1451.5208622889022</v>
       </c>
       <c r="BC15" s="10">
-        <f t="shared" si="39"/>
-        <v>1718.4137020599933</v>
+        <f t="shared" si="43"/>
+        <v>1437.0056536660131</v>
       </c>
       <c r="BD15" s="10">
-        <f t="shared" si="39"/>
-        <v>1701.2295650393933</v>
+        <f t="shared" si="43"/>
+        <v>1422.6355971293531</v>
       </c>
       <c r="BE15" s="10">
-        <f t="shared" si="39"/>
-        <v>1684.2172693889993</v>
+        <f t="shared" si="43"/>
+        <v>1408.4092411580596</v>
       </c>
       <c r="BF15" s="10">
-        <f t="shared" si="39"/>
-        <v>1667.3750966951093</v>
+        <f t="shared" si="43"/>
+        <v>1394.325148746479</v>
       </c>
       <c r="BG15" s="10">
-        <f t="shared" si="39"/>
-        <v>1650.7013457281582</v>
+        <f t="shared" si="43"/>
+        <v>1380.3818972590143</v>
       </c>
       <c r="BH15" s="10">
-        <f t="shared" si="39"/>
-        <v>1634.1943322708767</v>
+        <f t="shared" si="43"/>
+        <v>1366.5780782864242</v>
       </c>
       <c r="BI15" s="10">
-        <f t="shared" si="39"/>
-        <v>1617.8523889481678</v>
+        <f t="shared" si="43"/>
+        <v>1352.91229750356</v>
       </c>
       <c r="BJ15" s="10">
-        <f t="shared" si="39"/>
-        <v>1601.673865058686</v>
+        <f t="shared" si="43"/>
+        <v>1339.3831745285245</v>
       </c>
       <c r="BK15" s="10">
-        <f t="shared" si="39"/>
-        <v>1585.6571264080992</v>
+        <f t="shared" si="43"/>
+        <v>1325.9893427832392</v>
       </c>
       <c r="BL15" s="10">
-        <f t="shared" si="39"/>
-        <v>1569.8005551440183</v>
+        <f t="shared" si="43"/>
+        <v>1312.7294493554068</v>
       </c>
       <c r="BM15" s="10">
-        <f t="shared" si="39"/>
-        <v>1554.102549592578</v>
+        <f t="shared" si="43"/>
+        <v>1299.6021548618528</v>
       </c>
       <c r="BN15" s="10">
-        <f t="shared" si="39"/>
-        <v>1538.5615240966522</v>
+        <f t="shared" si="43"/>
+        <v>1286.6061333132343</v>
       </c>
       <c r="BO15" s="10">
-        <f t="shared" si="39"/>
-        <v>1523.1759088556857</v>
+        <f t="shared" si="43"/>
+        <v>1273.7400719801019</v>
       </c>
       <c r="BP15" s="10">
-        <f t="shared" si="39"/>
-        <v>1507.9441497671289</v>
+        <f t="shared" si="43"/>
+        <v>1261.002671260301</v>
       </c>
       <c r="BQ15" s="10">
-        <f t="shared" si="39"/>
-        <v>1492.8647082694577</v>
+        <f t="shared" si="43"/>
+        <v>1248.392644547698</v>
       </c>
       <c r="BR15" s="10">
-        <f t="shared" si="39"/>
-        <v>1477.936061186763</v>
+        <f t="shared" si="43"/>
+        <v>1235.908718102221</v>
       </c>
       <c r="BS15" s="10">
-        <f t="shared" si="39"/>
-        <v>1463.1567005748955</v>
+        <f t="shared" si="43"/>
+        <v>1223.5496309211987</v>
       </c>
       <c r="BT15" s="10">
-        <f t="shared" si="39"/>
-        <v>1448.5251335691464</v>
+        <f t="shared" si="43"/>
+        <v>1211.3141346119867</v>
       </c>
       <c r="BU15" s="10">
-        <f t="shared" si="39"/>
-        <v>1434.039882233455</v>
+        <f t="shared" si="43"/>
+        <v>1199.2009932658668</v>
       </c>
       <c r="BV15" s="10">
-        <f t="shared" si="39"/>
-        <v>1419.6994834111206</v>
+        <f t="shared" si="43"/>
+        <v>1187.2089833332082</v>
       </c>
       <c r="BW15" s="10">
-        <f t="shared" si="39"/>
-        <v>1405.5024885770094</v>
+        <f t="shared" si="43"/>
+        <v>1175.3368934998762</v>
       </c>
       <c r="BX15" s="10">
-        <f t="shared" si="39"/>
-        <v>1391.4474636912394</v>
+        <f t="shared" si="43"/>
+        <v>1163.5835245648775</v>
       </c>
       <c r="BY15" s="10">
-        <f t="shared" si="39"/>
-        <v>1377.5329890543269</v>
+        <f t="shared" si="43"/>
+        <v>1151.9476893192286</v>
       </c>
       <c r="BZ15" s="10">
-        <f t="shared" si="39"/>
-        <v>1363.7576591637837</v>
+        <f t="shared" si="43"/>
+        <v>1140.4282124260365</v>
       </c>
       <c r="CA15" s="10">
-        <f t="shared" si="39"/>
-        <v>1350.120082572146</v>
+        <f t="shared" si="43"/>
+        <v>1129.0239303017761</v>
       </c>
       <c r="CB15" s="10">
-        <f t="shared" si="39"/>
-        <v>1336.6188817464244</v>
+        <f t="shared" si="43"/>
+        <v>1117.7336909987582</v>
       </c>
       <c r="CC15" s="10">
-        <f t="shared" si="39"/>
-        <v>1323.2526929289602</v>
+        <f t="shared" si="43"/>
+        <v>1106.5563540887706</v>
       </c>
       <c r="CD15" s="10">
-        <f t="shared" si="39"/>
-        <v>1310.0201659996706</v>
+        <f t="shared" si="43"/>
+        <v>1095.4907905478829</v>
       </c>
       <c r="CE15" s="10">
-        <f t="shared" si="39"/>
-        <v>1296.9199643396739</v>
+        <f t="shared" si="43"/>
+        <v>1084.535882642404</v>
       </c>
       <c r="CF15" s="10">
-        <f t="shared" si="39"/>
-        <v>1283.9507646962772</v>
+        <f t="shared" si="43"/>
+        <v>1073.69052381598</v>
       </c>
       <c r="CG15" s="10">
-        <f t="shared" si="39"/>
-        <v>1271.1112570493144</v>
+        <f t="shared" si="43"/>
+        <v>1062.9536185778202</v>
       </c>
       <c r="CH15" s="10">
-        <f t="shared" si="39"/>
-        <v>1258.4001444788212</v>
+        <f t="shared" si="43"/>
+        <v>1052.3240823920419</v>
       </c>
       <c r="CI15" s="10">
-        <f t="shared" si="39"/>
-        <v>1245.8161430340331</v>
+        <f t="shared" si="43"/>
+        <v>1041.8008415681215</v>
       </c>
       <c r="CJ15" s="10">
-        <f t="shared" si="39"/>
-        <v>1233.3579816036927</v>
+        <f t="shared" si="43"/>
+        <v>1031.3828331524403</v>
       </c>
       <c r="CK15" s="10">
-        <f t="shared" si="39"/>
-        <v>1221.0244017876557</v>
+        <f t="shared" si="43"/>
+        <v>1021.0690048209159</v>
       </c>
       <c r="CL15" s="10">
-        <f t="shared" si="39"/>
-        <v>1208.8141577697793</v>
+        <f t="shared" si="43"/>
+        <v>1010.8583147727068</v>
       </c>
       <c r="CM15" s="10">
-        <f t="shared" si="39"/>
-        <v>1196.7260161920815</v>
+        <f t="shared" si="43"/>
+        <v>1000.7497316249797</v>
       </c>
       <c r="CN15" s="10">
-        <f t="shared" si="39"/>
-        <v>1184.7587560301606</v>
+        <f t="shared" si="43"/>
+        <v>990.74223430872996</v>
       </c>
       <c r="CO15" s="10">
-        <f t="shared" si="39"/>
-        <v>1172.9111684698589</v>
+        <f t="shared" si="43"/>
+        <v>980.83481196564264</v>
       </c>
       <c r="CP15" s="10">
-        <f t="shared" si="39"/>
-        <v>1161.1820567851603</v>
+        <f t="shared" si="43"/>
+        <v>971.0264638459862</v>
       </c>
       <c r="CQ15" s="10">
-        <f t="shared" si="39"/>
-        <v>1149.5702362173088</v>
+        <f t="shared" si="43"/>
+        <v>961.31619920752632</v>
       </c>
       <c r="CR15" s="10">
-        <f t="shared" si="39"/>
-        <v>1138.0745338551358</v>
+        <f t="shared" si="43"/>
+        <v>951.7030372154511</v>
       </c>
       <c r="CS15" s="10">
-        <f t="shared" si="39"/>
-        <v>1126.6937885165844</v>
+        <f t="shared" si="43"/>
+        <v>942.18600684329658</v>
       </c>
       <c r="CT15" s="10">
-        <f t="shared" si="39"/>
-        <v>1115.4268506314186</v>
+        <f t="shared" si="43"/>
+        <v>932.76414677486366</v>
       </c>
       <c r="CU15" s="10">
-        <f t="shared" si="39"/>
-        <v>1104.2725821251045</v>
+        <f t="shared" si="43"/>
+        <v>923.436505307115</v>
       </c>
       <c r="CV15" s="10">
-        <f t="shared" si="39"/>
-        <v>1093.2298563038535</v>
+        <f t="shared" si="43"/>
+        <v>914.2021402540438</v>
       </c>
       <c r="CW15" s="10">
-        <f t="shared" si="39"/>
-        <v>1082.2975577408149</v>
+        <f t="shared" si="43"/>
+        <v>905.06011885150338</v>
       </c>
       <c r="CX15" s="10">
-        <f t="shared" ref="CX15:EN15" si="40">CW15+(CW15*$AN$20)</f>
-        <v>1071.4745821634067</v>
+        <f t="shared" ref="CX15:EN15" si="44">CW15+(CW15*$AN$20)</f>
+        <v>896.00951766298829</v>
       </c>
       <c r="CY15" s="10">
-        <f t="shared" si="40"/>
-        <v>1060.7598363417726</v>
+        <f t="shared" si="44"/>
+        <v>887.04942248635837</v>
       </c>
       <c r="CZ15" s="10">
-        <f t="shared" si="40"/>
-        <v>1050.1522379783548</v>
+        <f t="shared" si="44"/>
+        <v>878.17892826149478</v>
       </c>
       <c r="DA15" s="10">
-        <f t="shared" si="40"/>
-        <v>1039.6507155985712</v>
+        <f t="shared" si="44"/>
+        <v>869.39713897887987</v>
       </c>
       <c r="DB15" s="10">
-        <f t="shared" si="40"/>
-        <v>1029.2542084425854</v>
+        <f t="shared" si="44"/>
+        <v>860.70316758909109</v>
       </c>
       <c r="DC15" s="10">
-        <f t="shared" si="40"/>
-        <v>1018.9616663581596</v>
+        <f t="shared" si="44"/>
+        <v>852.09613591320021</v>
       </c>
       <c r="DD15" s="10">
-        <f t="shared" si="40"/>
-        <v>1008.7720496945781</v>
+        <f t="shared" si="44"/>
+        <v>843.57517455406821</v>
       </c>
       <c r="DE15" s="10">
-        <f t="shared" si="40"/>
-        <v>998.68432919763234</v>
+        <f t="shared" si="44"/>
+        <v>835.13942280852757</v>
       </c>
       <c r="DF15" s="10">
-        <f t="shared" si="40"/>
-        <v>988.69748590565598</v>
+        <f t="shared" si="44"/>
+        <v>826.7880285804423</v>
       </c>
       <c r="DG15" s="10">
-        <f t="shared" si="40"/>
-        <v>978.81051104659946</v>
+        <f t="shared" si="44"/>
+        <v>818.52014829463792</v>
       </c>
       <c r="DH15" s="10">
-        <f t="shared" si="40"/>
-        <v>969.02240593613351</v>
+        <f t="shared" si="44"/>
+        <v>810.33494681169157</v>
       </c>
       <c r="DI15" s="10">
-        <f t="shared" si="40"/>
-        <v>959.33218187677221</v>
+        <f t="shared" si="44"/>
+        <v>802.23159734357466</v>
       </c>
       <c r="DJ15" s="10">
-        <f t="shared" si="40"/>
-        <v>949.73886005800443</v>
+        <f t="shared" si="44"/>
+        <v>794.20928137013891</v>
       </c>
       <c r="DK15" s="10">
-        <f t="shared" si="40"/>
-        <v>940.24147145742438</v>
+        <f t="shared" si="44"/>
+        <v>786.26718855643753</v>
       </c>
       <c r="DL15" s="10">
-        <f t="shared" si="40"/>
-        <v>930.83905674285018</v>
+        <f t="shared" si="44"/>
+        <v>778.40451667087314</v>
       </c>
       <c r="DM15" s="10">
-        <f t="shared" si="40"/>
-        <v>921.53066617542163</v>
+        <f t="shared" si="44"/>
+        <v>770.62047150416436</v>
       </c>
       <c r="DN15" s="10">
-        <f t="shared" si="40"/>
-        <v>912.31535951366743</v>
+        <f t="shared" si="44"/>
+        <v>762.91426678912273</v>
       </c>
       <c r="DO15" s="10">
-        <f t="shared" si="40"/>
-        <v>903.1922059185307</v>
+        <f t="shared" si="44"/>
+        <v>755.28512412123155</v>
       </c>
       <c r="DP15" s="10">
-        <f t="shared" si="40"/>
-        <v>894.16028385934544</v>
+        <f t="shared" si="44"/>
+        <v>747.7322728800192</v>
       </c>
       <c r="DQ15" s="10">
-        <f t="shared" si="40"/>
-        <v>885.218681020752</v>
+        <f t="shared" si="44"/>
+        <v>740.25495015121896</v>
       </c>
       <c r="DR15" s="10">
-        <f t="shared" si="40"/>
-        <v>876.36649421054449</v>
+        <f t="shared" si="44"/>
+        <v>732.85240064970674</v>
       </c>
       <c r="DS15" s="10">
-        <f t="shared" si="40"/>
-        <v>867.602829268439</v>
+        <f t="shared" si="44"/>
+        <v>725.52387664320963</v>
       </c>
       <c r="DT15" s="10">
-        <f t="shared" si="40"/>
-        <v>858.92680097575465</v>
+        <f t="shared" si="44"/>
+        <v>718.26863787677758</v>
       </c>
       <c r="DU15" s="10">
-        <f t="shared" si="40"/>
-        <v>850.33753296599707</v>
+        <f t="shared" si="44"/>
+        <v>711.08595149800976</v>
       </c>
       <c r="DV15" s="10">
-        <f t="shared" si="40"/>
-        <v>841.83415763633707</v>
+        <f t="shared" si="44"/>
+        <v>703.97509198302964</v>
       </c>
       <c r="DW15" s="10">
-        <f t="shared" si="40"/>
-        <v>833.41581605997374</v>
+        <f t="shared" si="44"/>
+        <v>696.9353410631993</v>
       </c>
       <c r="DX15" s="10">
-        <f t="shared" si="40"/>
-        <v>825.08165789937402</v>
+        <f t="shared" si="44"/>
+        <v>689.96598765256726</v>
       </c>
       <c r="DY15" s="10">
-        <f t="shared" si="40"/>
-        <v>816.83084132038027</v>
+        <f t="shared" si="44"/>
+        <v>683.06632777604159</v>
       </c>
       <c r="DZ15" s="10">
-        <f t="shared" si="40"/>
-        <v>808.66253290717646</v>
+        <f t="shared" si="44"/>
+        <v>676.23566449828115</v>
       </c>
       <c r="EA15" s="10">
-        <f t="shared" si="40"/>
-        <v>800.57590757810465</v>
+        <f t="shared" si="44"/>
+        <v>669.47330785329837</v>
       </c>
       <c r="EB15" s="10">
-        <f t="shared" si="40"/>
-        <v>792.5701485023236</v>
+        <f t="shared" si="44"/>
+        <v>662.77857477476539</v>
       </c>
       <c r="EC15" s="10">
-        <f t="shared" si="40"/>
-        <v>784.64444701730042</v>
+        <f t="shared" si="44"/>
+        <v>656.15078902701771</v>
       </c>
       <c r="ED15" s="10">
-        <f t="shared" si="40"/>
-        <v>776.79800254712745</v>
+        <f t="shared" si="44"/>
+        <v>649.58928113674756</v>
       </c>
       <c r="EE15" s="10">
-        <f t="shared" si="40"/>
-        <v>769.03002252165618</v>
+        <f t="shared" si="44"/>
+        <v>643.09338832538003</v>
       </c>
       <c r="EF15" s="10">
-        <f t="shared" si="40"/>
-        <v>761.33972229643962</v>
+        <f t="shared" si="44"/>
+        <v>636.6624544421262</v>
       </c>
       <c r="EG15" s="10">
-        <f t="shared" si="40"/>
-        <v>753.72632507347521</v>
+        <f t="shared" si="44"/>
+        <v>630.29582989770495</v>
       </c>
       <c r="EH15" s="10">
-        <f t="shared" si="40"/>
-        <v>746.18906182274043</v>
+        <f t="shared" si="44"/>
+        <v>623.9928715987279</v>
       </c>
       <c r="EI15" s="10">
-        <f t="shared" si="40"/>
-        <v>738.72717120451307</v>
+        <f t="shared" si="44"/>
+        <v>617.75294288274063</v>
       </c>
       <c r="EJ15" s="10">
-        <f t="shared" si="40"/>
-        <v>731.33989949246791</v>
+        <f t="shared" si="44"/>
+        <v>611.57541345391326</v>
       </c>
       <c r="EK15" s="10">
-        <f t="shared" si="40"/>
-        <v>724.02650049754322</v>
+        <f t="shared" si="44"/>
+        <v>605.45965931937417</v>
       </c>
       <c r="EL15" s="10">
-        <f t="shared" si="40"/>
-        <v>716.78623549256781</v>
+        <f t="shared" si="44"/>
+        <v>599.4050627261804</v>
       </c>
       <c r="EM15" s="10">
-        <f t="shared" si="40"/>
-        <v>709.61837313764215</v>
+        <f t="shared" si="44"/>
+        <v>593.4110120989186</v>
       </c>
       <c r="EN15" s="10">
-        <f t="shared" si="40"/>
-        <v>702.52218940626574</v>
+        <f t="shared" si="44"/>
+        <v>587.4769019779294</v>
       </c>
     </row>
     <row r="16" spans="1:144" x14ac:dyDescent="0.3">
@@ -3188,51 +3179,51 @@
         <v>255.2</v>
       </c>
       <c r="Y16" s="1">
-        <f t="shared" ref="Y16" si="41">247.6</f>
+        <f t="shared" ref="Y16" si="45">247.6</f>
         <v>247.6</v>
       </c>
       <c r="Z16" s="1">
-        <f t="shared" ref="Z16:AJ16" si="42">242.6</f>
+        <f t="shared" ref="Z16:AJ16" si="46">242.6</f>
         <v>242.6</v>
       </c>
       <c r="AA16" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>242.6</v>
       </c>
       <c r="AB16" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>242.6</v>
       </c>
       <c r="AC16" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>242.6</v>
       </c>
       <c r="AD16" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>242.6</v>
       </c>
       <c r="AE16" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>242.6</v>
       </c>
       <c r="AF16" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>242.6</v>
       </c>
       <c r="AG16" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>242.6</v>
       </c>
       <c r="AH16" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>242.6</v>
       </c>
       <c r="AI16" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>242.6</v>
       </c>
       <c r="AJ16" s="1">
-        <f t="shared" si="42"/>
+        <f t="shared" si="46"/>
         <v>242.6</v>
       </c>
     </row>
@@ -3241,136 +3232,136 @@
         <v>20</v>
       </c>
       <c r="C17" s="5">
-        <f t="shared" ref="C17:K17" si="43">C15/C16</f>
+        <f t="shared" ref="C17:K17" si="47">C15/C16</f>
         <v>0.95924764890282177</v>
       </c>
       <c r="D17" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>-2.6371473354231973</v>
       </c>
       <c r="E17" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>1.1383228840125397</v>
       </c>
       <c r="F17" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>0.9768808777429463</v>
       </c>
       <c r="G17" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>-4.3103448275861239E-2</v>
       </c>
       <c r="H17" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>1.0740595611285269</v>
       </c>
       <c r="I17" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>1.4177115987460809</v>
       </c>
       <c r="J17" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>1.4157523510971792</v>
       </c>
       <c r="K17" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="47"/>
         <v>1.2276645768025065</v>
       </c>
       <c r="L17" s="5">
-        <f t="shared" ref="L17:N17" si="44">L15/L16</f>
+        <f t="shared" ref="L17:N17" si="48">L15/L16</f>
         <v>1.4728773584905663</v>
       </c>
       <c r="M17" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>1.238506876227897</v>
       </c>
       <c r="N17" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="48"/>
         <v>2.2907915993537968</v>
       </c>
       <c r="O17" s="5">
-        <f t="shared" ref="O17:R17" si="45">O15/O16</f>
+        <f t="shared" ref="O17:R17" si="49">O15/O16</f>
         <v>1.2395622213214426</v>
       </c>
       <c r="P17" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="49"/>
         <v>0.99629018961253135</v>
       </c>
       <c r="Q17" s="5">
-        <f t="shared" si="45"/>
-        <v>1.3664916735366857</v>
+        <f t="shared" si="49"/>
+        <v>1.8462489694971138</v>
       </c>
       <c r="R17" s="5">
-        <f t="shared" si="45"/>
-        <v>1.1333345424567189</v>
+        <f t="shared" si="49"/>
+        <v>1.2372092333058533</v>
       </c>
       <c r="T17" s="5">
-        <f t="shared" ref="T17:Y17" si="46">T15/T16</f>
+        <f t="shared" ref="T17:Y17" si="50">T15/T16</f>
         <v>1.6869122257053271</v>
       </c>
       <c r="U17" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>2.2907523510971801</v>
       </c>
       <c r="V17" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>3.7833072100313463</v>
       </c>
       <c r="W17" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>0.43730407523510789</v>
       </c>
       <c r="X17" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>3.8644200626959222</v>
       </c>
       <c r="Y17" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="50"/>
         <v>6.3424878836833578</v>
       </c>
       <c r="Z17" s="5">
-        <f t="shared" ref="Z17" si="47">Z15/Z16</f>
-        <v>2.5737009068425376</v>
+        <f t="shared" ref="Z17" si="51">Z15/Z16</f>
+        <v>3.2656346248969474</v>
       </c>
       <c r="AA17" s="5">
-        <f t="shared" ref="AA17" si="48">AA15/AA16</f>
-        <v>7.1221429447650459</v>
+        <f t="shared" ref="AA17" si="52">AA15/AA16</f>
+        <v>5.1965278441879637</v>
       </c>
       <c r="AB17" s="5">
-        <f t="shared" ref="AB17" si="49">AB15/AB16</f>
-        <v>7.3284678625803812</v>
+        <f t="shared" ref="AB17" si="53">AB15/AB16</f>
+        <v>5.7031420245259676</v>
       </c>
       <c r="AC17" s="5">
-        <f t="shared" ref="AC17" si="50">AC15/AC16</f>
-        <v>7.5384485132095627</v>
+        <f t="shared" ref="AC17" si="54">AC15/AC16</f>
+        <v>5.8753824907790611</v>
       </c>
       <c r="AD17" s="5">
-        <f t="shared" ref="AD17" si="51">AD15/AD16</f>
-        <v>7.7521696830510365</v>
+        <f t="shared" ref="AD17" si="55">AD15/AD16</f>
+        <v>6.0506435188942396</v>
       </c>
       <c r="AE17" s="5">
-        <f t="shared" ref="AE17" si="52">AE15/AE16</f>
-        <v>7.8855116849829585</v>
+        <f t="shared" ref="AE17" si="56">AE15/AE16</f>
+        <v>6.2289951230955554</v>
       </c>
       <c r="AF17" s="5">
-        <f t="shared" ref="AF17" si="53">AF15/AF16</f>
-        <v>8.0202430249648877</v>
+        <f t="shared" ref="AF17" si="57">AF15/AF16</f>
+        <v>6.4105087858502641</v>
       </c>
       <c r="AG17" s="5">
-        <f t="shared" ref="AG17" si="54">AG15/AG16</f>
-        <v>8.1563950632252631</v>
+        <f t="shared" ref="AG17" si="58">AG15/AG16</f>
+        <v>6.5952574914896616</v>
       </c>
       <c r="AH17" s="5">
-        <f t="shared" ref="AH17" si="55">AH15/AH16</f>
-        <v>8.2939998219979891</v>
+        <f t="shared" ref="AH17" si="59">AH15/AH16</f>
+        <v>6.7833157606078522</v>
       </c>
       <c r="AI17" s="5">
-        <f t="shared" ref="AI17" si="56">AI15/AI16</f>
-        <v>8.4330900039476724</v>
+        <f t="shared" ref="AI17" si="60">AI15/AI16</f>
+        <v>6.9747596852575304</v>
       </c>
       <c r="AJ17" s="5">
-        <f t="shared" ref="AJ17" si="57">AJ15/AJ16</f>
-        <v>8.5736990111113691</v>
+        <f t="shared" ref="AJ17" si="61">AJ15/AJ16</f>
+        <v>7.1696669649620901</v>
       </c>
     </row>
     <row r="19" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -3383,112 +3374,112 @@
         <v>6.311737698835973E-2</v>
       </c>
       <c r="H19" s="8">
-        <f t="shared" ref="H19:N19" si="58">H3/D3-1</f>
+        <f t="shared" ref="H19:N19" si="62">H3/D3-1</f>
         <v>7.5233460476127778E-2</v>
       </c>
       <c r="I19" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>8.3267699308654741E-2</v>
       </c>
       <c r="J19" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>8.0248557478917126E-2</v>
       </c>
       <c r="K19" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>5.5749432908741792E-2</v>
       </c>
       <c r="L19" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>4.7420998980632012E-2</v>
       </c>
       <c r="M19" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>5.0854303833259396E-2</v>
       </c>
       <c r="N19" s="8">
-        <f t="shared" si="58"/>
+        <f t="shared" si="62"/>
         <v>3.3527816583120984E-2</v>
       </c>
       <c r="O19" s="8">
-        <f t="shared" ref="O19" si="59">O3/K3-1</f>
+        <f t="shared" ref="O19" si="63">O3/K3-1</f>
         <v>-3.346830840426418E-3</v>
       </c>
       <c r="P19" s="8">
-        <f t="shared" ref="P19" si="60">P3/L3-1</f>
+        <f t="shared" ref="P19" si="64">P3/L3-1</f>
         <v>-0.238282466521333</v>
       </c>
       <c r="Q19" s="8">
-        <f t="shared" ref="Q19" si="61">Q3/M3-1</f>
-        <v>-0.24238929889298888</v>
+        <f t="shared" ref="Q19" si="65">Q3/M3-1</f>
+        <v>-0.22832103321033215</v>
       </c>
       <c r="R19" s="8">
-        <f t="shared" ref="R19" si="62">R3/N3-1</f>
-        <v>-0.20489782937107426</v>
+        <f t="shared" ref="R19" si="66">R3/N3-1</f>
+        <v>-0.18502027510535102</v>
       </c>
       <c r="U19" s="8">
         <f>U3/T3-1</f>
         <v>0.51134998676683185</v>
       </c>
       <c r="V19" s="8">
-        <f t="shared" ref="V19:AJ19" si="63">V3/U3-1</f>
+        <f t="shared" ref="V19:AJ19" si="67">V3/U3-1</f>
         <v>0.14820302818039743</v>
       </c>
       <c r="W19" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>5.3004528496680026E-2</v>
       </c>
       <c r="X19" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>7.562725611658272E-2</v>
       </c>
       <c r="Y19" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
         <v>4.6776599270798913E-2</v>
       </c>
       <c r="Z19" s="8">
-        <f t="shared" si="63"/>
-        <v>-0.17476746487235317</v>
+        <f t="shared" si="67"/>
+        <v>-0.16619829804076791</v>
       </c>
       <c r="AA19" s="8">
-        <f t="shared" si="63"/>
+        <f t="shared" si="67"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AB19" s="8">
+        <f t="shared" si="67"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AB19" s="8">
-        <f t="shared" si="63"/>
+      <c r="AC19" s="8">
+        <f t="shared" si="67"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AC19" s="8">
-        <f t="shared" si="63"/>
+      <c r="AD19" s="8">
+        <f t="shared" si="67"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AD19" s="8">
-        <f t="shared" si="63"/>
+      <c r="AE19" s="8">
+        <f t="shared" si="67"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AE19" s="8">
-        <f t="shared" si="63"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="AF19" s="8">
-        <f t="shared" si="63"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="67"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG19" s="8">
-        <f t="shared" si="63"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="67"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH19" s="8">
-        <f t="shared" si="63"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="67"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI19" s="8">
-        <f t="shared" si="63"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="67"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ19" s="8">
-        <f t="shared" si="63"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="67"/>
+        <v>2.0000000000000018E-2</v>
       </c>
     </row>
     <row r="20" spans="1:40" x14ac:dyDescent="0.3">
@@ -3496,19 +3487,19 @@
         <v>37</v>
       </c>
       <c r="C20" s="9">
-        <f t="shared" ref="C20:F20" si="64">C5/C3</f>
+        <f t="shared" ref="C20:F20" si="68">C5/C3</f>
         <v>0.55609145295181561</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>0.57810513393835772</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>0.59254397479653453</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="64"/>
+        <f t="shared" si="68"/>
         <v>0.58814913448735018</v>
       </c>
       <c r="G20" s="9">
@@ -3516,116 +3507,116 @@
         <v>0.58654685046239752</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" ref="H20:N20" si="65">H5/H3</f>
+        <f t="shared" ref="H20:N20" si="69">H5/H3</f>
         <v>0.61590214067278293</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0.63020559841660939</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0.62104527898759143</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0.61887447318403432</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0.63465431329803801</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0.63603167281672812</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="65"/>
+        <f t="shared" si="69"/>
         <v>0.621412101455037</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" ref="O20:R20" si="66">O5/O3</f>
+        <f t="shared" ref="O20:R20" si="70">O5/O3</f>
         <v>0.61809211890054305</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="66"/>
+        <f t="shared" si="70"/>
         <v>0.74508100373077124</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" si="66"/>
-        <v>0.75</v>
+        <f t="shared" si="70"/>
+        <v>0.72270372584180109</v>
       </c>
       <c r="R20" s="9">
-        <f t="shared" si="66"/>
-        <v>0.72</v>
+        <f t="shared" si="70"/>
+        <v>0.73</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" ref="T20:AJ20" si="67">T5/T3</f>
+        <f t="shared" ref="T20:AJ20" si="71">T5/T3</f>
         <v>0.57780085099452339</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.50823050810927317</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.55727492432952441</v>
       </c>
       <c r="W20" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.57901421631980032</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.6138962545575074</v>
       </c>
       <c r="Y20" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.6279339006530773</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" si="67"/>
+        <f t="shared" si="71"/>
         <v>0.64</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" si="67"/>
-        <v>0.75</v>
+        <f t="shared" si="71"/>
+        <v>0.73</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" si="67"/>
-        <v>0.75</v>
+        <f t="shared" si="71"/>
+        <v>0.73</v>
       </c>
       <c r="AC20" s="9">
-        <f t="shared" si="67"/>
-        <v>0.75</v>
+        <f t="shared" si="71"/>
+        <v>0.73</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" si="67"/>
-        <v>0.75</v>
+        <f t="shared" si="71"/>
+        <v>0.73</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" si="67"/>
-        <v>0.75</v>
+        <f t="shared" si="71"/>
+        <v>0.73</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" si="67"/>
-        <v>0.75</v>
+        <f t="shared" si="71"/>
+        <v>0.73</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" si="67"/>
-        <v>0.75</v>
+        <f t="shared" si="71"/>
+        <v>0.73</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" si="67"/>
-        <v>0.75</v>
+        <f t="shared" si="71"/>
+        <v>0.73</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" si="67"/>
-        <v>0.75</v>
+        <f t="shared" si="71"/>
+        <v>0.73</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" si="67"/>
-        <v>0.75</v>
+        <f t="shared" si="71"/>
+        <v>0.73</v>
       </c>
       <c r="AM20" t="s">
         <v>40</v>
@@ -3639,19 +3630,19 @@
         <v>38</v>
       </c>
       <c r="C21" s="9">
-        <f t="shared" ref="C21:F21" si="68">C6/C3</f>
+        <f t="shared" ref="C21:F21" si="72">C6/C3</f>
         <v>0.38171868478412091</v>
       </c>
       <c r="D21" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>0.37844710421324917</v>
       </c>
       <c r="E21" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>0.40203027916338491</v>
       </c>
       <c r="F21" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="72"/>
         <v>0.40812250332889483</v>
       </c>
       <c r="G21" s="9">
@@ -3659,115 +3650,115 @@
         <v>0.45502530099459076</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" ref="H21:N21" si="69">H6/H3</f>
+        <f t="shared" ref="H21:N21" si="73">H6/H3</f>
         <v>0.4132517838939857</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.4047340146221271</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.41712548278412359</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.43198909181059419</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.41174867642478979</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.45318265682656828</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.39878349367893773</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" ref="O21:R21" si="70">O6/O3</f>
+        <f t="shared" ref="O21:R21" si="74">O6/O3</f>
         <v>0.42452634633721653</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.52690754842336585</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
+        <v>0.50647539350468218</v>
+      </c>
+      <c r="R21" s="9">
+        <f t="shared" si="74"/>
         <v>0.53</v>
       </c>
-      <c r="R21" s="9">
-        <f t="shared" si="70"/>
-        <v>0.53</v>
-      </c>
       <c r="T21" s="9">
-        <f t="shared" ref="T21:AJ21" si="71">T6/T3</f>
+        <f t="shared" ref="T21:AJ21" si="75">T6/T3</f>
         <v>0.41668193570716022</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0.387803760978501</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0.39785072385555742</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0.39268683987699987</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0.42196304275770635</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0.42403522659806059</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" si="71"/>
-        <v>0.49876855560085381</v>
+        <f t="shared" si="75"/>
+        <v>0.49348476217601828</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
+        <v>0.48999999999999994</v>
+      </c>
+      <c r="AB21" s="9">
+        <f t="shared" si="75"/>
+        <v>0.48</v>
+      </c>
+      <c r="AC21" s="9">
+        <f t="shared" si="75"/>
         <v>0.47999999999999993</v>
       </c>
-      <c r="AB21" s="9">
-        <f t="shared" si="71"/>
+      <c r="AD21" s="9">
+        <f t="shared" si="75"/>
         <v>0.48</v>
       </c>
-      <c r="AC21" s="9">
-        <f t="shared" si="71"/>
-        <v>0.47999999999999993</v>
-      </c>
-      <c r="AD21" s="9">
-        <f t="shared" si="71"/>
+      <c r="AE21" s="9">
+        <f t="shared" si="75"/>
         <v>0.48</v>
       </c>
-      <c r="AE21" s="9">
-        <f t="shared" si="71"/>
-        <v>0.47999999999999993</v>
-      </c>
       <c r="AF21" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
+        <v>0.48000000000000004</v>
+      </c>
+      <c r="AG21" s="9">
+        <f t="shared" si="75"/>
         <v>0.48</v>
       </c>
-      <c r="AG21" s="9">
-        <f t="shared" si="71"/>
+      <c r="AH21" s="9">
+        <f t="shared" si="75"/>
         <v>0.48</v>
       </c>
-      <c r="AH21" s="9">
-        <f t="shared" si="71"/>
+      <c r="AI21" s="9">
+        <f t="shared" si="75"/>
         <v>0.48000000000000004</v>
       </c>
-      <c r="AI21" s="9">
-        <f t="shared" si="71"/>
-        <v>0.47999999999999993</v>
-      </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0.48</v>
       </c>
       <c r="AM21" t="s">
@@ -3782,19 +3773,19 @@
         <v>39</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:F22" si="72">C7/C3</f>
+        <f t="shared" ref="C22:F22" si="76">C7/C3</f>
         <v>0.1743727681676947</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>0.19965802972510854</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>0.1905136956331496</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>0.18002663115845535</v>
       </c>
       <c r="G22" s="9">
@@ -3802,123 +3793,123 @@
         <v>0.13152154946780675</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22:N22" si="73">H7/H3</f>
+        <f t="shared" ref="H22:N22" si="77">H7/H3</f>
         <v>0.20265035677879714</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.22547158379448232</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.2039197962034679</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.1868853813734401</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.22290563687324824</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.18284901599015985</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.22262860777609927</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" ref="O22:R22" si="74">O7/O3</f>
+        <f t="shared" ref="O22:R22" si="78">O7/O3</f>
         <v>0.19356577256332652</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="74"/>
+        <f t="shared" si="78"/>
         <v>0.21817345530740537</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="74"/>
-        <v>0.21999999999999995</v>
+        <f t="shared" si="78"/>
+        <v>0.21622833233711891</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="74"/>
-        <v>0.19</v>
+        <f t="shared" si="78"/>
+        <v>0.2</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22:AJ22" si="75">T7/T3</f>
+        <f t="shared" ref="T22:AJ22" si="79">T7/T3</f>
         <v>0.16111891528736325</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0.12042674713077219</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0.15942420047396699</v>
       </c>
       <c r="W22" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0.18632737644280042</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0.19193321179980105</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="75"/>
+        <f t="shared" si="79"/>
         <v>0.20389867405501677</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" si="75"/>
-        <v>0.14123144439914623</v>
+        <f t="shared" si="79"/>
+        <v>0.14651523782398174</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="75"/>
-        <v>0.27000000000000007</v>
+        <f t="shared" si="79"/>
+        <v>0.24</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="75"/>
-        <v>0.27000000000000007</v>
+        <f t="shared" si="79"/>
+        <v>0.24999999999999994</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="75"/>
-        <v>0.27</v>
+        <f t="shared" si="79"/>
+        <v>0.25</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="75"/>
-        <v>0.27</v>
+        <f t="shared" si="79"/>
+        <v>0.25</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="75"/>
-        <v>0.27000000000000013</v>
+        <f t="shared" si="79"/>
+        <v>0.25000000000000006</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="75"/>
-        <v>0.26999999999999996</v>
+        <f t="shared" si="79"/>
+        <v>0.25</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="75"/>
-        <v>0.27</v>
+        <f t="shared" si="79"/>
+        <v>0.25000000000000006</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="75"/>
-        <v>0.26999999999999996</v>
+        <f t="shared" si="79"/>
+        <v>0.25</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="75"/>
-        <v>0.27000000000000007</v>
+        <f t="shared" si="79"/>
+        <v>0.25</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="75"/>
-        <v>0.27</v>
+        <f t="shared" si="79"/>
+        <v>0.25</v>
       </c>
       <c r="AM22" t="s">
         <v>42</v>
       </c>
       <c r="AN22" s="1">
         <f>NPV(AN21,Z15:EN15)</f>
-        <v>22163.088080340272</v>
+        <v>18241.672417985599</v>
       </c>
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.3">
@@ -3926,19 +3917,19 @@
         <v>18</v>
       </c>
       <c r="C23" s="9">
-        <f t="shared" ref="C23:F23" si="76">C12/C11</f>
+        <f t="shared" ref="C23:F23" si="80">C12/C11</f>
         <v>0.18354430379746831</v>
       </c>
       <c r="D23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>-8.4331576425491148E-2</v>
       </c>
       <c r="E23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>5.2631578947368404E-2</v>
       </c>
       <c r="F23" s="9">
-        <f t="shared" si="76"/>
+        <f t="shared" si="80"/>
         <v>0.16100543478260873</v>
       </c>
       <c r="G23" s="9">
@@ -3946,123 +3937,123 @@
         <v>0.57090909090909314</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ref="H23:N23" si="77">H12/H11</f>
+        <f t="shared" ref="H23:N23" si="81">H12/H11</f>
         <v>0.39207650273224037</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>0.14097654380086172</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>2.5278608317477566E-2</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>5.9490953695185582E-2</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>0.17338979273456648</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>0.15302585977072788</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="81"/>
         <v>0.19543747391848657</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" ref="O23:R23" si="78">O12/O11</f>
+        <f t="shared" ref="O23:R23" si="82">O12/O11</f>
         <v>0.1661947904869763</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
         <v>0.38099838969404171</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="82"/>
+        <v>0.30394997712368471</v>
+      </c>
+      <c r="R23" s="9">
+        <f t="shared" si="82"/>
         <v>0.16</v>
       </c>
-      <c r="R23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.16</v>
-      </c>
       <c r="T23" s="9">
-        <f t="shared" ref="T23:AJ23" si="79">T12/T11</f>
+        <f t="shared" ref="T23:AJ23" si="83">T12/T11</f>
         <v>0.12010040548368425</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0.12994445379565719</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0.16179990426041174</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0.74286987522281789</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0.17864774767074121</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="83"/>
         <v>0.15790881849315075</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.37103168314682372</v>
+        <f t="shared" si="83"/>
+        <v>0.38060045426388622</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.17</v>
+        <f t="shared" si="83"/>
+        <v>0.25</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.17</v>
+        <f t="shared" si="83"/>
+        <v>0.25</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.17</v>
+        <f t="shared" si="83"/>
+        <v>0.25</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.17</v>
+        <f t="shared" si="83"/>
+        <v>0.25</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.17</v>
+        <f t="shared" si="83"/>
+        <v>0.25</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.17</v>
+        <f t="shared" si="83"/>
+        <v>0.25</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.17</v>
+        <f t="shared" si="83"/>
+        <v>0.25</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.17</v>
+        <f t="shared" si="83"/>
+        <v>0.25</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.17</v>
+        <f t="shared" si="83"/>
+        <v>0.25</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="79"/>
-        <v>0.17</v>
+        <f t="shared" si="83"/>
+        <v>0.25</v>
       </c>
       <c r="AM23" t="s">
         <v>43</v>
       </c>
       <c r="AN23" s="1">
         <f>Main!D8</f>
-        <v>-14035.5</v>
+        <v>-13596.4</v>
       </c>
     </row>
     <row r="24" spans="1:40" x14ac:dyDescent="0.3">
@@ -4074,139 +4065,139 @@
         <v>2.2724110745258081E-3</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" ref="D24:N24" si="80">D14/D3</f>
+        <f t="shared" ref="D24:N24" si="84">D14/D3</f>
         <v>3.4635450918497086E-3</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>4.2443335958694314E-3</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>4.1278295605858854E-3</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>2.879078694817658E-3</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>4.1182466870540264E-3</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>5.9781072020034746E-3</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>4.5607691675569068E-3</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>4.0492521279233131E-3</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>5.6446589847399557E-3</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>7.0725707257072567E-3</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="84"/>
         <v>1.2363838753279796E-2</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" ref="O24:R24" si="81">O14/O3</f>
+        <f t="shared" ref="O24:R24" si="85">O14/O3</f>
         <v>2.9020355706645662E-3</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="85"/>
         <v>-1.5076404149844125E-2</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="81"/>
-        <v>-1.5220700152207001E-2</v>
+        <f t="shared" si="85"/>
+        <v>1.2651922693763697E-2</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="81"/>
-        <v>-1.4999999999999999E-2</v>
+        <f t="shared" si="85"/>
+        <v>-1.4634146341463415E-2</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" ref="T24:AJ24" si="82">T14/T3</f>
+        <f t="shared" ref="T24:AJ24" si="86">T14/T3</f>
         <v>7.8788248946436226E-3</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>2.7749339942884856E-3</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>2.6279358971350807E-3</v>
       </c>
       <c r="W24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>3.5429386336289495E-3</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>4.412495856811402E-3</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="86"/>
         <v>7.3025925192954696E-3</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="82"/>
-        <v>-9.8923235569198312E-3</v>
+        <f t="shared" si="86"/>
+        <v>-3.2160827874299822E-3</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="82"/>
-        <v>-9.6522186162178933E-3</v>
+        <f t="shared" si="86"/>
+        <v>-3.1078492320837803E-3</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="82"/>
-        <v>-9.5102742248029219E-3</v>
+        <f t="shared" si="86"/>
+        <v>-3.0324159982953393E-3</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="82"/>
-        <v>-9.3704172509087615E-3</v>
+        <f t="shared" si="86"/>
+        <v>-2.9878216453792308E-3</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="82"/>
-        <v>-9.2326169972189245E-3</v>
+        <f t="shared" si="86"/>
+        <v>-2.9438830917707126E-3</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="82"/>
-        <v>-9.1869109724802157E-3</v>
+        <f t="shared" si="86"/>
+        <v>-2.9005906933623196E-3</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="82"/>
-        <v>-9.1414312151907092E-3</v>
+        <f t="shared" si="86"/>
+        <v>-2.8579349478716968E-3</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="82"/>
-        <v>-9.0961766052145166E-3</v>
+        <f t="shared" si="86"/>
+        <v>-2.8159064927559363E-3</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="82"/>
-        <v>-9.0511460279609785E-3</v>
+        <f t="shared" si="86"/>
+        <v>-2.7744961031565835E-3</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="82"/>
-        <v>-9.0063383743572093E-3</v>
+        <f t="shared" si="86"/>
+        <v>-2.7336946898748687E-3</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="82"/>
-        <v>-8.9617525408207874E-3</v>
+        <f t="shared" si="86"/>
+        <v>-2.6934932973767087E-3</v>
       </c>
       <c r="AM24" t="s">
         <v>44</v>
       </c>
       <c r="AN24" s="1">
         <f>AN22+AN23</f>
-        <v>8127.5880803402724</v>
+        <v>4645.2724179855995</v>
       </c>
     </row>
     <row r="25" spans="1:40" x14ac:dyDescent="0.3">
@@ -4218,139 +4209,139 @@
         <v>0.11352780225386082</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" ref="D25:N25" si="83">D15/D3</f>
+        <f t="shared" ref="D25:N25" si="87">D15/D3</f>
         <v>-0.29505896795124725</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0.1271112277938217</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0.11065246338215708</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>-4.7984644913626716E-3</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0.11176350662589196</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0.14614048551924702</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0.14845098200345144</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0.1294521113957523</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0.14586577390221117</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0.12115621156211556</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="83"/>
+        <f t="shared" si="87"/>
         <v>0.22549097559036338</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" ref="O25:R25" si="84">O15/O3</f>
+        <f t="shared" ref="O25:R25" si="88">O15/O3</f>
         <v>0.12677749678703198</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="88"/>
         <v>0.12352430111923141</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="84"/>
-        <v>0.16819425672247587</v>
+        <f t="shared" si="88"/>
+        <v>0.22310221159593535</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="84"/>
-        <v>0.13747347999999998</v>
+        <f t="shared" si="88"/>
+        <v>0.14641315121951218</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" ref="T25:AJ25" si="85">T15/T3</f>
+        <f t="shared" ref="T25:AJ25" si="89">T15/T3</f>
         <v>8.7644292432663418E-2</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>7.8748855002963566E-2</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>0.11327107628053211</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>1.2433709167075127E-2</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>0.10215031488233337</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="89"/>
         <v>0.15539283593904604</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="85"/>
-        <v>7.4867483632700987E-2</v>
+        <f t="shared" si="89"/>
+        <v>9.4019149340168931E-2</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="85"/>
-        <v>0.20114471306964829</v>
+        <f t="shared" si="89"/>
+        <v>0.14385622008029708</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="85"/>
-        <v>0.20291350467856481</v>
+        <f t="shared" si="89"/>
+        <v>0.15328241995670172</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="85"/>
-        <v>0.20463483494048068</v>
+        <f t="shared" si="89"/>
+        <v>0.15481539111229078</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="85"/>
-        <v>0.20631019566441974</v>
+        <f t="shared" si="89"/>
+        <v>0.15630734435016894</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="85"/>
-        <v>0.20778104521758489</v>
+        <f t="shared" si="89"/>
+        <v>0.15775954204995027</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="85"/>
-        <v>0.20923879074011997</v>
+        <f t="shared" si="89"/>
+        <v>0.15917320977478921</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="85"/>
-        <v>0.21068399870890051</v>
+        <f t="shared" si="89"/>
+        <v>0.16054953736075692</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="85"/>
-        <v>0.21211723011124808</v>
+        <f t="shared" si="89"/>
+        <v>0.16188967997418827</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="85"/>
-        <v>0.21353904066481519</v>
+        <f t="shared" si="89"/>
+        <v>0.16319475913794593</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="85"/>
-        <v>0.21494998103528717</v>
+        <f t="shared" si="89"/>
+        <v>0.16446586372751376</v>
       </c>
       <c r="AM25" t="s">
         <v>45</v>
       </c>
       <c r="AN25" s="11">
         <f>AN24/AJ16</f>
-        <v>33.502011872795848</v>
+        <v>19.1478665209629</v>
       </c>
     </row>
     <row r="26" spans="1:40" x14ac:dyDescent="0.3">
@@ -4359,7 +4350,7 @@
       </c>
       <c r="AN26" s="11">
         <f>Main!D3</f>
-        <v>82.74</v>
+        <v>80.349999999999994</v>
       </c>
     </row>
     <row r="27" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4383,7 +4374,7 @@
       </c>
       <c r="AN27" s="8">
         <f>AN25/AN26-1</f>
-        <v>-0.59509291911051676</v>
+        <v>-0.7616942561174499</v>
       </c>
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.3">

--- a/Financial Analysis/GPN.xlsx
+++ b/Financial Analysis/GPN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCA139F9-34A0-4434-9566-D717CA51358C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3B1FEFC-1D2A-4D19-B53B-EB0FD22F0D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{AC685D6A-8DC8-48D8-9A0E-762C4546B5AC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{AC685D6A-8DC8-48D8-9A0E-762C4546B5AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -409,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -428,7 +428,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -875,14 +874,14 @@
         <v>0</v>
       </c>
       <c r="D3" s="11">
-        <v>80.349999999999994</v>
+        <v>71.349999999999994</v>
       </c>
       <c r="E3" s="3">
-        <v>45965</v>
+        <v>46052</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45965</v>
+        <v>46052</v>
       </c>
       <c r="G3" s="3">
         <v>46071</v>
@@ -905,7 +904,7 @@
       </c>
       <c r="D5" s="1">
         <f>D3*D4</f>
-        <v>19018.844999999998</v>
+        <v>16888.544999999998</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -924,7 +923,7 @@
       <c r="C7" t="s">
         <v>4</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="1">
         <f>973.2+1903.4+13322.8</f>
         <v>16199.4</v>
       </c>
@@ -947,7 +946,7 @@
       </c>
       <c r="D9" s="1">
         <f>D5-D8</f>
-        <v>32615.244999999995</v>
+        <v>30484.945</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -1241,7 +1240,7 @@
         <v>556.70000000000005</v>
       </c>
       <c r="R4" s="1">
-        <f t="shared" ref="Q4:R4" si="7">R3-R5</f>
+        <f t="shared" ref="R4" si="7">R3-R5</f>
         <v>553.5</v>
       </c>
       <c r="T4" s="1">
@@ -1864,7 +1863,7 @@
         <v>-21.5</v>
       </c>
       <c r="R9" s="1">
-        <f t="shared" ref="Q9:R9" si="17">N9*1.01</f>
+        <f t="shared" ref="R9" si="17">N9*1.01</f>
         <v>-43.026000000000003</v>
       </c>
       <c r="T9" s="1">
@@ -1983,7 +1982,7 @@
         <v>143.80000000000001</v>
       </c>
       <c r="R10" s="1">
-        <f t="shared" ref="Q10:R10" si="19">N10*0.99</f>
+        <f t="shared" ref="R10" si="19">N10*0.99</f>
         <v>155.232</v>
       </c>
       <c r="T10" s="1">
@@ -2240,7 +2239,7 @@
         <v>199.3</v>
       </c>
       <c r="R12" s="1">
-        <f t="shared" ref="Q12:R12" si="25">R11*0.16</f>
+        <f t="shared" ref="R12" si="25">R11*0.16</f>
         <v>47.647039999999997</v>
       </c>
       <c r="T12" s="1">
@@ -4350,7 +4349,7 @@
       </c>
       <c r="AN26" s="11">
         <f>Main!D3</f>
-        <v>80.349999999999994</v>
+        <v>71.349999999999994</v>
       </c>
     </row>
     <row r="27" spans="1:40" s="6" customFormat="1" x14ac:dyDescent="0.3">
@@ -4374,7 +4373,7 @@
       </c>
       <c r="AN27" s="8">
         <f>AN25/AN26-1</f>
-        <v>-0.7616942561174499</v>
+        <v>-0.73163466684004341</v>
       </c>
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.3">
